--- a/samples/Blank-Template.xlsx
+++ b/samples/Blank-Template.xlsx
@@ -36,7 +36,7 @@
     <numFmt numFmtId="169" formatCode="0.0%"/>
     <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0;-&quot;$&quot;#,##0;&quot;$&quot;0"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,6 +60,12 @@
       <i val="1"/>
       <color rgb="006B7280"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="006B7280"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -210,33 +216,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="9" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="10" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="9" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="10" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="10" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -269,33 +278,33 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="6" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="11" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="7" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="7" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="12" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="1" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="1" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="1" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1502,21 +1511,13 @@
       <c r="AC3" s="1" t="n"/>
       <c r="AD3" s="1" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" ht="14" customHeight="1">
       <c r="A4" s="1" t="n"/>
-      <c r="B4" s="1" t="n"/>
-      <c r="C4" s="1" t="n"/>
-      <c r="D4" s="1" t="n"/>
-      <c r="E4" s="1" t="n"/>
-      <c r="F4" s="1" t="n"/>
-      <c r="G4" s="1" t="n"/>
-      <c r="H4" s="1" t="n"/>
-      <c r="I4" s="1" t="n"/>
-      <c r="J4" s="1" t="n"/>
-      <c r="K4" s="1" t="n"/>
-      <c r="L4" s="1" t="n"/>
-      <c r="M4" s="1" t="n"/>
-      <c r="N4" s="1" t="n"/>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Budget Planner - Claude Skill by 6inq</t>
+        </is>
+      </c>
       <c r="O4" s="1" t="n"/>
       <c r="P4" s="1" t="n"/>
       <c r="Q4" s="1" t="n"/>
@@ -1536,43 +1537,43 @@
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="1" t="n"/>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>MONEY IN</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>MONEY OUT</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>NET SAVINGS</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>SAVINGS RATE</t>
         </is>
       </c>
-      <c r="I5" s="5" t="n"/>
+      <c r="I5" s="6" t="n"/>
       <c r="J5" s="1" t="n"/>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>AVG MONTHLY SPEND</t>
         </is>
       </c>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="L5" s="6" t="n"/>
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>PAYCHECKS</t>
         </is>
       </c>
-      <c r="N5" s="5" t="n"/>
+      <c r="N5" s="6" t="n"/>
       <c r="O5" s="1" t="n"/>
       <c r="P5" s="1" t="n"/>
       <c r="Q5" s="1" t="n"/>
@@ -1592,37 +1593,37 @@
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="1" t="n"/>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>D42</f>
         <v/>
       </c>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="6">
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="7">
         <f>G42</f>
         <v/>
       </c>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="6">
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="7">
         <f>H42</f>
         <v/>
       </c>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="8">
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="9">
         <f>IFERROR(H42/D42,0)</f>
         <v/>
       </c>
-      <c r="I6" s="7" t="n"/>
+      <c r="I6" s="8" t="n"/>
       <c r="J6" s="1" t="n"/>
-      <c r="K6" s="6">
+      <c r="K6" s="7">
         <f>G42/12</f>
         <v/>
       </c>
-      <c r="L6" s="7" t="n"/>
-      <c r="M6" s="9">
+      <c r="L6" s="8" t="n"/>
+      <c r="M6" s="10">
         <f>C42</f>
         <v/>
       </c>
-      <c r="N6" s="7" t="n"/>
+      <c r="N6" s="8" t="n"/>
       <c r="O6" s="1" t="n"/>
       <c r="P6" s="1" t="n"/>
       <c r="Q6" s="1" t="n"/>
@@ -1642,43 +1643,43 @@
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="1" t="n"/>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>earned this year</t>
         </is>
       </c>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="C7" s="12" t="n"/>
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>bills + expenses</t>
         </is>
       </c>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>money in - money out</t>
         </is>
       </c>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="G7" s="12" t="n"/>
+      <c r="H7" s="11" t="inlineStr">
         <is>
           <t>of income kept</t>
         </is>
       </c>
-      <c r="I7" s="11" t="n"/>
+      <c r="I7" s="12" t="n"/>
       <c r="J7" s="1" t="n"/>
-      <c r="K7" s="10" t="inlineStr">
+      <c r="K7" s="11" t="inlineStr">
         <is>
           <t>money out / 12</t>
         </is>
       </c>
-      <c r="L7" s="11" t="n"/>
-      <c r="M7" s="10" t="inlineStr">
+      <c r="L7" s="12" t="n"/>
+      <c r="M7" s="11" t="inlineStr">
         <is>
           <t>paydays this year</t>
         </is>
       </c>
-      <c r="N7" s="11" t="n"/>
+      <c r="N7" s="12" t="n"/>
       <c r="O7" s="1" t="n"/>
       <c r="P7" s="1" t="n"/>
       <c r="Q7" s="1" t="n"/>
@@ -2338,7 +2339,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n"/>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>Monthly Breakdown</t>
         </is>
@@ -2351,7 +2352,7 @@
       <c r="H28" s="1" t="n"/>
       <c r="I28" s="1" t="n"/>
       <c r="J28" s="1" t="n"/>
-      <c r="K28" s="12" t="inlineStr">
+      <c r="K28" s="13" t="inlineStr">
         <is>
           <t>Spending by Category</t>
         </is>
@@ -2378,63 +2379,63 @@
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="1" t="n"/>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>Paychecks</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="D29" s="14" t="inlineStr">
         <is>
           <t>Money In</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="E29" s="14" t="inlineStr">
         <is>
           <t>Bills</t>
         </is>
       </c>
-      <c r="F29" s="13" t="inlineStr">
+      <c r="F29" s="14" t="inlineStr">
         <is>
           <t>Expenses</t>
         </is>
       </c>
-      <c r="G29" s="13" t="inlineStr">
+      <c r="G29" s="14" t="inlineStr">
         <is>
           <t>Money Out</t>
         </is>
       </c>
-      <c r="H29" s="13" t="inlineStr">
+      <c r="H29" s="14" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="I29" s="13" t="inlineStr">
+      <c r="I29" s="14" t="inlineStr">
         <is>
           <t>Savings Rate</t>
         </is>
       </c>
       <c r="J29" s="1" t="n"/>
-      <c r="K29" s="13" t="inlineStr">
+      <c r="K29" s="14" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="L29" s="13" t="inlineStr">
+      <c r="L29" s="14" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="M29" s="13" t="inlineStr">
+      <c r="M29" s="14" t="inlineStr">
         <is>
           <t>Monthly Avg</t>
         </is>
       </c>
-      <c r="N29" s="13" t="inlineStr">
+      <c r="N29" s="14" t="inlineStr">
         <is>
           <t>% of Spend</t>
         </is>
@@ -2458,52 +2459,52 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
-      <c r="B30" s="14" t="n">
+      <c r="B30" s="15" t="n">
         <v>46023</v>
       </c>
-      <c r="C30" s="15">
+      <c r="C30" s="16">
         <f>COUNTIFS('Paychecks'!$D$6:$D$35,B30)</f>
         <v/>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="17">
         <f>'Income'!D22</f>
         <v/>
       </c>
-      <c r="E30" s="16">
+      <c r="E30" s="17">
         <f>SUMIFS('Expenses'!$F$6:$F$65,'Expenses'!$D$6:$D$65,"Bill")</f>
         <v/>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="17">
         <f>SUMIFS('Expenses'!$F$6:$F$65,'Expenses'!$D$6:$D$65,"Expense")</f>
         <v/>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="17">
         <f>E30+F30</f>
         <v/>
       </c>
-      <c r="H30" s="16">
+      <c r="H30" s="17">
         <f>D30-G30</f>
         <v/>
       </c>
-      <c r="I30" s="17">
+      <c r="I30" s="18">
         <f>IFERROR(H30/D30,0)</f>
         <v/>
       </c>
       <c r="J30" s="1" t="n"/>
-      <c r="K30" s="18" t="inlineStr">
+      <c r="K30" s="19" t="inlineStr">
         <is>
           <t>Housing</t>
         </is>
       </c>
-      <c r="L30" s="16">
+      <c r="L30" s="17">
         <f>SUMIF('Expenses'!$C$6:$C$65,K30,'Expenses'!$R$6:$R$65)</f>
         <v/>
       </c>
-      <c r="M30" s="16">
+      <c r="M30" s="17">
         <f>L30/12</f>
         <v/>
       </c>
-      <c r="N30" s="17">
+      <c r="N30" s="18">
         <f>IFERROR(L30/$L$43,0)</f>
         <v/>
       </c>
@@ -2526,52 +2527,52 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
-      <c r="B31" s="19" t="n">
+      <c r="B31" s="20" t="n">
         <v>46054</v>
       </c>
-      <c r="C31" s="20">
+      <c r="C31" s="21">
         <f>COUNTIFS('Paychecks'!$D$6:$D$35,B31)</f>
         <v/>
       </c>
-      <c r="D31" s="21">
+      <c r="D31" s="22">
         <f>'Income'!E22</f>
         <v/>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="22">
         <f>SUMIFS('Expenses'!$G$6:$G$65,'Expenses'!$D$6:$D$65,"Bill")</f>
         <v/>
       </c>
-      <c r="F31" s="21">
+      <c r="F31" s="22">
         <f>SUMIFS('Expenses'!$G$6:$G$65,'Expenses'!$D$6:$D$65,"Expense")</f>
         <v/>
       </c>
-      <c r="G31" s="21">
+      <c r="G31" s="22">
         <f>E31+F31</f>
         <v/>
       </c>
-      <c r="H31" s="21">
+      <c r="H31" s="22">
         <f>D31-G31</f>
         <v/>
       </c>
-      <c r="I31" s="22">
+      <c r="I31" s="23">
         <f>IFERROR(H31/D31,0)</f>
         <v/>
       </c>
       <c r="J31" s="1" t="n"/>
-      <c r="K31" s="23" t="inlineStr">
+      <c r="K31" s="24" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
       </c>
-      <c r="L31" s="21">
+      <c r="L31" s="22">
         <f>SUMIF('Expenses'!$C$6:$C$65,K31,'Expenses'!$R$6:$R$65)</f>
         <v/>
       </c>
-      <c r="M31" s="21">
+      <c r="M31" s="22">
         <f>L31/12</f>
         <v/>
       </c>
-      <c r="N31" s="22">
+      <c r="N31" s="23">
         <f>IFERROR(L31/$L$43,0)</f>
         <v/>
       </c>
@@ -2594,52 +2595,52 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
-      <c r="B32" s="14" t="n">
+      <c r="B32" s="15" t="n">
         <v>46082</v>
       </c>
-      <c r="C32" s="15">
+      <c r="C32" s="16">
         <f>COUNTIFS('Paychecks'!$D$6:$D$35,B32)</f>
         <v/>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="17">
         <f>'Income'!F22</f>
         <v/>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="17">
         <f>SUMIFS('Expenses'!$H$6:$H$65,'Expenses'!$D$6:$D$65,"Bill")</f>
         <v/>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="17">
         <f>SUMIFS('Expenses'!$H$6:$H$65,'Expenses'!$D$6:$D$65,"Expense")</f>
         <v/>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="17">
         <f>E32+F32</f>
         <v/>
       </c>
-      <c r="H32" s="16">
+      <c r="H32" s="17">
         <f>D32-G32</f>
         <v/>
       </c>
-      <c r="I32" s="17">
+      <c r="I32" s="18">
         <f>IFERROR(H32/D32,0)</f>
         <v/>
       </c>
       <c r="J32" s="1" t="n"/>
-      <c r="K32" s="18" t="inlineStr">
+      <c r="K32" s="19" t="inlineStr">
         <is>
           <t>Transportation</t>
         </is>
       </c>
-      <c r="L32" s="16">
+      <c r="L32" s="17">
         <f>SUMIF('Expenses'!$C$6:$C$65,K32,'Expenses'!$R$6:$R$65)</f>
         <v/>
       </c>
-      <c r="M32" s="16">
+      <c r="M32" s="17">
         <f>L32/12</f>
         <v/>
       </c>
-      <c r="N32" s="17">
+      <c r="N32" s="18">
         <f>IFERROR(L32/$L$43,0)</f>
         <v/>
       </c>
@@ -2662,52 +2663,52 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
-      <c r="B33" s="19" t="n">
+      <c r="B33" s="20" t="n">
         <v>46113</v>
       </c>
-      <c r="C33" s="20">
+      <c r="C33" s="21">
         <f>COUNTIFS('Paychecks'!$D$6:$D$35,B33)</f>
         <v/>
       </c>
-      <c r="D33" s="21">
+      <c r="D33" s="22">
         <f>'Income'!G22</f>
         <v/>
       </c>
-      <c r="E33" s="21">
+      <c r="E33" s="22">
         <f>SUMIFS('Expenses'!$I$6:$I$65,'Expenses'!$D$6:$D$65,"Bill")</f>
         <v/>
       </c>
-      <c r="F33" s="21">
+      <c r="F33" s="22">
         <f>SUMIFS('Expenses'!$I$6:$I$65,'Expenses'!$D$6:$D$65,"Expense")</f>
         <v/>
       </c>
-      <c r="G33" s="21">
+      <c r="G33" s="22">
         <f>E33+F33</f>
         <v/>
       </c>
-      <c r="H33" s="21">
+      <c r="H33" s="22">
         <f>D33-G33</f>
         <v/>
       </c>
-      <c r="I33" s="22">
+      <c r="I33" s="23">
         <f>IFERROR(H33/D33,0)</f>
         <v/>
       </c>
       <c r="J33" s="1" t="n"/>
-      <c r="K33" s="23" t="inlineStr">
+      <c r="K33" s="24" t="inlineStr">
         <is>
           <t>Food</t>
         </is>
       </c>
-      <c r="L33" s="21">
+      <c r="L33" s="22">
         <f>SUMIF('Expenses'!$C$6:$C$65,K33,'Expenses'!$R$6:$R$65)</f>
         <v/>
       </c>
-      <c r="M33" s="21">
+      <c r="M33" s="22">
         <f>L33/12</f>
         <v/>
       </c>
-      <c r="N33" s="22">
+      <c r="N33" s="23">
         <f>IFERROR(L33/$L$43,0)</f>
         <v/>
       </c>
@@ -2730,52 +2731,52 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n"/>
-      <c r="B34" s="14" t="n">
+      <c r="B34" s="15" t="n">
         <v>46143</v>
       </c>
-      <c r="C34" s="15">
+      <c r="C34" s="16">
         <f>COUNTIFS('Paychecks'!$D$6:$D$35,B34)</f>
         <v/>
       </c>
-      <c r="D34" s="16">
+      <c r="D34" s="17">
         <f>'Income'!H22</f>
         <v/>
       </c>
-      <c r="E34" s="16">
+      <c r="E34" s="17">
         <f>SUMIFS('Expenses'!$J$6:$J$65,'Expenses'!$D$6:$D$65,"Bill")</f>
         <v/>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="17">
         <f>SUMIFS('Expenses'!$J$6:$J$65,'Expenses'!$D$6:$D$65,"Expense")</f>
         <v/>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="17">
         <f>E34+F34</f>
         <v/>
       </c>
-      <c r="H34" s="16">
+      <c r="H34" s="17">
         <f>D34-G34</f>
         <v/>
       </c>
-      <c r="I34" s="17">
+      <c r="I34" s="18">
         <f>IFERROR(H34/D34,0)</f>
         <v/>
       </c>
       <c r="J34" s="1" t="n"/>
-      <c r="K34" s="18" t="inlineStr">
+      <c r="K34" s="19" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="L34" s="16">
+      <c r="L34" s="17">
         <f>SUMIF('Expenses'!$C$6:$C$65,K34,'Expenses'!$R$6:$R$65)</f>
         <v/>
       </c>
-      <c r="M34" s="16">
+      <c r="M34" s="17">
         <f>L34/12</f>
         <v/>
       </c>
-      <c r="N34" s="17">
+      <c r="N34" s="18">
         <f>IFERROR(L34/$L$43,0)</f>
         <v/>
       </c>
@@ -2798,52 +2799,52 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n"/>
-      <c r="B35" s="19" t="n">
+      <c r="B35" s="20" t="n">
         <v>46174</v>
       </c>
-      <c r="C35" s="20">
+      <c r="C35" s="21">
         <f>COUNTIFS('Paychecks'!$D$6:$D$35,B35)</f>
         <v/>
       </c>
-      <c r="D35" s="21">
+      <c r="D35" s="22">
         <f>'Income'!I22</f>
         <v/>
       </c>
-      <c r="E35" s="21">
+      <c r="E35" s="22">
         <f>SUMIFS('Expenses'!$K$6:$K$65,'Expenses'!$D$6:$D$65,"Bill")</f>
         <v/>
       </c>
-      <c r="F35" s="21">
+      <c r="F35" s="22">
         <f>SUMIFS('Expenses'!$K$6:$K$65,'Expenses'!$D$6:$D$65,"Expense")</f>
         <v/>
       </c>
-      <c r="G35" s="21">
+      <c r="G35" s="22">
         <f>E35+F35</f>
         <v/>
       </c>
-      <c r="H35" s="21">
+      <c r="H35" s="22">
         <f>D35-G35</f>
         <v/>
       </c>
-      <c r="I35" s="22">
+      <c r="I35" s="23">
         <f>IFERROR(H35/D35,0)</f>
         <v/>
       </c>
       <c r="J35" s="1" t="n"/>
-      <c r="K35" s="23" t="inlineStr">
+      <c r="K35" s="24" t="inlineStr">
         <is>
           <t>Health</t>
         </is>
       </c>
-      <c r="L35" s="21">
+      <c r="L35" s="22">
         <f>SUMIF('Expenses'!$C$6:$C$65,K35,'Expenses'!$R$6:$R$65)</f>
         <v/>
       </c>
-      <c r="M35" s="21">
+      <c r="M35" s="22">
         <f>L35/12</f>
         <v/>
       </c>
-      <c r="N35" s="22">
+      <c r="N35" s="23">
         <f>IFERROR(L35/$L$43,0)</f>
         <v/>
       </c>
@@ -2866,52 +2867,52 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n"/>
-      <c r="B36" s="14" t="n">
+      <c r="B36" s="15" t="n">
         <v>46204</v>
       </c>
-      <c r="C36" s="15">
+      <c r="C36" s="16">
         <f>COUNTIFS('Paychecks'!$D$6:$D$35,B36)</f>
         <v/>
       </c>
-      <c r="D36" s="16">
+      <c r="D36" s="17">
         <f>'Income'!J22</f>
         <v/>
       </c>
-      <c r="E36" s="16">
+      <c r="E36" s="17">
         <f>SUMIFS('Expenses'!$L$6:$L$65,'Expenses'!$D$6:$D$65,"Bill")</f>
         <v/>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="17">
         <f>SUMIFS('Expenses'!$L$6:$L$65,'Expenses'!$D$6:$D$65,"Expense")</f>
         <v/>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="17">
         <f>E36+F36</f>
         <v/>
       </c>
-      <c r="H36" s="16">
+      <c r="H36" s="17">
         <f>D36-G36</f>
         <v/>
       </c>
-      <c r="I36" s="17">
+      <c r="I36" s="18">
         <f>IFERROR(H36/D36,0)</f>
         <v/>
       </c>
       <c r="J36" s="1" t="n"/>
-      <c r="K36" s="18" t="inlineStr">
+      <c r="K36" s="19" t="inlineStr">
         <is>
           <t>Debt Payments</t>
         </is>
       </c>
-      <c r="L36" s="16">
+      <c r="L36" s="17">
         <f>SUMIF('Expenses'!$C$6:$C$65,K36,'Expenses'!$R$6:$R$65)</f>
         <v/>
       </c>
-      <c r="M36" s="16">
+      <c r="M36" s="17">
         <f>L36/12</f>
         <v/>
       </c>
-      <c r="N36" s="17">
+      <c r="N36" s="18">
         <f>IFERROR(L36/$L$43,0)</f>
         <v/>
       </c>
@@ -2934,52 +2935,52 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n"/>
-      <c r="B37" s="19" t="n">
+      <c r="B37" s="20" t="n">
         <v>46235</v>
       </c>
-      <c r="C37" s="20">
+      <c r="C37" s="21">
         <f>COUNTIFS('Paychecks'!$D$6:$D$35,B37)</f>
         <v/>
       </c>
-      <c r="D37" s="21">
+      <c r="D37" s="22">
         <f>'Income'!K22</f>
         <v/>
       </c>
-      <c r="E37" s="21">
+      <c r="E37" s="22">
         <f>SUMIFS('Expenses'!$M$6:$M$65,'Expenses'!$D$6:$D$65,"Bill")</f>
         <v/>
       </c>
-      <c r="F37" s="21">
+      <c r="F37" s="22">
         <f>SUMIFS('Expenses'!$M$6:$M$65,'Expenses'!$D$6:$D$65,"Expense")</f>
         <v/>
       </c>
-      <c r="G37" s="21">
+      <c r="G37" s="22">
         <f>E37+F37</f>
         <v/>
       </c>
-      <c r="H37" s="21">
+      <c r="H37" s="22">
         <f>D37-G37</f>
         <v/>
       </c>
-      <c r="I37" s="22">
+      <c r="I37" s="23">
         <f>IFERROR(H37/D37,0)</f>
         <v/>
       </c>
       <c r="J37" s="1" t="n"/>
-      <c r="K37" s="23" t="inlineStr">
+      <c r="K37" s="24" t="inlineStr">
         <is>
           <t>Subscriptions</t>
         </is>
       </c>
-      <c r="L37" s="21">
+      <c r="L37" s="22">
         <f>SUMIF('Expenses'!$C$6:$C$65,K37,'Expenses'!$R$6:$R$65)</f>
         <v/>
       </c>
-      <c r="M37" s="21">
+      <c r="M37" s="22">
         <f>L37/12</f>
         <v/>
       </c>
-      <c r="N37" s="22">
+      <c r="N37" s="23">
         <f>IFERROR(L37/$L$43,0)</f>
         <v/>
       </c>
@@ -3002,52 +3003,52 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n"/>
-      <c r="B38" s="14" t="n">
+      <c r="B38" s="15" t="n">
         <v>46266</v>
       </c>
-      <c r="C38" s="15">
+      <c r="C38" s="16">
         <f>COUNTIFS('Paychecks'!$D$6:$D$35,B38)</f>
         <v/>
       </c>
-      <c r="D38" s="16">
+      <c r="D38" s="17">
         <f>'Income'!L22</f>
         <v/>
       </c>
-      <c r="E38" s="16">
+      <c r="E38" s="17">
         <f>SUMIFS('Expenses'!$N$6:$N$65,'Expenses'!$D$6:$D$65,"Bill")</f>
         <v/>
       </c>
-      <c r="F38" s="16">
+      <c r="F38" s="17">
         <f>SUMIFS('Expenses'!$N$6:$N$65,'Expenses'!$D$6:$D$65,"Expense")</f>
         <v/>
       </c>
-      <c r="G38" s="16">
+      <c r="G38" s="17">
         <f>E38+F38</f>
         <v/>
       </c>
-      <c r="H38" s="16">
+      <c r="H38" s="17">
         <f>D38-G38</f>
         <v/>
       </c>
-      <c r="I38" s="17">
+      <c r="I38" s="18">
         <f>IFERROR(H38/D38,0)</f>
         <v/>
       </c>
       <c r="J38" s="1" t="n"/>
-      <c r="K38" s="18" t="inlineStr">
+      <c r="K38" s="19" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="L38" s="16">
+      <c r="L38" s="17">
         <f>SUMIF('Expenses'!$C$6:$C$65,K38,'Expenses'!$R$6:$R$65)</f>
         <v/>
       </c>
-      <c r="M38" s="16">
+      <c r="M38" s="17">
         <f>L38/12</f>
         <v/>
       </c>
-      <c r="N38" s="17">
+      <c r="N38" s="18">
         <f>IFERROR(L38/$L$43,0)</f>
         <v/>
       </c>
@@ -3070,52 +3071,52 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n"/>
-      <c r="B39" s="19" t="n">
+      <c r="B39" s="20" t="n">
         <v>46296</v>
       </c>
-      <c r="C39" s="20">
+      <c r="C39" s="21">
         <f>COUNTIFS('Paychecks'!$D$6:$D$35,B39)</f>
         <v/>
       </c>
-      <c r="D39" s="21">
+      <c r="D39" s="22">
         <f>'Income'!M22</f>
         <v/>
       </c>
-      <c r="E39" s="21">
+      <c r="E39" s="22">
         <f>SUMIFS('Expenses'!$O$6:$O$65,'Expenses'!$D$6:$D$65,"Bill")</f>
         <v/>
       </c>
-      <c r="F39" s="21">
+      <c r="F39" s="22">
         <f>SUMIFS('Expenses'!$O$6:$O$65,'Expenses'!$D$6:$D$65,"Expense")</f>
         <v/>
       </c>
-      <c r="G39" s="21">
+      <c r="G39" s="22">
         <f>E39+F39</f>
         <v/>
       </c>
-      <c r="H39" s="21">
+      <c r="H39" s="22">
         <f>D39-G39</f>
         <v/>
       </c>
-      <c r="I39" s="22">
+      <c r="I39" s="23">
         <f>IFERROR(H39/D39,0)</f>
         <v/>
       </c>
       <c r="J39" s="1" t="n"/>
-      <c r="K39" s="23" t="inlineStr">
+      <c r="K39" s="24" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="L39" s="21">
+      <c r="L39" s="22">
         <f>SUMIF('Expenses'!$C$6:$C$65,K39,'Expenses'!$R$6:$R$65)</f>
         <v/>
       </c>
-      <c r="M39" s="21">
+      <c r="M39" s="22">
         <f>L39/12</f>
         <v/>
       </c>
-      <c r="N39" s="22">
+      <c r="N39" s="23">
         <f>IFERROR(L39/$L$43,0)</f>
         <v/>
       </c>
@@ -3138,52 +3139,52 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n"/>
-      <c r="B40" s="14" t="n">
+      <c r="B40" s="15" t="n">
         <v>46327</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="16">
         <f>COUNTIFS('Paychecks'!$D$6:$D$35,B40)</f>
         <v/>
       </c>
-      <c r="D40" s="16">
+      <c r="D40" s="17">
         <f>'Income'!N22</f>
         <v/>
       </c>
-      <c r="E40" s="16">
+      <c r="E40" s="17">
         <f>SUMIFS('Expenses'!$P$6:$P$65,'Expenses'!$D$6:$D$65,"Bill")</f>
         <v/>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="17">
         <f>SUMIFS('Expenses'!$P$6:$P$65,'Expenses'!$D$6:$D$65,"Expense")</f>
         <v/>
       </c>
-      <c r="G40" s="16">
+      <c r="G40" s="17">
         <f>E40+F40</f>
         <v/>
       </c>
-      <c r="H40" s="16">
+      <c r="H40" s="17">
         <f>D40-G40</f>
         <v/>
       </c>
-      <c r="I40" s="17">
+      <c r="I40" s="18">
         <f>IFERROR(H40/D40,0)</f>
         <v/>
       </c>
       <c r="J40" s="1" t="n"/>
-      <c r="K40" s="18" t="inlineStr">
+      <c r="K40" s="19" t="inlineStr">
         <is>
           <t>Savings</t>
         </is>
       </c>
-      <c r="L40" s="16">
+      <c r="L40" s="17">
         <f>SUMIF('Expenses'!$C$6:$C$65,K40,'Expenses'!$R$6:$R$65)</f>
         <v/>
       </c>
-      <c r="M40" s="16">
+      <c r="M40" s="17">
         <f>L40/12</f>
         <v/>
       </c>
-      <c r="N40" s="17">
+      <c r="N40" s="18">
         <f>IFERROR(L40/$L$43,0)</f>
         <v/>
       </c>
@@ -3206,52 +3207,52 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n"/>
-      <c r="B41" s="19" t="n">
+      <c r="B41" s="20" t="n">
         <v>46357</v>
       </c>
-      <c r="C41" s="20">
+      <c r="C41" s="21">
         <f>COUNTIFS('Paychecks'!$D$6:$D$35,B41)</f>
         <v/>
       </c>
-      <c r="D41" s="21">
+      <c r="D41" s="22">
         <f>'Income'!O22</f>
         <v/>
       </c>
-      <c r="E41" s="21">
+      <c r="E41" s="22">
         <f>SUMIFS('Expenses'!$Q$6:$Q$65,'Expenses'!$D$6:$D$65,"Bill")</f>
         <v/>
       </c>
-      <c r="F41" s="21">
+      <c r="F41" s="22">
         <f>SUMIFS('Expenses'!$Q$6:$Q$65,'Expenses'!$D$6:$D$65,"Expense")</f>
         <v/>
       </c>
-      <c r="G41" s="21">
+      <c r="G41" s="22">
         <f>E41+F41</f>
         <v/>
       </c>
-      <c r="H41" s="21">
+      <c r="H41" s="22">
         <f>D41-G41</f>
         <v/>
       </c>
-      <c r="I41" s="22">
+      <c r="I41" s="23">
         <f>IFERROR(H41/D41,0)</f>
         <v/>
       </c>
       <c r="J41" s="1" t="n"/>
-      <c r="K41" s="23" t="inlineStr">
+      <c r="K41" s="24" t="inlineStr">
         <is>
           <t>Giving</t>
         </is>
       </c>
-      <c r="L41" s="21">
+      <c r="L41" s="22">
         <f>SUMIF('Expenses'!$C$6:$C$65,K41,'Expenses'!$R$6:$R$65)</f>
         <v/>
       </c>
-      <c r="M41" s="21">
+      <c r="M41" s="22">
         <f>L41/12</f>
         <v/>
       </c>
-      <c r="N41" s="22">
+      <c r="N41" s="23">
         <f>IFERROR(L41/$L$43,0)</f>
         <v/>
       </c>
@@ -3274,54 +3275,54 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n"/>
-      <c r="B42" s="24" t="inlineStr">
+      <c r="B42" s="25" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C42" s="25">
+      <c r="C42" s="26">
         <f>SUM(C30:C41)</f>
         <v/>
       </c>
-      <c r="D42" s="26">
+      <c r="D42" s="27">
         <f>SUM(D30:D41)</f>
         <v/>
       </c>
-      <c r="E42" s="26">
+      <c r="E42" s="27">
         <f>SUM(E30:E41)</f>
         <v/>
       </c>
-      <c r="F42" s="26">
+      <c r="F42" s="27">
         <f>SUM(F30:F41)</f>
         <v/>
       </c>
-      <c r="G42" s="26">
+      <c r="G42" s="27">
         <f>SUM(G30:G41)</f>
         <v/>
       </c>
-      <c r="H42" s="26">
+      <c r="H42" s="27">
         <f>SUM(H30:H41)</f>
         <v/>
       </c>
-      <c r="I42" s="27">
+      <c r="I42" s="28">
         <f>IFERROR(H42/D42,0)</f>
         <v/>
       </c>
       <c r="J42" s="1" t="n"/>
-      <c r="K42" s="18" t="inlineStr">
+      <c r="K42" s="19" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="L42" s="16">
+      <c r="L42" s="17">
         <f>SUMIF('Expenses'!$C$6:$C$65,K42,'Expenses'!$R$6:$R$65)</f>
         <v/>
       </c>
-      <c r="M42" s="16">
+      <c r="M42" s="17">
         <f>L42/12</f>
         <v/>
       </c>
-      <c r="N42" s="17">
+      <c r="N42" s="18">
         <f>IFERROR(L42/$L$43,0)</f>
         <v/>
       </c>
@@ -3353,20 +3354,20 @@
       <c r="H43" s="1" t="n"/>
       <c r="I43" s="1" t="n"/>
       <c r="J43" s="1" t="n"/>
-      <c r="K43" s="24" t="inlineStr">
+      <c r="K43" s="25" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="L43" s="28">
+      <c r="L43" s="29">
         <f>SUM(L30:L42)</f>
         <v/>
       </c>
-      <c r="M43" s="28">
+      <c r="M43" s="29">
         <f>SUM(M30:M42)</f>
         <v/>
       </c>
-      <c r="N43" s="29">
+      <c r="N43" s="30">
         <f>IF(L43&gt;0,1,0)</f>
         <v/>
       </c>
@@ -3453,7 +3454,7 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n"/>
-      <c r="B46" s="12" t="inlineStr">
+      <c r="B46" s="13" t="inlineStr">
         <is>
           <t>Debt Tracker</t>
         </is>
@@ -3489,18 +3490,18 @@
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="1" t="n"/>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>TOTAL DEBT</t>
         </is>
       </c>
-      <c r="C47" s="5" t="n"/>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>MIN PAYMENTS</t>
         </is>
       </c>
-      <c r="E47" s="5" t="n"/>
+      <c r="E47" s="6" t="n"/>
       <c r="F47" s="1" t="n"/>
       <c r="G47" s="1" t="n"/>
       <c r="H47" s="1" t="n"/>
@@ -3529,16 +3530,16 @@
     </row>
     <row r="48" ht="32.4" customHeight="1">
       <c r="A48" s="1" t="n"/>
-      <c r="B48" s="30">
+      <c r="B48" s="31">
         <f>'Debt Tracker'!C16</f>
         <v/>
       </c>
-      <c r="C48" s="7" t="n"/>
-      <c r="D48" s="30">
+      <c r="C48" s="8" t="n"/>
+      <c r="D48" s="31">
         <f>'Debt Tracker'!E16</f>
         <v/>
       </c>
-      <c r="E48" s="7" t="n"/>
+      <c r="E48" s="8" t="n"/>
       <c r="F48" s="1" t="n"/>
       <c r="G48" s="1" t="n"/>
       <c r="H48" s="1" t="n"/>
@@ -3567,18 +3568,18 @@
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="1" t="n"/>
-      <c r="B49" s="10" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>current balances</t>
         </is>
       </c>
-      <c r="C49" s="11" t="n"/>
-      <c r="D49" s="10" t="inlineStr">
+      <c r="C49" s="12" t="n"/>
+      <c r="D49" s="11" t="inlineStr">
         <is>
           <t>per month</t>
         </is>
       </c>
-      <c r="E49" s="11" t="n"/>
+      <c r="E49" s="12" t="n"/>
       <c r="F49" s="1" t="n"/>
       <c r="G49" s="1" t="n"/>
       <c r="H49" s="1" t="n"/>
@@ -8438,7 +8439,7 @@
       <c r="AD200" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="27">
     <mergeCell ref="B47:C47"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="K5:L5"/>
@@ -8449,6 +8450,7 @@
     <mergeCell ref="B48:C48"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="D49:E49"/>
+    <mergeCell ref="B4:N4"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="D48:E48"/>
     <mergeCell ref="B3:N3"/>
@@ -8504,9 +8506,20 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;R&amp;8 &amp;K9AA3C2Budget Planner - Claude Skill by 6inq</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -8614,23 +8627,13 @@
       <c r="AC3" s="1" t="n"/>
       <c r="AD3" s="1" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" ht="14" customHeight="1">
       <c r="A4" s="1" t="n"/>
-      <c r="B4" s="1" t="n"/>
-      <c r="C4" s="1" t="n"/>
-      <c r="D4" s="1" t="n"/>
-      <c r="E4" s="1" t="n"/>
-      <c r="F4" s="1" t="n"/>
-      <c r="G4" s="1" t="n"/>
-      <c r="H4" s="1" t="n"/>
-      <c r="I4" s="1" t="n"/>
-      <c r="J4" s="1" t="n"/>
-      <c r="K4" s="1" t="n"/>
-      <c r="L4" s="1" t="n"/>
-      <c r="M4" s="1" t="n"/>
-      <c r="N4" s="1" t="n"/>
-      <c r="O4" s="1" t="n"/>
-      <c r="P4" s="1" t="n"/>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Budget Planner - Claude Skill by 6inq</t>
+        </is>
+      </c>
       <c r="Q4" s="1" t="n"/>
       <c r="R4" s="1" t="n"/>
       <c r="S4" s="1" t="n"/>
@@ -8648,53 +8651,53 @@
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="1" t="n"/>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D5" s="31" t="n">
+      <c r="D5" s="32" t="n">
         <v>46023</v>
       </c>
-      <c r="E5" s="31" t="n">
+      <c r="E5" s="32" t="n">
         <v>46054</v>
       </c>
-      <c r="F5" s="31" t="n">
+      <c r="F5" s="32" t="n">
         <v>46082</v>
       </c>
-      <c r="G5" s="31" t="n">
+      <c r="G5" s="32" t="n">
         <v>46113</v>
       </c>
-      <c r="H5" s="31" t="n">
+      <c r="H5" s="32" t="n">
         <v>46143</v>
       </c>
-      <c r="I5" s="31" t="n">
+      <c r="I5" s="32" t="n">
         <v>46174</v>
       </c>
-      <c r="J5" s="31" t="n">
+      <c r="J5" s="32" t="n">
         <v>46204</v>
       </c>
-      <c r="K5" s="31" t="n">
+      <c r="K5" s="32" t="n">
         <v>46235</v>
       </c>
-      <c r="L5" s="31" t="n">
+      <c r="L5" s="32" t="n">
         <v>46266</v>
       </c>
-      <c r="M5" s="31" t="n">
+      <c r="M5" s="32" t="n">
         <v>46296</v>
       </c>
-      <c r="N5" s="31" t="n">
+      <c r="N5" s="32" t="n">
         <v>46327</v>
       </c>
-      <c r="O5" s="31" t="n">
+      <c r="O5" s="32" t="n">
         <v>46357</v>
       </c>
-      <c r="P5" s="13" t="inlineStr">
+      <c r="P5" s="14" t="inlineStr">
         <is>
           <t>Annual Total</t>
         </is>
@@ -8716,65 +8719,65 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>Paycheck (Semi-monthly (1st &amp; 15th))</t>
         </is>
       </c>
-      <c r="C6" s="33" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>Primary</t>
         </is>
       </c>
-      <c r="D6" s="34">
+      <c r="D6" s="35">
         <f>SUMIFS('Paychecks'!$E$6:$E$35,'Paychecks'!$D$6:$D$35,D$5)</f>
         <v/>
       </c>
-      <c r="E6" s="34">
+      <c r="E6" s="35">
         <f>SUMIFS('Paychecks'!$E$6:$E$35,'Paychecks'!$D$6:$D$35,E$5)</f>
         <v/>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="35">
         <f>SUMIFS('Paychecks'!$E$6:$E$35,'Paychecks'!$D$6:$D$35,F$5)</f>
         <v/>
       </c>
-      <c r="G6" s="34">
+      <c r="G6" s="35">
         <f>SUMIFS('Paychecks'!$E$6:$E$35,'Paychecks'!$D$6:$D$35,G$5)</f>
         <v/>
       </c>
-      <c r="H6" s="34">
+      <c r="H6" s="35">
         <f>SUMIFS('Paychecks'!$E$6:$E$35,'Paychecks'!$D$6:$D$35,H$5)</f>
         <v/>
       </c>
-      <c r="I6" s="34">
+      <c r="I6" s="35">
         <f>SUMIFS('Paychecks'!$E$6:$E$35,'Paychecks'!$D$6:$D$35,I$5)</f>
         <v/>
       </c>
-      <c r="J6" s="34">
+      <c r="J6" s="35">
         <f>SUMIFS('Paychecks'!$E$6:$E$35,'Paychecks'!$D$6:$D$35,J$5)</f>
         <v/>
       </c>
-      <c r="K6" s="34">
+      <c r="K6" s="35">
         <f>SUMIFS('Paychecks'!$E$6:$E$35,'Paychecks'!$D$6:$D$35,K$5)</f>
         <v/>
       </c>
-      <c r="L6" s="34">
+      <c r="L6" s="35">
         <f>SUMIFS('Paychecks'!$E$6:$E$35,'Paychecks'!$D$6:$D$35,L$5)</f>
         <v/>
       </c>
-      <c r="M6" s="34">
+      <c r="M6" s="35">
         <f>SUMIFS('Paychecks'!$E$6:$E$35,'Paychecks'!$D$6:$D$35,M$5)</f>
         <v/>
       </c>
-      <c r="N6" s="34">
+      <c r="N6" s="35">
         <f>SUMIFS('Paychecks'!$E$6:$E$35,'Paychecks'!$D$6:$D$35,N$5)</f>
         <v/>
       </c>
-      <c r="O6" s="34">
+      <c r="O6" s="35">
         <f>SUMIFS('Paychecks'!$E$6:$E$35,'Paychecks'!$D$6:$D$35,O$5)</f>
         <v/>
       </c>
-      <c r="P6" s="35">
+      <c r="P6" s="36">
         <f>IF(COUNT(D6:O6)=0,"",SUM(D6:O6))</f>
         <v/>
       </c>
@@ -8795,21 +8798,21 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
-      <c r="B7" s="36" t="n"/>
-      <c r="C7" s="36" t="n"/>
-      <c r="D7" s="37" t="n"/>
-      <c r="E7" s="37" t="n"/>
-      <c r="F7" s="37" t="n"/>
-      <c r="G7" s="37" t="n"/>
-      <c r="H7" s="37" t="n"/>
-      <c r="I7" s="37" t="n"/>
-      <c r="J7" s="37" t="n"/>
-      <c r="K7" s="37" t="n"/>
-      <c r="L7" s="37" t="n"/>
-      <c r="M7" s="37" t="n"/>
-      <c r="N7" s="37" t="n"/>
-      <c r="O7" s="37" t="n"/>
-      <c r="P7" s="35">
+      <c r="B7" s="37" t="n"/>
+      <c r="C7" s="37" t="n"/>
+      <c r="D7" s="38" t="n"/>
+      <c r="E7" s="38" t="n"/>
+      <c r="F7" s="38" t="n"/>
+      <c r="G7" s="38" t="n"/>
+      <c r="H7" s="38" t="n"/>
+      <c r="I7" s="38" t="n"/>
+      <c r="J7" s="38" t="n"/>
+      <c r="K7" s="38" t="n"/>
+      <c r="L7" s="38" t="n"/>
+      <c r="M7" s="38" t="n"/>
+      <c r="N7" s="38" t="n"/>
+      <c r="O7" s="38" t="n"/>
+      <c r="P7" s="36">
         <f>IF(COUNT(D7:O7)=0,"",SUM(D7:O7))</f>
         <v/>
       </c>
@@ -8830,21 +8833,21 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
-      <c r="B8" s="38" t="n"/>
-      <c r="C8" s="38" t="n"/>
-      <c r="D8" s="39" t="n"/>
-      <c r="E8" s="39" t="n"/>
-      <c r="F8" s="39" t="n"/>
-      <c r="G8" s="39" t="n"/>
-      <c r="H8" s="39" t="n"/>
-      <c r="I8" s="39" t="n"/>
-      <c r="J8" s="39" t="n"/>
-      <c r="K8" s="39" t="n"/>
-      <c r="L8" s="39" t="n"/>
-      <c r="M8" s="39" t="n"/>
-      <c r="N8" s="39" t="n"/>
-      <c r="O8" s="39" t="n"/>
-      <c r="P8" s="35">
+      <c r="B8" s="39" t="n"/>
+      <c r="C8" s="39" t="n"/>
+      <c r="D8" s="40" t="n"/>
+      <c r="E8" s="40" t="n"/>
+      <c r="F8" s="40" t="n"/>
+      <c r="G8" s="40" t="n"/>
+      <c r="H8" s="40" t="n"/>
+      <c r="I8" s="40" t="n"/>
+      <c r="J8" s="40" t="n"/>
+      <c r="K8" s="40" t="n"/>
+      <c r="L8" s="40" t="n"/>
+      <c r="M8" s="40" t="n"/>
+      <c r="N8" s="40" t="n"/>
+      <c r="O8" s="40" t="n"/>
+      <c r="P8" s="36">
         <f>IF(COUNT(D8:O8)=0,"",SUM(D8:O8))</f>
         <v/>
       </c>
@@ -8865,21 +8868,21 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
-      <c r="B9" s="36" t="n"/>
-      <c r="C9" s="36" t="n"/>
-      <c r="D9" s="37" t="n"/>
-      <c r="E9" s="37" t="n"/>
-      <c r="F9" s="37" t="n"/>
-      <c r="G9" s="37" t="n"/>
-      <c r="H9" s="37" t="n"/>
-      <c r="I9" s="37" t="n"/>
-      <c r="J9" s="37" t="n"/>
-      <c r="K9" s="37" t="n"/>
-      <c r="L9" s="37" t="n"/>
-      <c r="M9" s="37" t="n"/>
-      <c r="N9" s="37" t="n"/>
-      <c r="O9" s="37" t="n"/>
-      <c r="P9" s="35">
+      <c r="B9" s="37" t="n"/>
+      <c r="C9" s="37" t="n"/>
+      <c r="D9" s="38" t="n"/>
+      <c r="E9" s="38" t="n"/>
+      <c r="F9" s="38" t="n"/>
+      <c r="G9" s="38" t="n"/>
+      <c r="H9" s="38" t="n"/>
+      <c r="I9" s="38" t="n"/>
+      <c r="J9" s="38" t="n"/>
+      <c r="K9" s="38" t="n"/>
+      <c r="L9" s="38" t="n"/>
+      <c r="M9" s="38" t="n"/>
+      <c r="N9" s="38" t="n"/>
+      <c r="O9" s="38" t="n"/>
+      <c r="P9" s="36">
         <f>IF(COUNT(D9:O9)=0,"",SUM(D9:O9))</f>
         <v/>
       </c>
@@ -8900,21 +8903,21 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
-      <c r="B10" s="38" t="n"/>
-      <c r="C10" s="38" t="n"/>
-      <c r="D10" s="39" t="n"/>
-      <c r="E10" s="39" t="n"/>
-      <c r="F10" s="39" t="n"/>
-      <c r="G10" s="39" t="n"/>
-      <c r="H10" s="39" t="n"/>
-      <c r="I10" s="39" t="n"/>
-      <c r="J10" s="39" t="n"/>
-      <c r="K10" s="39" t="n"/>
-      <c r="L10" s="39" t="n"/>
-      <c r="M10" s="39" t="n"/>
-      <c r="N10" s="39" t="n"/>
-      <c r="O10" s="39" t="n"/>
-      <c r="P10" s="35">
+      <c r="B10" s="39" t="n"/>
+      <c r="C10" s="39" t="n"/>
+      <c r="D10" s="40" t="n"/>
+      <c r="E10" s="40" t="n"/>
+      <c r="F10" s="40" t="n"/>
+      <c r="G10" s="40" t="n"/>
+      <c r="H10" s="40" t="n"/>
+      <c r="I10" s="40" t="n"/>
+      <c r="J10" s="40" t="n"/>
+      <c r="K10" s="40" t="n"/>
+      <c r="L10" s="40" t="n"/>
+      <c r="M10" s="40" t="n"/>
+      <c r="N10" s="40" t="n"/>
+      <c r="O10" s="40" t="n"/>
+      <c r="P10" s="36">
         <f>IF(COUNT(D10:O10)=0,"",SUM(D10:O10))</f>
         <v/>
       </c>
@@ -8935,21 +8938,21 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
-      <c r="B11" s="36" t="n"/>
-      <c r="C11" s="36" t="n"/>
-      <c r="D11" s="37" t="n"/>
-      <c r="E11" s="37" t="n"/>
-      <c r="F11" s="37" t="n"/>
-      <c r="G11" s="37" t="n"/>
-      <c r="H11" s="37" t="n"/>
-      <c r="I11" s="37" t="n"/>
-      <c r="J11" s="37" t="n"/>
-      <c r="K11" s="37" t="n"/>
-      <c r="L11" s="37" t="n"/>
-      <c r="M11" s="37" t="n"/>
-      <c r="N11" s="37" t="n"/>
-      <c r="O11" s="37" t="n"/>
-      <c r="P11" s="35">
+      <c r="B11" s="37" t="n"/>
+      <c r="C11" s="37" t="n"/>
+      <c r="D11" s="38" t="n"/>
+      <c r="E11" s="38" t="n"/>
+      <c r="F11" s="38" t="n"/>
+      <c r="G11" s="38" t="n"/>
+      <c r="H11" s="38" t="n"/>
+      <c r="I11" s="38" t="n"/>
+      <c r="J11" s="38" t="n"/>
+      <c r="K11" s="38" t="n"/>
+      <c r="L11" s="38" t="n"/>
+      <c r="M11" s="38" t="n"/>
+      <c r="N11" s="38" t="n"/>
+      <c r="O11" s="38" t="n"/>
+      <c r="P11" s="36">
         <f>IF(COUNT(D11:O11)=0,"",SUM(D11:O11))</f>
         <v/>
       </c>
@@ -8970,21 +8973,21 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
-      <c r="B12" s="38" t="n"/>
-      <c r="C12" s="38" t="n"/>
-      <c r="D12" s="39" t="n"/>
-      <c r="E12" s="39" t="n"/>
-      <c r="F12" s="39" t="n"/>
-      <c r="G12" s="39" t="n"/>
-      <c r="H12" s="39" t="n"/>
-      <c r="I12" s="39" t="n"/>
-      <c r="J12" s="39" t="n"/>
-      <c r="K12" s="39" t="n"/>
-      <c r="L12" s="39" t="n"/>
-      <c r="M12" s="39" t="n"/>
-      <c r="N12" s="39" t="n"/>
-      <c r="O12" s="39" t="n"/>
-      <c r="P12" s="35">
+      <c r="B12" s="39" t="n"/>
+      <c r="C12" s="39" t="n"/>
+      <c r="D12" s="40" t="n"/>
+      <c r="E12" s="40" t="n"/>
+      <c r="F12" s="40" t="n"/>
+      <c r="G12" s="40" t="n"/>
+      <c r="H12" s="40" t="n"/>
+      <c r="I12" s="40" t="n"/>
+      <c r="J12" s="40" t="n"/>
+      <c r="K12" s="40" t="n"/>
+      <c r="L12" s="40" t="n"/>
+      <c r="M12" s="40" t="n"/>
+      <c r="N12" s="40" t="n"/>
+      <c r="O12" s="40" t="n"/>
+      <c r="P12" s="36">
         <f>IF(COUNT(D12:O12)=0,"",SUM(D12:O12))</f>
         <v/>
       </c>
@@ -9005,21 +9008,21 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
-      <c r="B13" s="36" t="n"/>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="37" t="n"/>
-      <c r="E13" s="37" t="n"/>
-      <c r="F13" s="37" t="n"/>
-      <c r="G13" s="37" t="n"/>
-      <c r="H13" s="37" t="n"/>
-      <c r="I13" s="37" t="n"/>
-      <c r="J13" s="37" t="n"/>
-      <c r="K13" s="37" t="n"/>
-      <c r="L13" s="37" t="n"/>
-      <c r="M13" s="37" t="n"/>
-      <c r="N13" s="37" t="n"/>
-      <c r="O13" s="37" t="n"/>
-      <c r="P13" s="35">
+      <c r="B13" s="37" t="n"/>
+      <c r="C13" s="37" t="n"/>
+      <c r="D13" s="38" t="n"/>
+      <c r="E13" s="38" t="n"/>
+      <c r="F13" s="38" t="n"/>
+      <c r="G13" s="38" t="n"/>
+      <c r="H13" s="38" t="n"/>
+      <c r="I13" s="38" t="n"/>
+      <c r="J13" s="38" t="n"/>
+      <c r="K13" s="38" t="n"/>
+      <c r="L13" s="38" t="n"/>
+      <c r="M13" s="38" t="n"/>
+      <c r="N13" s="38" t="n"/>
+      <c r="O13" s="38" t="n"/>
+      <c r="P13" s="36">
         <f>IF(COUNT(D13:O13)=0,"",SUM(D13:O13))</f>
         <v/>
       </c>
@@ -9040,21 +9043,21 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
-      <c r="B14" s="38" t="n"/>
-      <c r="C14" s="38" t="n"/>
-      <c r="D14" s="39" t="n"/>
-      <c r="E14" s="39" t="n"/>
-      <c r="F14" s="39" t="n"/>
-      <c r="G14" s="39" t="n"/>
-      <c r="H14" s="39" t="n"/>
-      <c r="I14" s="39" t="n"/>
-      <c r="J14" s="39" t="n"/>
-      <c r="K14" s="39" t="n"/>
-      <c r="L14" s="39" t="n"/>
-      <c r="M14" s="39" t="n"/>
-      <c r="N14" s="39" t="n"/>
-      <c r="O14" s="39" t="n"/>
-      <c r="P14" s="35">
+      <c r="B14" s="39" t="n"/>
+      <c r="C14" s="39" t="n"/>
+      <c r="D14" s="40" t="n"/>
+      <c r="E14" s="40" t="n"/>
+      <c r="F14" s="40" t="n"/>
+      <c r="G14" s="40" t="n"/>
+      <c r="H14" s="40" t="n"/>
+      <c r="I14" s="40" t="n"/>
+      <c r="J14" s="40" t="n"/>
+      <c r="K14" s="40" t="n"/>
+      <c r="L14" s="40" t="n"/>
+      <c r="M14" s="40" t="n"/>
+      <c r="N14" s="40" t="n"/>
+      <c r="O14" s="40" t="n"/>
+      <c r="P14" s="36">
         <f>IF(COUNT(D14:O14)=0,"",SUM(D14:O14))</f>
         <v/>
       </c>
@@ -9075,21 +9078,21 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
-      <c r="B15" s="36" t="n"/>
-      <c r="C15" s="36" t="n"/>
-      <c r="D15" s="37" t="n"/>
-      <c r="E15" s="37" t="n"/>
-      <c r="F15" s="37" t="n"/>
-      <c r="G15" s="37" t="n"/>
-      <c r="H15" s="37" t="n"/>
-      <c r="I15" s="37" t="n"/>
-      <c r="J15" s="37" t="n"/>
-      <c r="K15" s="37" t="n"/>
-      <c r="L15" s="37" t="n"/>
-      <c r="M15" s="37" t="n"/>
-      <c r="N15" s="37" t="n"/>
-      <c r="O15" s="37" t="n"/>
-      <c r="P15" s="35">
+      <c r="B15" s="37" t="n"/>
+      <c r="C15" s="37" t="n"/>
+      <c r="D15" s="38" t="n"/>
+      <c r="E15" s="38" t="n"/>
+      <c r="F15" s="38" t="n"/>
+      <c r="G15" s="38" t="n"/>
+      <c r="H15" s="38" t="n"/>
+      <c r="I15" s="38" t="n"/>
+      <c r="J15" s="38" t="n"/>
+      <c r="K15" s="38" t="n"/>
+      <c r="L15" s="38" t="n"/>
+      <c r="M15" s="38" t="n"/>
+      <c r="N15" s="38" t="n"/>
+      <c r="O15" s="38" t="n"/>
+      <c r="P15" s="36">
         <f>IF(COUNT(D15:O15)=0,"",SUM(D15:O15))</f>
         <v/>
       </c>
@@ -9110,21 +9113,21 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n"/>
-      <c r="B16" s="38" t="n"/>
-      <c r="C16" s="38" t="n"/>
-      <c r="D16" s="39" t="n"/>
-      <c r="E16" s="39" t="n"/>
-      <c r="F16" s="39" t="n"/>
-      <c r="G16" s="39" t="n"/>
-      <c r="H16" s="39" t="n"/>
-      <c r="I16" s="39" t="n"/>
-      <c r="J16" s="39" t="n"/>
-      <c r="K16" s="39" t="n"/>
-      <c r="L16" s="39" t="n"/>
-      <c r="M16" s="39" t="n"/>
-      <c r="N16" s="39" t="n"/>
-      <c r="O16" s="39" t="n"/>
-      <c r="P16" s="35">
+      <c r="B16" s="39" t="n"/>
+      <c r="C16" s="39" t="n"/>
+      <c r="D16" s="40" t="n"/>
+      <c r="E16" s="40" t="n"/>
+      <c r="F16" s="40" t="n"/>
+      <c r="G16" s="40" t="n"/>
+      <c r="H16" s="40" t="n"/>
+      <c r="I16" s="40" t="n"/>
+      <c r="J16" s="40" t="n"/>
+      <c r="K16" s="40" t="n"/>
+      <c r="L16" s="40" t="n"/>
+      <c r="M16" s="40" t="n"/>
+      <c r="N16" s="40" t="n"/>
+      <c r="O16" s="40" t="n"/>
+      <c r="P16" s="36">
         <f>IF(COUNT(D16:O16)=0,"",SUM(D16:O16))</f>
         <v/>
       </c>
@@ -9145,21 +9148,21 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
-      <c r="B17" s="36" t="n"/>
-      <c r="C17" s="36" t="n"/>
-      <c r="D17" s="37" t="n"/>
-      <c r="E17" s="37" t="n"/>
-      <c r="F17" s="37" t="n"/>
-      <c r="G17" s="37" t="n"/>
-      <c r="H17" s="37" t="n"/>
-      <c r="I17" s="37" t="n"/>
-      <c r="J17" s="37" t="n"/>
-      <c r="K17" s="37" t="n"/>
-      <c r="L17" s="37" t="n"/>
-      <c r="M17" s="37" t="n"/>
-      <c r="N17" s="37" t="n"/>
-      <c r="O17" s="37" t="n"/>
-      <c r="P17" s="35">
+      <c r="B17" s="37" t="n"/>
+      <c r="C17" s="37" t="n"/>
+      <c r="D17" s="38" t="n"/>
+      <c r="E17" s="38" t="n"/>
+      <c r="F17" s="38" t="n"/>
+      <c r="G17" s="38" t="n"/>
+      <c r="H17" s="38" t="n"/>
+      <c r="I17" s="38" t="n"/>
+      <c r="J17" s="38" t="n"/>
+      <c r="K17" s="38" t="n"/>
+      <c r="L17" s="38" t="n"/>
+      <c r="M17" s="38" t="n"/>
+      <c r="N17" s="38" t="n"/>
+      <c r="O17" s="38" t="n"/>
+      <c r="P17" s="36">
         <f>IF(COUNT(D17:O17)=0,"",SUM(D17:O17))</f>
         <v/>
       </c>
@@ -9180,21 +9183,21 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
-      <c r="B18" s="38" t="n"/>
-      <c r="C18" s="38" t="n"/>
-      <c r="D18" s="39" t="n"/>
-      <c r="E18" s="39" t="n"/>
-      <c r="F18" s="39" t="n"/>
-      <c r="G18" s="39" t="n"/>
-      <c r="H18" s="39" t="n"/>
-      <c r="I18" s="39" t="n"/>
-      <c r="J18" s="39" t="n"/>
-      <c r="K18" s="39" t="n"/>
-      <c r="L18" s="39" t="n"/>
-      <c r="M18" s="39" t="n"/>
-      <c r="N18" s="39" t="n"/>
-      <c r="O18" s="39" t="n"/>
-      <c r="P18" s="35">
+      <c r="B18" s="39" t="n"/>
+      <c r="C18" s="39" t="n"/>
+      <c r="D18" s="40" t="n"/>
+      <c r="E18" s="40" t="n"/>
+      <c r="F18" s="40" t="n"/>
+      <c r="G18" s="40" t="n"/>
+      <c r="H18" s="40" t="n"/>
+      <c r="I18" s="40" t="n"/>
+      <c r="J18" s="40" t="n"/>
+      <c r="K18" s="40" t="n"/>
+      <c r="L18" s="40" t="n"/>
+      <c r="M18" s="40" t="n"/>
+      <c r="N18" s="40" t="n"/>
+      <c r="O18" s="40" t="n"/>
+      <c r="P18" s="36">
         <f>IF(COUNT(D18:O18)=0,"",SUM(D18:O18))</f>
         <v/>
       </c>
@@ -9215,21 +9218,21 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
-      <c r="B19" s="36" t="n"/>
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="37" t="n"/>
-      <c r="E19" s="37" t="n"/>
-      <c r="F19" s="37" t="n"/>
-      <c r="G19" s="37" t="n"/>
-      <c r="H19" s="37" t="n"/>
-      <c r="I19" s="37" t="n"/>
-      <c r="J19" s="37" t="n"/>
-      <c r="K19" s="37" t="n"/>
-      <c r="L19" s="37" t="n"/>
-      <c r="M19" s="37" t="n"/>
-      <c r="N19" s="37" t="n"/>
-      <c r="O19" s="37" t="n"/>
-      <c r="P19" s="35">
+      <c r="B19" s="37" t="n"/>
+      <c r="C19" s="37" t="n"/>
+      <c r="D19" s="38" t="n"/>
+      <c r="E19" s="38" t="n"/>
+      <c r="F19" s="38" t="n"/>
+      <c r="G19" s="38" t="n"/>
+      <c r="H19" s="38" t="n"/>
+      <c r="I19" s="38" t="n"/>
+      <c r="J19" s="38" t="n"/>
+      <c r="K19" s="38" t="n"/>
+      <c r="L19" s="38" t="n"/>
+      <c r="M19" s="38" t="n"/>
+      <c r="N19" s="38" t="n"/>
+      <c r="O19" s="38" t="n"/>
+      <c r="P19" s="36">
         <f>IF(COUNT(D19:O19)=0,"",SUM(D19:O19))</f>
         <v/>
       </c>
@@ -9250,21 +9253,21 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
-      <c r="B20" s="38" t="n"/>
-      <c r="C20" s="38" t="n"/>
-      <c r="D20" s="39" t="n"/>
-      <c r="E20" s="39" t="n"/>
-      <c r="F20" s="39" t="n"/>
-      <c r="G20" s="39" t="n"/>
-      <c r="H20" s="39" t="n"/>
-      <c r="I20" s="39" t="n"/>
-      <c r="J20" s="39" t="n"/>
-      <c r="K20" s="39" t="n"/>
-      <c r="L20" s="39" t="n"/>
-      <c r="M20" s="39" t="n"/>
-      <c r="N20" s="39" t="n"/>
-      <c r="O20" s="39" t="n"/>
-      <c r="P20" s="35">
+      <c r="B20" s="39" t="n"/>
+      <c r="C20" s="39" t="n"/>
+      <c r="D20" s="40" t="n"/>
+      <c r="E20" s="40" t="n"/>
+      <c r="F20" s="40" t="n"/>
+      <c r="G20" s="40" t="n"/>
+      <c r="H20" s="40" t="n"/>
+      <c r="I20" s="40" t="n"/>
+      <c r="J20" s="40" t="n"/>
+      <c r="K20" s="40" t="n"/>
+      <c r="L20" s="40" t="n"/>
+      <c r="M20" s="40" t="n"/>
+      <c r="N20" s="40" t="n"/>
+      <c r="O20" s="40" t="n"/>
+      <c r="P20" s="36">
         <f>IF(COUNT(D20:O20)=0,"",SUM(D20:O20))</f>
         <v/>
       </c>
@@ -9285,21 +9288,21 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
-      <c r="B21" s="36" t="n"/>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="37" t="n"/>
-      <c r="E21" s="37" t="n"/>
-      <c r="F21" s="37" t="n"/>
-      <c r="G21" s="37" t="n"/>
-      <c r="H21" s="37" t="n"/>
-      <c r="I21" s="37" t="n"/>
-      <c r="J21" s="37" t="n"/>
-      <c r="K21" s="37" t="n"/>
-      <c r="L21" s="37" t="n"/>
-      <c r="M21" s="37" t="n"/>
-      <c r="N21" s="37" t="n"/>
-      <c r="O21" s="37" t="n"/>
-      <c r="P21" s="35">
+      <c r="B21" s="37" t="n"/>
+      <c r="C21" s="37" t="n"/>
+      <c r="D21" s="38" t="n"/>
+      <c r="E21" s="38" t="n"/>
+      <c r="F21" s="38" t="n"/>
+      <c r="G21" s="38" t="n"/>
+      <c r="H21" s="38" t="n"/>
+      <c r="I21" s="38" t="n"/>
+      <c r="J21" s="38" t="n"/>
+      <c r="K21" s="38" t="n"/>
+      <c r="L21" s="38" t="n"/>
+      <c r="M21" s="38" t="n"/>
+      <c r="N21" s="38" t="n"/>
+      <c r="O21" s="38" t="n"/>
+      <c r="P21" s="36">
         <f>IF(COUNT(D21:O21)=0,"",SUM(D21:O21))</f>
         <v/>
       </c>
@@ -9320,61 +9323,61 @@
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="1" t="n"/>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B22" s="25" t="inlineStr">
         <is>
           <t>TOTAL INCOME</t>
         </is>
       </c>
-      <c r="C22" s="24" t="n"/>
-      <c r="D22" s="28">
+      <c r="C22" s="25" t="n"/>
+      <c r="D22" s="29">
         <f>SUM(D6:D21)</f>
         <v/>
       </c>
-      <c r="E22" s="28">
+      <c r="E22" s="29">
         <f>SUM(E6:E21)</f>
         <v/>
       </c>
-      <c r="F22" s="28">
+      <c r="F22" s="29">
         <f>SUM(F6:F21)</f>
         <v/>
       </c>
-      <c r="G22" s="28">
+      <c r="G22" s="29">
         <f>SUM(G6:G21)</f>
         <v/>
       </c>
-      <c r="H22" s="28">
+      <c r="H22" s="29">
         <f>SUM(H6:H21)</f>
         <v/>
       </c>
-      <c r="I22" s="28">
+      <c r="I22" s="29">
         <f>SUM(I6:I21)</f>
         <v/>
       </c>
-      <c r="J22" s="28">
+      <c r="J22" s="29">
         <f>SUM(J6:J21)</f>
         <v/>
       </c>
-      <c r="K22" s="28">
+      <c r="K22" s="29">
         <f>SUM(K6:K21)</f>
         <v/>
       </c>
-      <c r="L22" s="28">
+      <c r="L22" s="29">
         <f>SUM(L6:L21)</f>
         <v/>
       </c>
-      <c r="M22" s="28">
+      <c r="M22" s="29">
         <f>SUM(M6:M21)</f>
         <v/>
       </c>
-      <c r="N22" s="28">
+      <c r="N22" s="29">
         <f>SUM(N6:N21)</f>
         <v/>
       </c>
-      <c r="O22" s="28">
+      <c r="O22" s="29">
         <f>SUM(O6:O21)</f>
         <v/>
       </c>
-      <c r="P22" s="28">
+      <c r="P22" s="29">
         <f>SUM(P6:P21)</f>
         <v/>
       </c>
@@ -15090,17 +15093,29 @@
       <c r="AD200" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B3:P3"/>
     <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B4:P4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="C7:C21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$C$2:$C$8</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;R&amp;8 &amp;K9AA3C2Budget Planner - Claude Skill by 6inq</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -15218,13 +15233,13 @@
       <c r="AC3" s="1" t="n"/>
       <c r="AD3" s="1" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" ht="14" customHeight="1">
       <c r="A4" s="1" t="n"/>
-      <c r="B4" s="1" t="n"/>
-      <c r="C4" s="1" t="n"/>
-      <c r="D4" s="1" t="n"/>
-      <c r="E4" s="1" t="n"/>
-      <c r="F4" s="1" t="n"/>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Budget Planner - Claude Skill by 6inq</t>
+        </is>
+      </c>
       <c r="G4" s="1" t="n"/>
       <c r="H4" s="1" t="n"/>
       <c r="I4" s="1" t="n"/>
@@ -15252,27 +15267,27 @@
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="1" t="n"/>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>Pay Date</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>Net Pay</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -15304,18 +15319,18 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
-      <c r="B6" s="40" t="n">
+      <c r="B6" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="41" t="n">
+      <c r="C6" s="42" t="n">
         <v>46023</v>
       </c>
-      <c r="D6" s="42">
+      <c r="D6" s="43">
         <f>IF(C6="","",DATE(YEAR(C6),MONTH(C6),1))</f>
         <v/>
       </c>
-      <c r="E6" s="39" t="n"/>
-      <c r="F6" s="38" t="n"/>
+      <c r="E6" s="40" t="n"/>
+      <c r="F6" s="39" t="n"/>
       <c r="G6" s="1" t="n"/>
       <c r="H6" s="1" t="n"/>
       <c r="I6" s="1" t="n"/>
@@ -15343,18 +15358,18 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
-      <c r="B7" s="40" t="n">
+      <c r="B7" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="43" t="n">
+      <c r="C7" s="44" t="n">
         <v>46037</v>
       </c>
-      <c r="D7" s="42">
+      <c r="D7" s="43">
         <f>IF(C7="","",DATE(YEAR(C7),MONTH(C7),1))</f>
         <v/>
       </c>
-      <c r="E7" s="37" t="n"/>
-      <c r="F7" s="36" t="n"/>
+      <c r="E7" s="38" t="n"/>
+      <c r="F7" s="37" t="n"/>
       <c r="G7" s="1" t="n"/>
       <c r="H7" s="1" t="n"/>
       <c r="I7" s="1" t="n"/>
@@ -15382,18 +15397,18 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
-      <c r="B8" s="40" t="n">
+      <c r="B8" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="41" t="n">
+      <c r="C8" s="42" t="n">
         <v>46054</v>
       </c>
-      <c r="D8" s="42">
+      <c r="D8" s="43">
         <f>IF(C8="","",DATE(YEAR(C8),MONTH(C8),1))</f>
         <v/>
       </c>
-      <c r="E8" s="39" t="n"/>
-      <c r="F8" s="38" t="n"/>
+      <c r="E8" s="40" t="n"/>
+      <c r="F8" s="39" t="n"/>
       <c r="G8" s="1" t="n"/>
       <c r="H8" s="1" t="n"/>
       <c r="I8" s="1" t="n"/>
@@ -15421,18 +15436,18 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
-      <c r="B9" s="40" t="n">
+      <c r="B9" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="43" t="n">
+      <c r="C9" s="44" t="n">
         <v>46068</v>
       </c>
-      <c r="D9" s="42">
+      <c r="D9" s="43">
         <f>IF(C9="","",DATE(YEAR(C9),MONTH(C9),1))</f>
         <v/>
       </c>
-      <c r="E9" s="37" t="n"/>
-      <c r="F9" s="36" t="n"/>
+      <c r="E9" s="38" t="n"/>
+      <c r="F9" s="37" t="n"/>
       <c r="G9" s="1" t="n"/>
       <c r="H9" s="1" t="n"/>
       <c r="I9" s="1" t="n"/>
@@ -15460,18 +15475,18 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
-      <c r="B10" s="40" t="n">
+      <c r="B10" s="41" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="41" t="n">
+      <c r="C10" s="42" t="n">
         <v>46082</v>
       </c>
-      <c r="D10" s="42">
+      <c r="D10" s="43">
         <f>IF(C10="","",DATE(YEAR(C10),MONTH(C10),1))</f>
         <v/>
       </c>
-      <c r="E10" s="39" t="n"/>
-      <c r="F10" s="38" t="n"/>
+      <c r="E10" s="40" t="n"/>
+      <c r="F10" s="39" t="n"/>
       <c r="G10" s="1" t="n"/>
       <c r="H10" s="1" t="n"/>
       <c r="I10" s="1" t="n"/>
@@ -15499,18 +15514,18 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
-      <c r="B11" s="40" t="n">
+      <c r="B11" s="41" t="n">
         <v>6</v>
       </c>
-      <c r="C11" s="43" t="n">
+      <c r="C11" s="44" t="n">
         <v>46096</v>
       </c>
-      <c r="D11" s="42">
+      <c r="D11" s="43">
         <f>IF(C11="","",DATE(YEAR(C11),MONTH(C11),1))</f>
         <v/>
       </c>
-      <c r="E11" s="37" t="n"/>
-      <c r="F11" s="36" t="n"/>
+      <c r="E11" s="38" t="n"/>
+      <c r="F11" s="37" t="n"/>
       <c r="G11" s="1" t="n"/>
       <c r="H11" s="1" t="n"/>
       <c r="I11" s="1" t="n"/>
@@ -15538,18 +15553,18 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
-      <c r="B12" s="40" t="n">
+      <c r="B12" s="41" t="n">
         <v>7</v>
       </c>
-      <c r="C12" s="41" t="n">
+      <c r="C12" s="42" t="n">
         <v>46113</v>
       </c>
-      <c r="D12" s="42">
+      <c r="D12" s="43">
         <f>IF(C12="","",DATE(YEAR(C12),MONTH(C12),1))</f>
         <v/>
       </c>
-      <c r="E12" s="39" t="n"/>
-      <c r="F12" s="38" t="n"/>
+      <c r="E12" s="40" t="n"/>
+      <c r="F12" s="39" t="n"/>
       <c r="G12" s="1" t="n"/>
       <c r="H12" s="1" t="n"/>
       <c r="I12" s="1" t="n"/>
@@ -15577,18 +15592,18 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
-      <c r="B13" s="40" t="n">
+      <c r="B13" s="41" t="n">
         <v>8</v>
       </c>
-      <c r="C13" s="43" t="n">
+      <c r="C13" s="44" t="n">
         <v>46127</v>
       </c>
-      <c r="D13" s="42">
+      <c r="D13" s="43">
         <f>IF(C13="","",DATE(YEAR(C13),MONTH(C13),1))</f>
         <v/>
       </c>
-      <c r="E13" s="37" t="n"/>
-      <c r="F13" s="36" t="n"/>
+      <c r="E13" s="38" t="n"/>
+      <c r="F13" s="37" t="n"/>
       <c r="G13" s="1" t="n"/>
       <c r="H13" s="1" t="n"/>
       <c r="I13" s="1" t="n"/>
@@ -15616,18 +15631,18 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
-      <c r="B14" s="40" t="n">
+      <c r="B14" s="41" t="n">
         <v>9</v>
       </c>
-      <c r="C14" s="41" t="n">
+      <c r="C14" s="42" t="n">
         <v>46143</v>
       </c>
-      <c r="D14" s="42">
+      <c r="D14" s="43">
         <f>IF(C14="","",DATE(YEAR(C14),MONTH(C14),1))</f>
         <v/>
       </c>
-      <c r="E14" s="39" t="n"/>
-      <c r="F14" s="38" t="n"/>
+      <c r="E14" s="40" t="n"/>
+      <c r="F14" s="39" t="n"/>
       <c r="G14" s="1" t="n"/>
       <c r="H14" s="1" t="n"/>
       <c r="I14" s="1" t="n"/>
@@ -15655,18 +15670,18 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
-      <c r="B15" s="40" t="n">
+      <c r="B15" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="C15" s="43" t="n">
+      <c r="C15" s="44" t="n">
         <v>46157</v>
       </c>
-      <c r="D15" s="42">
+      <c r="D15" s="43">
         <f>IF(C15="","",DATE(YEAR(C15),MONTH(C15),1))</f>
         <v/>
       </c>
-      <c r="E15" s="37" t="n"/>
-      <c r="F15" s="36" t="n"/>
+      <c r="E15" s="38" t="n"/>
+      <c r="F15" s="37" t="n"/>
       <c r="G15" s="1" t="n"/>
       <c r="H15" s="1" t="n"/>
       <c r="I15" s="1" t="n"/>
@@ -15694,18 +15709,18 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n"/>
-      <c r="B16" s="40" t="n">
+      <c r="B16" s="41" t="n">
         <v>11</v>
       </c>
-      <c r="C16" s="41" t="n">
+      <c r="C16" s="42" t="n">
         <v>46174</v>
       </c>
-      <c r="D16" s="42">
+      <c r="D16" s="43">
         <f>IF(C16="","",DATE(YEAR(C16),MONTH(C16),1))</f>
         <v/>
       </c>
-      <c r="E16" s="39" t="n"/>
-      <c r="F16" s="38" t="n"/>
+      <c r="E16" s="40" t="n"/>
+      <c r="F16" s="39" t="n"/>
       <c r="G16" s="1" t="n"/>
       <c r="H16" s="1" t="n"/>
       <c r="I16" s="1" t="n"/>
@@ -15733,18 +15748,18 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
-      <c r="B17" s="40" t="n">
+      <c r="B17" s="41" t="n">
         <v>12</v>
       </c>
-      <c r="C17" s="43" t="n">
+      <c r="C17" s="44" t="n">
         <v>46188</v>
       </c>
-      <c r="D17" s="42">
+      <c r="D17" s="43">
         <f>IF(C17="","",DATE(YEAR(C17),MONTH(C17),1))</f>
         <v/>
       </c>
-      <c r="E17" s="37" t="n"/>
-      <c r="F17" s="36" t="n"/>
+      <c r="E17" s="38" t="n"/>
+      <c r="F17" s="37" t="n"/>
       <c r="G17" s="1" t="n"/>
       <c r="H17" s="1" t="n"/>
       <c r="I17" s="1" t="n"/>
@@ -15772,18 +15787,18 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
-      <c r="B18" s="40" t="n">
+      <c r="B18" s="41" t="n">
         <v>13</v>
       </c>
-      <c r="C18" s="41" t="n">
+      <c r="C18" s="42" t="n">
         <v>46204</v>
       </c>
-      <c r="D18" s="42">
+      <c r="D18" s="43">
         <f>IF(C18="","",DATE(YEAR(C18),MONTH(C18),1))</f>
         <v/>
       </c>
-      <c r="E18" s="39" t="n"/>
-      <c r="F18" s="38" t="n"/>
+      <c r="E18" s="40" t="n"/>
+      <c r="F18" s="39" t="n"/>
       <c r="G18" s="1" t="n"/>
       <c r="H18" s="1" t="n"/>
       <c r="I18" s="1" t="n"/>
@@ -15811,18 +15826,18 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
-      <c r="B19" s="40" t="n">
+      <c r="B19" s="41" t="n">
         <v>14</v>
       </c>
-      <c r="C19" s="43" t="n">
+      <c r="C19" s="44" t="n">
         <v>46218</v>
       </c>
-      <c r="D19" s="42">
+      <c r="D19" s="43">
         <f>IF(C19="","",DATE(YEAR(C19),MONTH(C19),1))</f>
         <v/>
       </c>
-      <c r="E19" s="37" t="n"/>
-      <c r="F19" s="36" t="n"/>
+      <c r="E19" s="38" t="n"/>
+      <c r="F19" s="37" t="n"/>
       <c r="G19" s="1" t="n"/>
       <c r="H19" s="1" t="n"/>
       <c r="I19" s="1" t="n"/>
@@ -15850,18 +15865,18 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
-      <c r="B20" s="40" t="n">
+      <c r="B20" s="41" t="n">
         <v>15</v>
       </c>
-      <c r="C20" s="41" t="n">
+      <c r="C20" s="42" t="n">
         <v>46235</v>
       </c>
-      <c r="D20" s="42">
+      <c r="D20" s="43">
         <f>IF(C20="","",DATE(YEAR(C20),MONTH(C20),1))</f>
         <v/>
       </c>
-      <c r="E20" s="39" t="n"/>
-      <c r="F20" s="38" t="n"/>
+      <c r="E20" s="40" t="n"/>
+      <c r="F20" s="39" t="n"/>
       <c r="G20" s="1" t="n"/>
       <c r="H20" s="1" t="n"/>
       <c r="I20" s="1" t="n"/>
@@ -15889,18 +15904,18 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
-      <c r="B21" s="40" t="n">
+      <c r="B21" s="41" t="n">
         <v>16</v>
       </c>
-      <c r="C21" s="43" t="n">
+      <c r="C21" s="44" t="n">
         <v>46249</v>
       </c>
-      <c r="D21" s="42">
+      <c r="D21" s="43">
         <f>IF(C21="","",DATE(YEAR(C21),MONTH(C21),1))</f>
         <v/>
       </c>
-      <c r="E21" s="37" t="n"/>
-      <c r="F21" s="36" t="n"/>
+      <c r="E21" s="38" t="n"/>
+      <c r="F21" s="37" t="n"/>
       <c r="G21" s="1" t="n"/>
       <c r="H21" s="1" t="n"/>
       <c r="I21" s="1" t="n"/>
@@ -15928,18 +15943,18 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
-      <c r="B22" s="40" t="n">
+      <c r="B22" s="41" t="n">
         <v>17</v>
       </c>
-      <c r="C22" s="41" t="n">
+      <c r="C22" s="42" t="n">
         <v>46266</v>
       </c>
-      <c r="D22" s="42">
+      <c r="D22" s="43">
         <f>IF(C22="","",DATE(YEAR(C22),MONTH(C22),1))</f>
         <v/>
       </c>
-      <c r="E22" s="39" t="n"/>
-      <c r="F22" s="38" t="n"/>
+      <c r="E22" s="40" t="n"/>
+      <c r="F22" s="39" t="n"/>
       <c r="G22" s="1" t="n"/>
       <c r="H22" s="1" t="n"/>
       <c r="I22" s="1" t="n"/>
@@ -15967,18 +15982,18 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
-      <c r="B23" s="40" t="n">
+      <c r="B23" s="41" t="n">
         <v>18</v>
       </c>
-      <c r="C23" s="43" t="n">
+      <c r="C23" s="44" t="n">
         <v>46280</v>
       </c>
-      <c r="D23" s="42">
+      <c r="D23" s="43">
         <f>IF(C23="","",DATE(YEAR(C23),MONTH(C23),1))</f>
         <v/>
       </c>
-      <c r="E23" s="37" t="n"/>
-      <c r="F23" s="36" t="n"/>
+      <c r="E23" s="38" t="n"/>
+      <c r="F23" s="37" t="n"/>
       <c r="G23" s="1" t="n"/>
       <c r="H23" s="1" t="n"/>
       <c r="I23" s="1" t="n"/>
@@ -16006,18 +16021,18 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
-      <c r="B24" s="40" t="n">
+      <c r="B24" s="41" t="n">
         <v>19</v>
       </c>
-      <c r="C24" s="41" t="n">
+      <c r="C24" s="42" t="n">
         <v>46296</v>
       </c>
-      <c r="D24" s="42">
+      <c r="D24" s="43">
         <f>IF(C24="","",DATE(YEAR(C24),MONTH(C24),1))</f>
         <v/>
       </c>
-      <c r="E24" s="39" t="n"/>
-      <c r="F24" s="38" t="n"/>
+      <c r="E24" s="40" t="n"/>
+      <c r="F24" s="39" t="n"/>
       <c r="G24" s="1" t="n"/>
       <c r="H24" s="1" t="n"/>
       <c r="I24" s="1" t="n"/>
@@ -16045,18 +16060,18 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
-      <c r="B25" s="40" t="n">
+      <c r="B25" s="41" t="n">
         <v>20</v>
       </c>
-      <c r="C25" s="43" t="n">
+      <c r="C25" s="44" t="n">
         <v>46310</v>
       </c>
-      <c r="D25" s="42">
+      <c r="D25" s="43">
         <f>IF(C25="","",DATE(YEAR(C25),MONTH(C25),1))</f>
         <v/>
       </c>
-      <c r="E25" s="37" t="n"/>
-      <c r="F25" s="36" t="n"/>
+      <c r="E25" s="38" t="n"/>
+      <c r="F25" s="37" t="n"/>
       <c r="G25" s="1" t="n"/>
       <c r="H25" s="1" t="n"/>
       <c r="I25" s="1" t="n"/>
@@ -16084,18 +16099,18 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
-      <c r="B26" s="40" t="n">
+      <c r="B26" s="41" t="n">
         <v>21</v>
       </c>
-      <c r="C26" s="41" t="n">
+      <c r="C26" s="42" t="n">
         <v>46327</v>
       </c>
-      <c r="D26" s="42">
+      <c r="D26" s="43">
         <f>IF(C26="","",DATE(YEAR(C26),MONTH(C26),1))</f>
         <v/>
       </c>
-      <c r="E26" s="39" t="n"/>
-      <c r="F26" s="38" t="n"/>
+      <c r="E26" s="40" t="n"/>
+      <c r="F26" s="39" t="n"/>
       <c r="G26" s="1" t="n"/>
       <c r="H26" s="1" t="n"/>
       <c r="I26" s="1" t="n"/>
@@ -16123,18 +16138,18 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
-      <c r="B27" s="40" t="n">
+      <c r="B27" s="41" t="n">
         <v>22</v>
       </c>
-      <c r="C27" s="43" t="n">
+      <c r="C27" s="44" t="n">
         <v>46341</v>
       </c>
-      <c r="D27" s="42">
+      <c r="D27" s="43">
         <f>IF(C27="","",DATE(YEAR(C27),MONTH(C27),1))</f>
         <v/>
       </c>
-      <c r="E27" s="37" t="n"/>
-      <c r="F27" s="36" t="n"/>
+      <c r="E27" s="38" t="n"/>
+      <c r="F27" s="37" t="n"/>
       <c r="G27" s="1" t="n"/>
       <c r="H27" s="1" t="n"/>
       <c r="I27" s="1" t="n"/>
@@ -16162,18 +16177,18 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n"/>
-      <c r="B28" s="40" t="n">
+      <c r="B28" s="41" t="n">
         <v>23</v>
       </c>
-      <c r="C28" s="41" t="n">
+      <c r="C28" s="42" t="n">
         <v>46357</v>
       </c>
-      <c r="D28" s="42">
+      <c r="D28" s="43">
         <f>IF(C28="","",DATE(YEAR(C28),MONTH(C28),1))</f>
         <v/>
       </c>
-      <c r="E28" s="39" t="n"/>
-      <c r="F28" s="38" t="n"/>
+      <c r="E28" s="40" t="n"/>
+      <c r="F28" s="39" t="n"/>
       <c r="G28" s="1" t="n"/>
       <c r="H28" s="1" t="n"/>
       <c r="I28" s="1" t="n"/>
@@ -16201,18 +16216,18 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
-      <c r="B29" s="40" t="n">
+      <c r="B29" s="41" t="n">
         <v>24</v>
       </c>
-      <c r="C29" s="43" t="n">
+      <c r="C29" s="44" t="n">
         <v>46371</v>
       </c>
-      <c r="D29" s="42">
+      <c r="D29" s="43">
         <f>IF(C29="","",DATE(YEAR(C29),MONTH(C29),1))</f>
         <v/>
       </c>
-      <c r="E29" s="37" t="n"/>
-      <c r="F29" s="36" t="n"/>
+      <c r="E29" s="38" t="n"/>
+      <c r="F29" s="37" t="n"/>
       <c r="G29" s="1" t="n"/>
       <c r="H29" s="1" t="n"/>
       <c r="I29" s="1" t="n"/>
@@ -16240,14 +16255,14 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
-      <c r="B30" s="40" t="n"/>
-      <c r="C30" s="41" t="n"/>
-      <c r="D30" s="42">
+      <c r="B30" s="41" t="n"/>
+      <c r="C30" s="42" t="n"/>
+      <c r="D30" s="43">
         <f>IF(C30="","",DATE(YEAR(C30),MONTH(C30),1))</f>
         <v/>
       </c>
-      <c r="E30" s="39" t="n"/>
-      <c r="F30" s="38" t="n"/>
+      <c r="E30" s="40" t="n"/>
+      <c r="F30" s="39" t="n"/>
       <c r="G30" s="1" t="n"/>
       <c r="H30" s="1" t="n"/>
       <c r="I30" s="1" t="n"/>
@@ -16275,14 +16290,14 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
-      <c r="B31" s="40" t="n"/>
-      <c r="C31" s="43" t="n"/>
-      <c r="D31" s="42">
+      <c r="B31" s="41" t="n"/>
+      <c r="C31" s="44" t="n"/>
+      <c r="D31" s="43">
         <f>IF(C31="","",DATE(YEAR(C31),MONTH(C31),1))</f>
         <v/>
       </c>
-      <c r="E31" s="37" t="n"/>
-      <c r="F31" s="36" t="n"/>
+      <c r="E31" s="38" t="n"/>
+      <c r="F31" s="37" t="n"/>
       <c r="G31" s="1" t="n"/>
       <c r="H31" s="1" t="n"/>
       <c r="I31" s="1" t="n"/>
@@ -16310,14 +16325,14 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
-      <c r="B32" s="40" t="n"/>
-      <c r="C32" s="41" t="n"/>
-      <c r="D32" s="42">
+      <c r="B32" s="41" t="n"/>
+      <c r="C32" s="42" t="n"/>
+      <c r="D32" s="43">
         <f>IF(C32="","",DATE(YEAR(C32),MONTH(C32),1))</f>
         <v/>
       </c>
-      <c r="E32" s="39" t="n"/>
-      <c r="F32" s="38" t="n"/>
+      <c r="E32" s="40" t="n"/>
+      <c r="F32" s="39" t="n"/>
       <c r="G32" s="1" t="n"/>
       <c r="H32" s="1" t="n"/>
       <c r="I32" s="1" t="n"/>
@@ -16345,14 +16360,14 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
-      <c r="B33" s="40" t="n"/>
-      <c r="C33" s="43" t="n"/>
-      <c r="D33" s="42">
+      <c r="B33" s="41" t="n"/>
+      <c r="C33" s="44" t="n"/>
+      <c r="D33" s="43">
         <f>IF(C33="","",DATE(YEAR(C33),MONTH(C33),1))</f>
         <v/>
       </c>
-      <c r="E33" s="37" t="n"/>
-      <c r="F33" s="36" t="n"/>
+      <c r="E33" s="38" t="n"/>
+      <c r="F33" s="37" t="n"/>
       <c r="G33" s="1" t="n"/>
       <c r="H33" s="1" t="n"/>
       <c r="I33" s="1" t="n"/>
@@ -16380,14 +16395,14 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n"/>
-      <c r="B34" s="40" t="n"/>
-      <c r="C34" s="41" t="n"/>
-      <c r="D34" s="42">
+      <c r="B34" s="41" t="n"/>
+      <c r="C34" s="42" t="n"/>
+      <c r="D34" s="43">
         <f>IF(C34="","",DATE(YEAR(C34),MONTH(C34),1))</f>
         <v/>
       </c>
-      <c r="E34" s="39" t="n"/>
-      <c r="F34" s="38" t="n"/>
+      <c r="E34" s="40" t="n"/>
+      <c r="F34" s="39" t="n"/>
       <c r="G34" s="1" t="n"/>
       <c r="H34" s="1" t="n"/>
       <c r="I34" s="1" t="n"/>
@@ -16415,14 +16430,14 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n"/>
-      <c r="B35" s="40" t="n"/>
-      <c r="C35" s="43" t="n"/>
-      <c r="D35" s="42">
+      <c r="B35" s="41" t="n"/>
+      <c r="C35" s="44" t="n"/>
+      <c r="D35" s="43">
         <f>IF(C35="","",DATE(YEAR(C35),MONTH(C35),1))</f>
         <v/>
       </c>
-      <c r="E35" s="37" t="n"/>
-      <c r="F35" s="36" t="n"/>
+      <c r="E35" s="38" t="n"/>
+      <c r="F35" s="37" t="n"/>
       <c r="G35" s="1" t="n"/>
       <c r="H35" s="1" t="n"/>
       <c r="I35" s="1" t="n"/>
@@ -16450,18 +16465,18 @@
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="1" t="n"/>
-      <c r="B36" s="24" t="inlineStr">
+      <c r="B36" s="25" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C36" s="24" t="n"/>
-      <c r="D36" s="24" t="n"/>
-      <c r="E36" s="28">
+      <c r="C36" s="25" t="n"/>
+      <c r="D36" s="25" t="n"/>
+      <c r="E36" s="29">
         <f>SUM(E6:E35)</f>
         <v/>
       </c>
-      <c r="F36" s="24" t="n"/>
+      <c r="F36" s="25" t="n"/>
       <c r="G36" s="1" t="n"/>
       <c r="H36" s="1" t="n"/>
       <c r="I36" s="1" t="n"/>
@@ -21736,12 +21751,24 @@
       <c r="AD200" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B4:F4"/>
     <mergeCell ref="B3:F3"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;R&amp;8 &amp;K9AA3C2Budget Planner - Claude Skill by 6inq</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -21847,25 +21874,13 @@
       <c r="AC3" s="1" t="n"/>
       <c r="AD3" s="1" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" ht="14" customHeight="1">
       <c r="A4" s="1" t="n"/>
-      <c r="B4" s="1" t="n"/>
-      <c r="C4" s="1" t="n"/>
-      <c r="D4" s="1" t="n"/>
-      <c r="E4" s="1" t="n"/>
-      <c r="F4" s="1" t="n"/>
-      <c r="G4" s="1" t="n"/>
-      <c r="H4" s="1" t="n"/>
-      <c r="I4" s="1" t="n"/>
-      <c r="J4" s="1" t="n"/>
-      <c r="K4" s="1" t="n"/>
-      <c r="L4" s="1" t="n"/>
-      <c r="M4" s="1" t="n"/>
-      <c r="N4" s="1" t="n"/>
-      <c r="O4" s="1" t="n"/>
-      <c r="P4" s="1" t="n"/>
-      <c r="Q4" s="1" t="n"/>
-      <c r="R4" s="1" t="n"/>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Budget Planner - Claude Skill by 6inq</t>
+        </is>
+      </c>
       <c r="S4" s="1" t="n"/>
       <c r="T4" s="1" t="n"/>
       <c r="U4" s="1" t="n"/>
@@ -21881,63 +21896,63 @@
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="1" t="n"/>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>Due Day</t>
         </is>
       </c>
-      <c r="F5" s="31" t="n">
+      <c r="F5" s="32" t="n">
         <v>46023</v>
       </c>
-      <c r="G5" s="31" t="n">
+      <c r="G5" s="32" t="n">
         <v>46054</v>
       </c>
-      <c r="H5" s="31" t="n">
+      <c r="H5" s="32" t="n">
         <v>46082</v>
       </c>
-      <c r="I5" s="31" t="n">
+      <c r="I5" s="32" t="n">
         <v>46113</v>
       </c>
-      <c r="J5" s="31" t="n">
+      <c r="J5" s="32" t="n">
         <v>46143</v>
       </c>
-      <c r="K5" s="31" t="n">
+      <c r="K5" s="32" t="n">
         <v>46174</v>
       </c>
-      <c r="L5" s="31" t="n">
+      <c r="L5" s="32" t="n">
         <v>46204</v>
       </c>
-      <c r="M5" s="31" t="n">
+      <c r="M5" s="32" t="n">
         <v>46235</v>
       </c>
-      <c r="N5" s="31" t="n">
+      <c r="N5" s="32" t="n">
         <v>46266</v>
       </c>
-      <c r="O5" s="31" t="n">
+      <c r="O5" s="32" t="n">
         <v>46296</v>
       </c>
-      <c r="P5" s="31" t="n">
+      <c r="P5" s="32" t="n">
         <v>46327</v>
       </c>
-      <c r="Q5" s="31" t="n">
+      <c r="Q5" s="32" t="n">
         <v>46357</v>
       </c>
-      <c r="R5" s="13" t="inlineStr">
+      <c r="R5" s="14" t="inlineStr">
         <is>
           <t>Annual Total</t>
         </is>
@@ -21957,37 +21972,37 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
-      <c r="B6" s="38" t="inlineStr">
+      <c r="B6" s="39" t="inlineStr">
         <is>
           <t>Rent / Mortgage</t>
         </is>
       </c>
-      <c r="C6" s="38" t="inlineStr">
+      <c r="C6" s="39" t="inlineStr">
         <is>
           <t>Housing</t>
         </is>
       </c>
-      <c r="D6" s="44" t="inlineStr">
+      <c r="D6" s="45" t="inlineStr">
         <is>
           <t>Bill</t>
         </is>
       </c>
-      <c r="E6" s="44" t="n">
+      <c r="E6" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="39" t="n"/>
-      <c r="G6" s="39" t="n"/>
-      <c r="H6" s="39" t="n"/>
-      <c r="I6" s="39" t="n"/>
-      <c r="J6" s="39" t="n"/>
-      <c r="K6" s="39" t="n"/>
-      <c r="L6" s="39" t="n"/>
-      <c r="M6" s="39" t="n"/>
-      <c r="N6" s="39" t="n"/>
-      <c r="O6" s="39" t="n"/>
-      <c r="P6" s="39" t="n"/>
-      <c r="Q6" s="39" t="n"/>
-      <c r="R6" s="35">
+      <c r="F6" s="40" t="n"/>
+      <c r="G6" s="40" t="n"/>
+      <c r="H6" s="40" t="n"/>
+      <c r="I6" s="40" t="n"/>
+      <c r="J6" s="40" t="n"/>
+      <c r="K6" s="40" t="n"/>
+      <c r="L6" s="40" t="n"/>
+      <c r="M6" s="40" t="n"/>
+      <c r="N6" s="40" t="n"/>
+      <c r="O6" s="40" t="n"/>
+      <c r="P6" s="40" t="n"/>
+      <c r="Q6" s="40" t="n"/>
+      <c r="R6" s="36">
         <f>IF(COUNT(F6:Q6)=0,"",SUM(F6:Q6))</f>
         <v/>
       </c>
@@ -22006,35 +22021,35 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>Electricity</t>
         </is>
       </c>
-      <c r="C7" s="36" t="inlineStr">
+      <c r="C7" s="37" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
       </c>
-      <c r="D7" s="45" t="inlineStr">
+      <c r="D7" s="46" t="inlineStr">
         <is>
           <t>Bill</t>
         </is>
       </c>
-      <c r="E7" s="45" t="n"/>
-      <c r="F7" s="37" t="n"/>
-      <c r="G7" s="37" t="n"/>
-      <c r="H7" s="37" t="n"/>
-      <c r="I7" s="37" t="n"/>
-      <c r="J7" s="37" t="n"/>
-      <c r="K7" s="37" t="n"/>
-      <c r="L7" s="37" t="n"/>
-      <c r="M7" s="37" t="n"/>
-      <c r="N7" s="37" t="n"/>
-      <c r="O7" s="37" t="n"/>
-      <c r="P7" s="37" t="n"/>
-      <c r="Q7" s="37" t="n"/>
-      <c r="R7" s="35">
+      <c r="E7" s="46" t="n"/>
+      <c r="F7" s="38" t="n"/>
+      <c r="G7" s="38" t="n"/>
+      <c r="H7" s="38" t="n"/>
+      <c r="I7" s="38" t="n"/>
+      <c r="J7" s="38" t="n"/>
+      <c r="K7" s="38" t="n"/>
+      <c r="L7" s="38" t="n"/>
+      <c r="M7" s="38" t="n"/>
+      <c r="N7" s="38" t="n"/>
+      <c r="O7" s="38" t="n"/>
+      <c r="P7" s="38" t="n"/>
+      <c r="Q7" s="38" t="n"/>
+      <c r="R7" s="36">
         <f>IF(COUNT(F7:Q7)=0,"",SUM(F7:Q7))</f>
         <v/>
       </c>
@@ -22053,35 +22068,35 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
-      <c r="B8" s="38" t="inlineStr">
+      <c r="B8" s="39" t="inlineStr">
         <is>
           <t>Water / Sewer</t>
         </is>
       </c>
-      <c r="C8" s="38" t="inlineStr">
+      <c r="C8" s="39" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
       </c>
-      <c r="D8" s="44" t="inlineStr">
+      <c r="D8" s="45" t="inlineStr">
         <is>
           <t>Bill</t>
         </is>
       </c>
-      <c r="E8" s="44" t="n"/>
-      <c r="F8" s="39" t="n"/>
-      <c r="G8" s="39" t="n"/>
-      <c r="H8" s="39" t="n"/>
-      <c r="I8" s="39" t="n"/>
-      <c r="J8" s="39" t="n"/>
-      <c r="K8" s="39" t="n"/>
-      <c r="L8" s="39" t="n"/>
-      <c r="M8" s="39" t="n"/>
-      <c r="N8" s="39" t="n"/>
-      <c r="O8" s="39" t="n"/>
-      <c r="P8" s="39" t="n"/>
-      <c r="Q8" s="39" t="n"/>
-      <c r="R8" s="35">
+      <c r="E8" s="45" t="n"/>
+      <c r="F8" s="40" t="n"/>
+      <c r="G8" s="40" t="n"/>
+      <c r="H8" s="40" t="n"/>
+      <c r="I8" s="40" t="n"/>
+      <c r="J8" s="40" t="n"/>
+      <c r="K8" s="40" t="n"/>
+      <c r="L8" s="40" t="n"/>
+      <c r="M8" s="40" t="n"/>
+      <c r="N8" s="40" t="n"/>
+      <c r="O8" s="40" t="n"/>
+      <c r="P8" s="40" t="n"/>
+      <c r="Q8" s="40" t="n"/>
+      <c r="R8" s="36">
         <f>IF(COUNT(F8:Q8)=0,"",SUM(F8:Q8))</f>
         <v/>
       </c>
@@ -22100,35 +22115,35 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>Internet</t>
         </is>
       </c>
-      <c r="C9" s="36" t="inlineStr">
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
       </c>
-      <c r="D9" s="45" t="inlineStr">
+      <c r="D9" s="46" t="inlineStr">
         <is>
           <t>Bill</t>
         </is>
       </c>
-      <c r="E9" s="45" t="n"/>
-      <c r="F9" s="37" t="n"/>
-      <c r="G9" s="37" t="n"/>
-      <c r="H9" s="37" t="n"/>
-      <c r="I9" s="37" t="n"/>
-      <c r="J9" s="37" t="n"/>
-      <c r="K9" s="37" t="n"/>
-      <c r="L9" s="37" t="n"/>
-      <c r="M9" s="37" t="n"/>
-      <c r="N9" s="37" t="n"/>
-      <c r="O9" s="37" t="n"/>
-      <c r="P9" s="37" t="n"/>
-      <c r="Q9" s="37" t="n"/>
-      <c r="R9" s="35">
+      <c r="E9" s="46" t="n"/>
+      <c r="F9" s="38" t="n"/>
+      <c r="G9" s="38" t="n"/>
+      <c r="H9" s="38" t="n"/>
+      <c r="I9" s="38" t="n"/>
+      <c r="J9" s="38" t="n"/>
+      <c r="K9" s="38" t="n"/>
+      <c r="L9" s="38" t="n"/>
+      <c r="M9" s="38" t="n"/>
+      <c r="N9" s="38" t="n"/>
+      <c r="O9" s="38" t="n"/>
+      <c r="P9" s="38" t="n"/>
+      <c r="Q9" s="38" t="n"/>
+      <c r="R9" s="36">
         <f>IF(COUNT(F9:Q9)=0,"",SUM(F9:Q9))</f>
         <v/>
       </c>
@@ -22147,35 +22162,35 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
-      <c r="B10" s="38" t="inlineStr">
+      <c r="B10" s="39" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="C10" s="38" t="inlineStr">
+      <c r="C10" s="39" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
       </c>
-      <c r="D10" s="44" t="inlineStr">
+      <c r="D10" s="45" t="inlineStr">
         <is>
           <t>Bill</t>
         </is>
       </c>
-      <c r="E10" s="44" t="n"/>
-      <c r="F10" s="39" t="n"/>
-      <c r="G10" s="39" t="n"/>
-      <c r="H10" s="39" t="n"/>
-      <c r="I10" s="39" t="n"/>
-      <c r="J10" s="39" t="n"/>
-      <c r="K10" s="39" t="n"/>
-      <c r="L10" s="39" t="n"/>
-      <c r="M10" s="39" t="n"/>
-      <c r="N10" s="39" t="n"/>
-      <c r="O10" s="39" t="n"/>
-      <c r="P10" s="39" t="n"/>
-      <c r="Q10" s="39" t="n"/>
-      <c r="R10" s="35">
+      <c r="E10" s="45" t="n"/>
+      <c r="F10" s="40" t="n"/>
+      <c r="G10" s="40" t="n"/>
+      <c r="H10" s="40" t="n"/>
+      <c r="I10" s="40" t="n"/>
+      <c r="J10" s="40" t="n"/>
+      <c r="K10" s="40" t="n"/>
+      <c r="L10" s="40" t="n"/>
+      <c r="M10" s="40" t="n"/>
+      <c r="N10" s="40" t="n"/>
+      <c r="O10" s="40" t="n"/>
+      <c r="P10" s="40" t="n"/>
+      <c r="Q10" s="40" t="n"/>
+      <c r="R10" s="36">
         <f>IF(COUNT(F10:Q10)=0,"",SUM(F10:Q10))</f>
         <v/>
       </c>
@@ -22194,35 +22209,35 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
-      <c r="B11" s="36" t="inlineStr">
+      <c r="B11" s="37" t="inlineStr">
         <is>
           <t>Car Payment</t>
         </is>
       </c>
-      <c r="C11" s="36" t="inlineStr">
+      <c r="C11" s="37" t="inlineStr">
         <is>
           <t>Transportation</t>
         </is>
       </c>
-      <c r="D11" s="45" t="inlineStr">
+      <c r="D11" s="46" t="inlineStr">
         <is>
           <t>Bill</t>
         </is>
       </c>
-      <c r="E11" s="45" t="n"/>
-      <c r="F11" s="37" t="n"/>
-      <c r="G11" s="37" t="n"/>
-      <c r="H11" s="37" t="n"/>
-      <c r="I11" s="37" t="n"/>
-      <c r="J11" s="37" t="n"/>
-      <c r="K11" s="37" t="n"/>
-      <c r="L11" s="37" t="n"/>
-      <c r="M11" s="37" t="n"/>
-      <c r="N11" s="37" t="n"/>
-      <c r="O11" s="37" t="n"/>
-      <c r="P11" s="37" t="n"/>
-      <c r="Q11" s="37" t="n"/>
-      <c r="R11" s="35">
+      <c r="E11" s="46" t="n"/>
+      <c r="F11" s="38" t="n"/>
+      <c r="G11" s="38" t="n"/>
+      <c r="H11" s="38" t="n"/>
+      <c r="I11" s="38" t="n"/>
+      <c r="J11" s="38" t="n"/>
+      <c r="K11" s="38" t="n"/>
+      <c r="L11" s="38" t="n"/>
+      <c r="M11" s="38" t="n"/>
+      <c r="N11" s="38" t="n"/>
+      <c r="O11" s="38" t="n"/>
+      <c r="P11" s="38" t="n"/>
+      <c r="Q11" s="38" t="n"/>
+      <c r="R11" s="36">
         <f>IF(COUNT(F11:Q11)=0,"",SUM(F11:Q11))</f>
         <v/>
       </c>
@@ -22241,35 +22256,35 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
-      <c r="B12" s="38" t="inlineStr">
+      <c r="B12" s="39" t="inlineStr">
         <is>
           <t>Car Insurance</t>
         </is>
       </c>
-      <c r="C12" s="38" t="inlineStr">
+      <c r="C12" s="39" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D12" s="44" t="inlineStr">
+      <c r="D12" s="45" t="inlineStr">
         <is>
           <t>Bill</t>
         </is>
       </c>
-      <c r="E12" s="44" t="n"/>
-      <c r="F12" s="39" t="n"/>
-      <c r="G12" s="39" t="n"/>
-      <c r="H12" s="39" t="n"/>
-      <c r="I12" s="39" t="n"/>
-      <c r="J12" s="39" t="n"/>
-      <c r="K12" s="39" t="n"/>
-      <c r="L12" s="39" t="n"/>
-      <c r="M12" s="39" t="n"/>
-      <c r="N12" s="39" t="n"/>
-      <c r="O12" s="39" t="n"/>
-      <c r="P12" s="39" t="n"/>
-      <c r="Q12" s="39" t="n"/>
-      <c r="R12" s="35">
+      <c r="E12" s="45" t="n"/>
+      <c r="F12" s="40" t="n"/>
+      <c r="G12" s="40" t="n"/>
+      <c r="H12" s="40" t="n"/>
+      <c r="I12" s="40" t="n"/>
+      <c r="J12" s="40" t="n"/>
+      <c r="K12" s="40" t="n"/>
+      <c r="L12" s="40" t="n"/>
+      <c r="M12" s="40" t="n"/>
+      <c r="N12" s="40" t="n"/>
+      <c r="O12" s="40" t="n"/>
+      <c r="P12" s="40" t="n"/>
+      <c r="Q12" s="40" t="n"/>
+      <c r="R12" s="36">
         <f>IF(COUNT(F12:Q12)=0,"",SUM(F12:Q12))</f>
         <v/>
       </c>
@@ -22288,35 +22303,35 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>Health Insurance</t>
         </is>
       </c>
-      <c r="C13" s="36" t="inlineStr">
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D13" s="45" t="inlineStr">
+      <c r="D13" s="46" t="inlineStr">
         <is>
           <t>Bill</t>
         </is>
       </c>
-      <c r="E13" s="45" t="n"/>
-      <c r="F13" s="37" t="n"/>
-      <c r="G13" s="37" t="n"/>
-      <c r="H13" s="37" t="n"/>
-      <c r="I13" s="37" t="n"/>
-      <c r="J13" s="37" t="n"/>
-      <c r="K13" s="37" t="n"/>
-      <c r="L13" s="37" t="n"/>
-      <c r="M13" s="37" t="n"/>
-      <c r="N13" s="37" t="n"/>
-      <c r="O13" s="37" t="n"/>
-      <c r="P13" s="37" t="n"/>
-      <c r="Q13" s="37" t="n"/>
-      <c r="R13" s="35">
+      <c r="E13" s="46" t="n"/>
+      <c r="F13" s="38" t="n"/>
+      <c r="G13" s="38" t="n"/>
+      <c r="H13" s="38" t="n"/>
+      <c r="I13" s="38" t="n"/>
+      <c r="J13" s="38" t="n"/>
+      <c r="K13" s="38" t="n"/>
+      <c r="L13" s="38" t="n"/>
+      <c r="M13" s="38" t="n"/>
+      <c r="N13" s="38" t="n"/>
+      <c r="O13" s="38" t="n"/>
+      <c r="P13" s="38" t="n"/>
+      <c r="Q13" s="38" t="n"/>
+      <c r="R13" s="36">
         <f>IF(COUNT(F13:Q13)=0,"",SUM(F13:Q13))</f>
         <v/>
       </c>
@@ -22335,35 +22350,35 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
-      <c r="B14" s="38" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>Gas / Fuel</t>
         </is>
       </c>
-      <c r="C14" s="38" t="inlineStr">
+      <c r="C14" s="39" t="inlineStr">
         <is>
           <t>Transportation</t>
         </is>
       </c>
-      <c r="D14" s="44" t="inlineStr">
+      <c r="D14" s="45" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="E14" s="44" t="n"/>
-      <c r="F14" s="39" t="n"/>
-      <c r="G14" s="39" t="n"/>
-      <c r="H14" s="39" t="n"/>
-      <c r="I14" s="39" t="n"/>
-      <c r="J14" s="39" t="n"/>
-      <c r="K14" s="39" t="n"/>
-      <c r="L14" s="39" t="n"/>
-      <c r="M14" s="39" t="n"/>
-      <c r="N14" s="39" t="n"/>
-      <c r="O14" s="39" t="n"/>
-      <c r="P14" s="39" t="n"/>
-      <c r="Q14" s="39" t="n"/>
-      <c r="R14" s="35">
+      <c r="E14" s="45" t="n"/>
+      <c r="F14" s="40" t="n"/>
+      <c r="G14" s="40" t="n"/>
+      <c r="H14" s="40" t="n"/>
+      <c r="I14" s="40" t="n"/>
+      <c r="J14" s="40" t="n"/>
+      <c r="K14" s="40" t="n"/>
+      <c r="L14" s="40" t="n"/>
+      <c r="M14" s="40" t="n"/>
+      <c r="N14" s="40" t="n"/>
+      <c r="O14" s="40" t="n"/>
+      <c r="P14" s="40" t="n"/>
+      <c r="Q14" s="40" t="n"/>
+      <c r="R14" s="36">
         <f>IF(COUNT(F14:Q14)=0,"",SUM(F14:Q14))</f>
         <v/>
       </c>
@@ -22382,35 +22397,35 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
-      <c r="B15" s="36" t="inlineStr">
+      <c r="B15" s="37" t="inlineStr">
         <is>
           <t>Groceries</t>
         </is>
       </c>
-      <c r="C15" s="36" t="inlineStr">
+      <c r="C15" s="37" t="inlineStr">
         <is>
           <t>Food</t>
         </is>
       </c>
-      <c r="D15" s="45" t="inlineStr">
+      <c r="D15" s="46" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="E15" s="45" t="n"/>
-      <c r="F15" s="37" t="n"/>
-      <c r="G15" s="37" t="n"/>
-      <c r="H15" s="37" t="n"/>
-      <c r="I15" s="37" t="n"/>
-      <c r="J15" s="37" t="n"/>
-      <c r="K15" s="37" t="n"/>
-      <c r="L15" s="37" t="n"/>
-      <c r="M15" s="37" t="n"/>
-      <c r="N15" s="37" t="n"/>
-      <c r="O15" s="37" t="n"/>
-      <c r="P15" s="37" t="n"/>
-      <c r="Q15" s="37" t="n"/>
-      <c r="R15" s="35">
+      <c r="E15" s="46" t="n"/>
+      <c r="F15" s="38" t="n"/>
+      <c r="G15" s="38" t="n"/>
+      <c r="H15" s="38" t="n"/>
+      <c r="I15" s="38" t="n"/>
+      <c r="J15" s="38" t="n"/>
+      <c r="K15" s="38" t="n"/>
+      <c r="L15" s="38" t="n"/>
+      <c r="M15" s="38" t="n"/>
+      <c r="N15" s="38" t="n"/>
+      <c r="O15" s="38" t="n"/>
+      <c r="P15" s="38" t="n"/>
+      <c r="Q15" s="38" t="n"/>
+      <c r="R15" s="36">
         <f>IF(COUNT(F15:Q15)=0,"",SUM(F15:Q15))</f>
         <v/>
       </c>
@@ -22429,35 +22444,35 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n"/>
-      <c r="B16" s="38" t="inlineStr">
+      <c r="B16" s="39" t="inlineStr">
         <is>
           <t>Dining Out</t>
         </is>
       </c>
-      <c r="C16" s="38" t="inlineStr">
+      <c r="C16" s="39" t="inlineStr">
         <is>
           <t>Food</t>
         </is>
       </c>
-      <c r="D16" s="44" t="inlineStr">
+      <c r="D16" s="45" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="E16" s="44" t="n"/>
-      <c r="F16" s="39" t="n"/>
-      <c r="G16" s="39" t="n"/>
-      <c r="H16" s="39" t="n"/>
-      <c r="I16" s="39" t="n"/>
-      <c r="J16" s="39" t="n"/>
-      <c r="K16" s="39" t="n"/>
-      <c r="L16" s="39" t="n"/>
-      <c r="M16" s="39" t="n"/>
-      <c r="N16" s="39" t="n"/>
-      <c r="O16" s="39" t="n"/>
-      <c r="P16" s="39" t="n"/>
-      <c r="Q16" s="39" t="n"/>
-      <c r="R16" s="35">
+      <c r="E16" s="45" t="n"/>
+      <c r="F16" s="40" t="n"/>
+      <c r="G16" s="40" t="n"/>
+      <c r="H16" s="40" t="n"/>
+      <c r="I16" s="40" t="n"/>
+      <c r="J16" s="40" t="n"/>
+      <c r="K16" s="40" t="n"/>
+      <c r="L16" s="40" t="n"/>
+      <c r="M16" s="40" t="n"/>
+      <c r="N16" s="40" t="n"/>
+      <c r="O16" s="40" t="n"/>
+      <c r="P16" s="40" t="n"/>
+      <c r="Q16" s="40" t="n"/>
+      <c r="R16" s="36">
         <f>IF(COUNT(F16:Q16)=0,"",SUM(F16:Q16))</f>
         <v/>
       </c>
@@ -22476,35 +22491,35 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
-      <c r="B17" s="36" t="inlineStr">
+      <c r="B17" s="37" t="inlineStr">
         <is>
           <t>Streaming Services</t>
         </is>
       </c>
-      <c r="C17" s="36" t="inlineStr">
+      <c r="C17" s="37" t="inlineStr">
         <is>
           <t>Subscriptions</t>
         </is>
       </c>
-      <c r="D17" s="45" t="inlineStr">
+      <c r="D17" s="46" t="inlineStr">
         <is>
           <t>Bill</t>
         </is>
       </c>
-      <c r="E17" s="45" t="n"/>
-      <c r="F17" s="37" t="n"/>
-      <c r="G17" s="37" t="n"/>
-      <c r="H17" s="37" t="n"/>
-      <c r="I17" s="37" t="n"/>
-      <c r="J17" s="37" t="n"/>
-      <c r="K17" s="37" t="n"/>
-      <c r="L17" s="37" t="n"/>
-      <c r="M17" s="37" t="n"/>
-      <c r="N17" s="37" t="n"/>
-      <c r="O17" s="37" t="n"/>
-      <c r="P17" s="37" t="n"/>
-      <c r="Q17" s="37" t="n"/>
-      <c r="R17" s="35">
+      <c r="E17" s="46" t="n"/>
+      <c r="F17" s="38" t="n"/>
+      <c r="G17" s="38" t="n"/>
+      <c r="H17" s="38" t="n"/>
+      <c r="I17" s="38" t="n"/>
+      <c r="J17" s="38" t="n"/>
+      <c r="K17" s="38" t="n"/>
+      <c r="L17" s="38" t="n"/>
+      <c r="M17" s="38" t="n"/>
+      <c r="N17" s="38" t="n"/>
+      <c r="O17" s="38" t="n"/>
+      <c r="P17" s="38" t="n"/>
+      <c r="Q17" s="38" t="n"/>
+      <c r="R17" s="36">
         <f>IF(COUNT(F17:Q17)=0,"",SUM(F17:Q17))</f>
         <v/>
       </c>
@@ -22523,35 +22538,35 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
-      <c r="B18" s="38" t="inlineStr">
+      <c r="B18" s="39" t="inlineStr">
         <is>
           <t>Gym</t>
         </is>
       </c>
-      <c r="C18" s="38" t="inlineStr">
+      <c r="C18" s="39" t="inlineStr">
         <is>
           <t>Health</t>
         </is>
       </c>
-      <c r="D18" s="44" t="inlineStr">
+      <c r="D18" s="45" t="inlineStr">
         <is>
           <t>Bill</t>
         </is>
       </c>
-      <c r="E18" s="44" t="n"/>
-      <c r="F18" s="39" t="n"/>
-      <c r="G18" s="39" t="n"/>
-      <c r="H18" s="39" t="n"/>
-      <c r="I18" s="39" t="n"/>
-      <c r="J18" s="39" t="n"/>
-      <c r="K18" s="39" t="n"/>
-      <c r="L18" s="39" t="n"/>
-      <c r="M18" s="39" t="n"/>
-      <c r="N18" s="39" t="n"/>
-      <c r="O18" s="39" t="n"/>
-      <c r="P18" s="39" t="n"/>
-      <c r="Q18" s="39" t="n"/>
-      <c r="R18" s="35">
+      <c r="E18" s="45" t="n"/>
+      <c r="F18" s="40" t="n"/>
+      <c r="G18" s="40" t="n"/>
+      <c r="H18" s="40" t="n"/>
+      <c r="I18" s="40" t="n"/>
+      <c r="J18" s="40" t="n"/>
+      <c r="K18" s="40" t="n"/>
+      <c r="L18" s="40" t="n"/>
+      <c r="M18" s="40" t="n"/>
+      <c r="N18" s="40" t="n"/>
+      <c r="O18" s="40" t="n"/>
+      <c r="P18" s="40" t="n"/>
+      <c r="Q18" s="40" t="n"/>
+      <c r="R18" s="36">
         <f>IF(COUNT(F18:Q18)=0,"",SUM(F18:Q18))</f>
         <v/>
       </c>
@@ -22570,35 +22585,35 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
-      <c r="B19" s="36" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="C19" s="36" t="inlineStr">
+      <c r="C19" s="37" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="D19" s="45" t="inlineStr">
+      <c r="D19" s="46" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="E19" s="45" t="n"/>
-      <c r="F19" s="37" t="n"/>
-      <c r="G19" s="37" t="n"/>
-      <c r="H19" s="37" t="n"/>
-      <c r="I19" s="37" t="n"/>
-      <c r="J19" s="37" t="n"/>
-      <c r="K19" s="37" t="n"/>
-      <c r="L19" s="37" t="n"/>
-      <c r="M19" s="37" t="n"/>
-      <c r="N19" s="37" t="n"/>
-      <c r="O19" s="37" t="n"/>
-      <c r="P19" s="37" t="n"/>
-      <c r="Q19" s="37" t="n"/>
-      <c r="R19" s="35">
+      <c r="E19" s="46" t="n"/>
+      <c r="F19" s="38" t="n"/>
+      <c r="G19" s="38" t="n"/>
+      <c r="H19" s="38" t="n"/>
+      <c r="I19" s="38" t="n"/>
+      <c r="J19" s="38" t="n"/>
+      <c r="K19" s="38" t="n"/>
+      <c r="L19" s="38" t="n"/>
+      <c r="M19" s="38" t="n"/>
+      <c r="N19" s="38" t="n"/>
+      <c r="O19" s="38" t="n"/>
+      <c r="P19" s="38" t="n"/>
+      <c r="Q19" s="38" t="n"/>
+      <c r="R19" s="36">
         <f>IF(COUNT(F19:Q19)=0,"",SUM(F19:Q19))</f>
         <v/>
       </c>
@@ -22617,35 +22632,35 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
-      <c r="B20" s="38" t="inlineStr">
+      <c r="B20" s="39" t="inlineStr">
         <is>
           <t>Personal Care</t>
         </is>
       </c>
-      <c r="C20" s="38" t="inlineStr">
+      <c r="C20" s="39" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="D20" s="44" t="inlineStr">
+      <c r="D20" s="45" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="E20" s="44" t="n"/>
-      <c r="F20" s="39" t="n"/>
-      <c r="G20" s="39" t="n"/>
-      <c r="H20" s="39" t="n"/>
-      <c r="I20" s="39" t="n"/>
-      <c r="J20" s="39" t="n"/>
-      <c r="K20" s="39" t="n"/>
-      <c r="L20" s="39" t="n"/>
-      <c r="M20" s="39" t="n"/>
-      <c r="N20" s="39" t="n"/>
-      <c r="O20" s="39" t="n"/>
-      <c r="P20" s="39" t="n"/>
-      <c r="Q20" s="39" t="n"/>
-      <c r="R20" s="35">
+      <c r="E20" s="45" t="n"/>
+      <c r="F20" s="40" t="n"/>
+      <c r="G20" s="40" t="n"/>
+      <c r="H20" s="40" t="n"/>
+      <c r="I20" s="40" t="n"/>
+      <c r="J20" s="40" t="n"/>
+      <c r="K20" s="40" t="n"/>
+      <c r="L20" s="40" t="n"/>
+      <c r="M20" s="40" t="n"/>
+      <c r="N20" s="40" t="n"/>
+      <c r="O20" s="40" t="n"/>
+      <c r="P20" s="40" t="n"/>
+      <c r="Q20" s="40" t="n"/>
+      <c r="R20" s="36">
         <f>IF(COUNT(F20:Q20)=0,"",SUM(F20:Q20))</f>
         <v/>
       </c>
@@ -22664,35 +22679,35 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
-      <c r="B21" s="36" t="inlineStr">
+      <c r="B21" s="37" t="inlineStr">
         <is>
           <t>Clothing</t>
         </is>
       </c>
-      <c r="C21" s="36" t="inlineStr">
+      <c r="C21" s="37" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="D21" s="45" t="inlineStr">
+      <c r="D21" s="46" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="E21" s="45" t="n"/>
-      <c r="F21" s="37" t="n"/>
-      <c r="G21" s="37" t="n"/>
-      <c r="H21" s="37" t="n"/>
-      <c r="I21" s="37" t="n"/>
-      <c r="J21" s="37" t="n"/>
-      <c r="K21" s="37" t="n"/>
-      <c r="L21" s="37" t="n"/>
-      <c r="M21" s="37" t="n"/>
-      <c r="N21" s="37" t="n"/>
-      <c r="O21" s="37" t="n"/>
-      <c r="P21" s="37" t="n"/>
-      <c r="Q21" s="37" t="n"/>
-      <c r="R21" s="35">
+      <c r="E21" s="46" t="n"/>
+      <c r="F21" s="38" t="n"/>
+      <c r="G21" s="38" t="n"/>
+      <c r="H21" s="38" t="n"/>
+      <c r="I21" s="38" t="n"/>
+      <c r="J21" s="38" t="n"/>
+      <c r="K21" s="38" t="n"/>
+      <c r="L21" s="38" t="n"/>
+      <c r="M21" s="38" t="n"/>
+      <c r="N21" s="38" t="n"/>
+      <c r="O21" s="38" t="n"/>
+      <c r="P21" s="38" t="n"/>
+      <c r="Q21" s="38" t="n"/>
+      <c r="R21" s="36">
         <f>IF(COUNT(F21:Q21)=0,"",SUM(F21:Q21))</f>
         <v/>
       </c>
@@ -22711,35 +22726,35 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
-      <c r="B22" s="38" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>Savings Transfer</t>
         </is>
       </c>
-      <c r="C22" s="38" t="inlineStr">
+      <c r="C22" s="39" t="inlineStr">
         <is>
           <t>Savings</t>
         </is>
       </c>
-      <c r="D22" s="44" t="inlineStr">
+      <c r="D22" s="45" t="inlineStr">
         <is>
           <t>Bill</t>
         </is>
       </c>
-      <c r="E22" s="44" t="n"/>
-      <c r="F22" s="39" t="n"/>
-      <c r="G22" s="39" t="n"/>
-      <c r="H22" s="39" t="n"/>
-      <c r="I22" s="39" t="n"/>
-      <c r="J22" s="39" t="n"/>
-      <c r="K22" s="39" t="n"/>
-      <c r="L22" s="39" t="n"/>
-      <c r="M22" s="39" t="n"/>
-      <c r="N22" s="39" t="n"/>
-      <c r="O22" s="39" t="n"/>
-      <c r="P22" s="39" t="n"/>
-      <c r="Q22" s="39" t="n"/>
-      <c r="R22" s="35">
+      <c r="E22" s="45" t="n"/>
+      <c r="F22" s="40" t="n"/>
+      <c r="G22" s="40" t="n"/>
+      <c r="H22" s="40" t="n"/>
+      <c r="I22" s="40" t="n"/>
+      <c r="J22" s="40" t="n"/>
+      <c r="K22" s="40" t="n"/>
+      <c r="L22" s="40" t="n"/>
+      <c r="M22" s="40" t="n"/>
+      <c r="N22" s="40" t="n"/>
+      <c r="O22" s="40" t="n"/>
+      <c r="P22" s="40" t="n"/>
+      <c r="Q22" s="40" t="n"/>
+      <c r="R22" s="36">
         <f>IF(COUNT(F22:Q22)=0,"",SUM(F22:Q22))</f>
         <v/>
       </c>
@@ -22758,23 +22773,23 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
-      <c r="B23" s="36" t="n"/>
-      <c r="C23" s="36" t="n"/>
-      <c r="D23" s="45" t="n"/>
-      <c r="E23" s="45" t="n"/>
-      <c r="F23" s="37" t="n"/>
-      <c r="G23" s="37" t="n"/>
-      <c r="H23" s="37" t="n"/>
-      <c r="I23" s="37" t="n"/>
-      <c r="J23" s="37" t="n"/>
-      <c r="K23" s="37" t="n"/>
-      <c r="L23" s="37" t="n"/>
-      <c r="M23" s="37" t="n"/>
-      <c r="N23" s="37" t="n"/>
-      <c r="O23" s="37" t="n"/>
-      <c r="P23" s="37" t="n"/>
-      <c r="Q23" s="37" t="n"/>
-      <c r="R23" s="35">
+      <c r="B23" s="37" t="n"/>
+      <c r="C23" s="37" t="n"/>
+      <c r="D23" s="46" t="n"/>
+      <c r="E23" s="46" t="n"/>
+      <c r="F23" s="38" t="n"/>
+      <c r="G23" s="38" t="n"/>
+      <c r="H23" s="38" t="n"/>
+      <c r="I23" s="38" t="n"/>
+      <c r="J23" s="38" t="n"/>
+      <c r="K23" s="38" t="n"/>
+      <c r="L23" s="38" t="n"/>
+      <c r="M23" s="38" t="n"/>
+      <c r="N23" s="38" t="n"/>
+      <c r="O23" s="38" t="n"/>
+      <c r="P23" s="38" t="n"/>
+      <c r="Q23" s="38" t="n"/>
+      <c r="R23" s="36">
         <f>IF(COUNT(F23:Q23)=0,"",SUM(F23:Q23))</f>
         <v/>
       </c>
@@ -22793,23 +22808,23 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
-      <c r="B24" s="38" t="n"/>
-      <c r="C24" s="38" t="n"/>
-      <c r="D24" s="44" t="n"/>
-      <c r="E24" s="44" t="n"/>
-      <c r="F24" s="39" t="n"/>
-      <c r="G24" s="39" t="n"/>
-      <c r="H24" s="39" t="n"/>
-      <c r="I24" s="39" t="n"/>
-      <c r="J24" s="39" t="n"/>
-      <c r="K24" s="39" t="n"/>
-      <c r="L24" s="39" t="n"/>
-      <c r="M24" s="39" t="n"/>
-      <c r="N24" s="39" t="n"/>
-      <c r="O24" s="39" t="n"/>
-      <c r="P24" s="39" t="n"/>
-      <c r="Q24" s="39" t="n"/>
-      <c r="R24" s="35">
+      <c r="B24" s="39" t="n"/>
+      <c r="C24" s="39" t="n"/>
+      <c r="D24" s="45" t="n"/>
+      <c r="E24" s="45" t="n"/>
+      <c r="F24" s="40" t="n"/>
+      <c r="G24" s="40" t="n"/>
+      <c r="H24" s="40" t="n"/>
+      <c r="I24" s="40" t="n"/>
+      <c r="J24" s="40" t="n"/>
+      <c r="K24" s="40" t="n"/>
+      <c r="L24" s="40" t="n"/>
+      <c r="M24" s="40" t="n"/>
+      <c r="N24" s="40" t="n"/>
+      <c r="O24" s="40" t="n"/>
+      <c r="P24" s="40" t="n"/>
+      <c r="Q24" s="40" t="n"/>
+      <c r="R24" s="36">
         <f>IF(COUNT(F24:Q24)=0,"",SUM(F24:Q24))</f>
         <v/>
       </c>
@@ -22828,23 +22843,23 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
-      <c r="B25" s="36" t="n"/>
-      <c r="C25" s="36" t="n"/>
-      <c r="D25" s="45" t="n"/>
-      <c r="E25" s="45" t="n"/>
-      <c r="F25" s="37" t="n"/>
-      <c r="G25" s="37" t="n"/>
-      <c r="H25" s="37" t="n"/>
-      <c r="I25" s="37" t="n"/>
-      <c r="J25" s="37" t="n"/>
-      <c r="K25" s="37" t="n"/>
-      <c r="L25" s="37" t="n"/>
-      <c r="M25" s="37" t="n"/>
-      <c r="N25" s="37" t="n"/>
-      <c r="O25" s="37" t="n"/>
-      <c r="P25" s="37" t="n"/>
-      <c r="Q25" s="37" t="n"/>
-      <c r="R25" s="35">
+      <c r="B25" s="37" t="n"/>
+      <c r="C25" s="37" t="n"/>
+      <c r="D25" s="46" t="n"/>
+      <c r="E25" s="46" t="n"/>
+      <c r="F25" s="38" t="n"/>
+      <c r="G25" s="38" t="n"/>
+      <c r="H25" s="38" t="n"/>
+      <c r="I25" s="38" t="n"/>
+      <c r="J25" s="38" t="n"/>
+      <c r="K25" s="38" t="n"/>
+      <c r="L25" s="38" t="n"/>
+      <c r="M25" s="38" t="n"/>
+      <c r="N25" s="38" t="n"/>
+      <c r="O25" s="38" t="n"/>
+      <c r="P25" s="38" t="n"/>
+      <c r="Q25" s="38" t="n"/>
+      <c r="R25" s="36">
         <f>IF(COUNT(F25:Q25)=0,"",SUM(F25:Q25))</f>
         <v/>
       </c>
@@ -22863,23 +22878,23 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
-      <c r="B26" s="38" t="n"/>
-      <c r="C26" s="38" t="n"/>
-      <c r="D26" s="44" t="n"/>
-      <c r="E26" s="44" t="n"/>
-      <c r="F26" s="39" t="n"/>
-      <c r="G26" s="39" t="n"/>
-      <c r="H26" s="39" t="n"/>
-      <c r="I26" s="39" t="n"/>
-      <c r="J26" s="39" t="n"/>
-      <c r="K26" s="39" t="n"/>
-      <c r="L26" s="39" t="n"/>
-      <c r="M26" s="39" t="n"/>
-      <c r="N26" s="39" t="n"/>
-      <c r="O26" s="39" t="n"/>
-      <c r="P26" s="39" t="n"/>
-      <c r="Q26" s="39" t="n"/>
-      <c r="R26" s="35">
+      <c r="B26" s="39" t="n"/>
+      <c r="C26" s="39" t="n"/>
+      <c r="D26" s="45" t="n"/>
+      <c r="E26" s="45" t="n"/>
+      <c r="F26" s="40" t="n"/>
+      <c r="G26" s="40" t="n"/>
+      <c r="H26" s="40" t="n"/>
+      <c r="I26" s="40" t="n"/>
+      <c r="J26" s="40" t="n"/>
+      <c r="K26" s="40" t="n"/>
+      <c r="L26" s="40" t="n"/>
+      <c r="M26" s="40" t="n"/>
+      <c r="N26" s="40" t="n"/>
+      <c r="O26" s="40" t="n"/>
+      <c r="P26" s="40" t="n"/>
+      <c r="Q26" s="40" t="n"/>
+      <c r="R26" s="36">
         <f>IF(COUNT(F26:Q26)=0,"",SUM(F26:Q26))</f>
         <v/>
       </c>
@@ -22898,23 +22913,23 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
-      <c r="B27" s="36" t="n"/>
-      <c r="C27" s="36" t="n"/>
-      <c r="D27" s="45" t="n"/>
-      <c r="E27" s="45" t="n"/>
-      <c r="F27" s="37" t="n"/>
-      <c r="G27" s="37" t="n"/>
-      <c r="H27" s="37" t="n"/>
-      <c r="I27" s="37" t="n"/>
-      <c r="J27" s="37" t="n"/>
-      <c r="K27" s="37" t="n"/>
-      <c r="L27" s="37" t="n"/>
-      <c r="M27" s="37" t="n"/>
-      <c r="N27" s="37" t="n"/>
-      <c r="O27" s="37" t="n"/>
-      <c r="P27" s="37" t="n"/>
-      <c r="Q27" s="37" t="n"/>
-      <c r="R27" s="35">
+      <c r="B27" s="37" t="n"/>
+      <c r="C27" s="37" t="n"/>
+      <c r="D27" s="46" t="n"/>
+      <c r="E27" s="46" t="n"/>
+      <c r="F27" s="38" t="n"/>
+      <c r="G27" s="38" t="n"/>
+      <c r="H27" s="38" t="n"/>
+      <c r="I27" s="38" t="n"/>
+      <c r="J27" s="38" t="n"/>
+      <c r="K27" s="38" t="n"/>
+      <c r="L27" s="38" t="n"/>
+      <c r="M27" s="38" t="n"/>
+      <c r="N27" s="38" t="n"/>
+      <c r="O27" s="38" t="n"/>
+      <c r="P27" s="38" t="n"/>
+      <c r="Q27" s="38" t="n"/>
+      <c r="R27" s="36">
         <f>IF(COUNT(F27:Q27)=0,"",SUM(F27:Q27))</f>
         <v/>
       </c>
@@ -22933,23 +22948,23 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n"/>
-      <c r="B28" s="38" t="n"/>
-      <c r="C28" s="38" t="n"/>
-      <c r="D28" s="44" t="n"/>
-      <c r="E28" s="44" t="n"/>
-      <c r="F28" s="39" t="n"/>
-      <c r="G28" s="39" t="n"/>
-      <c r="H28" s="39" t="n"/>
-      <c r="I28" s="39" t="n"/>
-      <c r="J28" s="39" t="n"/>
-      <c r="K28" s="39" t="n"/>
-      <c r="L28" s="39" t="n"/>
-      <c r="M28" s="39" t="n"/>
-      <c r="N28" s="39" t="n"/>
-      <c r="O28" s="39" t="n"/>
-      <c r="P28" s="39" t="n"/>
-      <c r="Q28" s="39" t="n"/>
-      <c r="R28" s="35">
+      <c r="B28" s="39" t="n"/>
+      <c r="C28" s="39" t="n"/>
+      <c r="D28" s="45" t="n"/>
+      <c r="E28" s="45" t="n"/>
+      <c r="F28" s="40" t="n"/>
+      <c r="G28" s="40" t="n"/>
+      <c r="H28" s="40" t="n"/>
+      <c r="I28" s="40" t="n"/>
+      <c r="J28" s="40" t="n"/>
+      <c r="K28" s="40" t="n"/>
+      <c r="L28" s="40" t="n"/>
+      <c r="M28" s="40" t="n"/>
+      <c r="N28" s="40" t="n"/>
+      <c r="O28" s="40" t="n"/>
+      <c r="P28" s="40" t="n"/>
+      <c r="Q28" s="40" t="n"/>
+      <c r="R28" s="36">
         <f>IF(COUNT(F28:Q28)=0,"",SUM(F28:Q28))</f>
         <v/>
       </c>
@@ -22968,23 +22983,23 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
-      <c r="B29" s="36" t="n"/>
-      <c r="C29" s="36" t="n"/>
-      <c r="D29" s="45" t="n"/>
-      <c r="E29" s="45" t="n"/>
-      <c r="F29" s="37" t="n"/>
-      <c r="G29" s="37" t="n"/>
-      <c r="H29" s="37" t="n"/>
-      <c r="I29" s="37" t="n"/>
-      <c r="J29" s="37" t="n"/>
-      <c r="K29" s="37" t="n"/>
-      <c r="L29" s="37" t="n"/>
-      <c r="M29" s="37" t="n"/>
-      <c r="N29" s="37" t="n"/>
-      <c r="O29" s="37" t="n"/>
-      <c r="P29" s="37" t="n"/>
-      <c r="Q29" s="37" t="n"/>
-      <c r="R29" s="35">
+      <c r="B29" s="37" t="n"/>
+      <c r="C29" s="37" t="n"/>
+      <c r="D29" s="46" t="n"/>
+      <c r="E29" s="46" t="n"/>
+      <c r="F29" s="38" t="n"/>
+      <c r="G29" s="38" t="n"/>
+      <c r="H29" s="38" t="n"/>
+      <c r="I29" s="38" t="n"/>
+      <c r="J29" s="38" t="n"/>
+      <c r="K29" s="38" t="n"/>
+      <c r="L29" s="38" t="n"/>
+      <c r="M29" s="38" t="n"/>
+      <c r="N29" s="38" t="n"/>
+      <c r="O29" s="38" t="n"/>
+      <c r="P29" s="38" t="n"/>
+      <c r="Q29" s="38" t="n"/>
+      <c r="R29" s="36">
         <f>IF(COUNT(F29:Q29)=0,"",SUM(F29:Q29))</f>
         <v/>
       </c>
@@ -23003,23 +23018,23 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
-      <c r="B30" s="38" t="n"/>
-      <c r="C30" s="38" t="n"/>
-      <c r="D30" s="44" t="n"/>
-      <c r="E30" s="44" t="n"/>
-      <c r="F30" s="39" t="n"/>
-      <c r="G30" s="39" t="n"/>
-      <c r="H30" s="39" t="n"/>
-      <c r="I30" s="39" t="n"/>
-      <c r="J30" s="39" t="n"/>
-      <c r="K30" s="39" t="n"/>
-      <c r="L30" s="39" t="n"/>
-      <c r="M30" s="39" t="n"/>
-      <c r="N30" s="39" t="n"/>
-      <c r="O30" s="39" t="n"/>
-      <c r="P30" s="39" t="n"/>
-      <c r="Q30" s="39" t="n"/>
-      <c r="R30" s="35">
+      <c r="B30" s="39" t="n"/>
+      <c r="C30" s="39" t="n"/>
+      <c r="D30" s="45" t="n"/>
+      <c r="E30" s="45" t="n"/>
+      <c r="F30" s="40" t="n"/>
+      <c r="G30" s="40" t="n"/>
+      <c r="H30" s="40" t="n"/>
+      <c r="I30" s="40" t="n"/>
+      <c r="J30" s="40" t="n"/>
+      <c r="K30" s="40" t="n"/>
+      <c r="L30" s="40" t="n"/>
+      <c r="M30" s="40" t="n"/>
+      <c r="N30" s="40" t="n"/>
+      <c r="O30" s="40" t="n"/>
+      <c r="P30" s="40" t="n"/>
+      <c r="Q30" s="40" t="n"/>
+      <c r="R30" s="36">
         <f>IF(COUNT(F30:Q30)=0,"",SUM(F30:Q30))</f>
         <v/>
       </c>
@@ -23038,23 +23053,23 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
-      <c r="B31" s="36" t="n"/>
-      <c r="C31" s="36" t="n"/>
-      <c r="D31" s="45" t="n"/>
-      <c r="E31" s="45" t="n"/>
-      <c r="F31" s="37" t="n"/>
-      <c r="G31" s="37" t="n"/>
-      <c r="H31" s="37" t="n"/>
-      <c r="I31" s="37" t="n"/>
-      <c r="J31" s="37" t="n"/>
-      <c r="K31" s="37" t="n"/>
-      <c r="L31" s="37" t="n"/>
-      <c r="M31" s="37" t="n"/>
-      <c r="N31" s="37" t="n"/>
-      <c r="O31" s="37" t="n"/>
-      <c r="P31" s="37" t="n"/>
-      <c r="Q31" s="37" t="n"/>
-      <c r="R31" s="35">
+      <c r="B31" s="37" t="n"/>
+      <c r="C31" s="37" t="n"/>
+      <c r="D31" s="46" t="n"/>
+      <c r="E31" s="46" t="n"/>
+      <c r="F31" s="38" t="n"/>
+      <c r="G31" s="38" t="n"/>
+      <c r="H31" s="38" t="n"/>
+      <c r="I31" s="38" t="n"/>
+      <c r="J31" s="38" t="n"/>
+      <c r="K31" s="38" t="n"/>
+      <c r="L31" s="38" t="n"/>
+      <c r="M31" s="38" t="n"/>
+      <c r="N31" s="38" t="n"/>
+      <c r="O31" s="38" t="n"/>
+      <c r="P31" s="38" t="n"/>
+      <c r="Q31" s="38" t="n"/>
+      <c r="R31" s="36">
         <f>IF(COUNT(F31:Q31)=0,"",SUM(F31:Q31))</f>
         <v/>
       </c>
@@ -23073,23 +23088,23 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
-      <c r="B32" s="38" t="n"/>
-      <c r="C32" s="38" t="n"/>
-      <c r="D32" s="44" t="n"/>
-      <c r="E32" s="44" t="n"/>
-      <c r="F32" s="39" t="n"/>
-      <c r="G32" s="39" t="n"/>
-      <c r="H32" s="39" t="n"/>
-      <c r="I32" s="39" t="n"/>
-      <c r="J32" s="39" t="n"/>
-      <c r="K32" s="39" t="n"/>
-      <c r="L32" s="39" t="n"/>
-      <c r="M32" s="39" t="n"/>
-      <c r="N32" s="39" t="n"/>
-      <c r="O32" s="39" t="n"/>
-      <c r="P32" s="39" t="n"/>
-      <c r="Q32" s="39" t="n"/>
-      <c r="R32" s="35">
+      <c r="B32" s="39" t="n"/>
+      <c r="C32" s="39" t="n"/>
+      <c r="D32" s="45" t="n"/>
+      <c r="E32" s="45" t="n"/>
+      <c r="F32" s="40" t="n"/>
+      <c r="G32" s="40" t="n"/>
+      <c r="H32" s="40" t="n"/>
+      <c r="I32" s="40" t="n"/>
+      <c r="J32" s="40" t="n"/>
+      <c r="K32" s="40" t="n"/>
+      <c r="L32" s="40" t="n"/>
+      <c r="M32" s="40" t="n"/>
+      <c r="N32" s="40" t="n"/>
+      <c r="O32" s="40" t="n"/>
+      <c r="P32" s="40" t="n"/>
+      <c r="Q32" s="40" t="n"/>
+      <c r="R32" s="36">
         <f>IF(COUNT(F32:Q32)=0,"",SUM(F32:Q32))</f>
         <v/>
       </c>
@@ -23108,23 +23123,23 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
-      <c r="B33" s="36" t="n"/>
-      <c r="C33" s="36" t="n"/>
-      <c r="D33" s="45" t="n"/>
-      <c r="E33" s="45" t="n"/>
-      <c r="F33" s="37" t="n"/>
-      <c r="G33" s="37" t="n"/>
-      <c r="H33" s="37" t="n"/>
-      <c r="I33" s="37" t="n"/>
-      <c r="J33" s="37" t="n"/>
-      <c r="K33" s="37" t="n"/>
-      <c r="L33" s="37" t="n"/>
-      <c r="M33" s="37" t="n"/>
-      <c r="N33" s="37" t="n"/>
-      <c r="O33" s="37" t="n"/>
-      <c r="P33" s="37" t="n"/>
-      <c r="Q33" s="37" t="n"/>
-      <c r="R33" s="35">
+      <c r="B33" s="37" t="n"/>
+      <c r="C33" s="37" t="n"/>
+      <c r="D33" s="46" t="n"/>
+      <c r="E33" s="46" t="n"/>
+      <c r="F33" s="38" t="n"/>
+      <c r="G33" s="38" t="n"/>
+      <c r="H33" s="38" t="n"/>
+      <c r="I33" s="38" t="n"/>
+      <c r="J33" s="38" t="n"/>
+      <c r="K33" s="38" t="n"/>
+      <c r="L33" s="38" t="n"/>
+      <c r="M33" s="38" t="n"/>
+      <c r="N33" s="38" t="n"/>
+      <c r="O33" s="38" t="n"/>
+      <c r="P33" s="38" t="n"/>
+      <c r="Q33" s="38" t="n"/>
+      <c r="R33" s="36">
         <f>IF(COUNT(F33:Q33)=0,"",SUM(F33:Q33))</f>
         <v/>
       </c>
@@ -23143,23 +23158,23 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n"/>
-      <c r="B34" s="38" t="n"/>
-      <c r="C34" s="38" t="n"/>
-      <c r="D34" s="44" t="n"/>
-      <c r="E34" s="44" t="n"/>
-      <c r="F34" s="39" t="n"/>
-      <c r="G34" s="39" t="n"/>
-      <c r="H34" s="39" t="n"/>
-      <c r="I34" s="39" t="n"/>
-      <c r="J34" s="39" t="n"/>
-      <c r="K34" s="39" t="n"/>
-      <c r="L34" s="39" t="n"/>
-      <c r="M34" s="39" t="n"/>
-      <c r="N34" s="39" t="n"/>
-      <c r="O34" s="39" t="n"/>
-      <c r="P34" s="39" t="n"/>
-      <c r="Q34" s="39" t="n"/>
-      <c r="R34" s="35">
+      <c r="B34" s="39" t="n"/>
+      <c r="C34" s="39" t="n"/>
+      <c r="D34" s="45" t="n"/>
+      <c r="E34" s="45" t="n"/>
+      <c r="F34" s="40" t="n"/>
+      <c r="G34" s="40" t="n"/>
+      <c r="H34" s="40" t="n"/>
+      <c r="I34" s="40" t="n"/>
+      <c r="J34" s="40" t="n"/>
+      <c r="K34" s="40" t="n"/>
+      <c r="L34" s="40" t="n"/>
+      <c r="M34" s="40" t="n"/>
+      <c r="N34" s="40" t="n"/>
+      <c r="O34" s="40" t="n"/>
+      <c r="P34" s="40" t="n"/>
+      <c r="Q34" s="40" t="n"/>
+      <c r="R34" s="36">
         <f>IF(COUNT(F34:Q34)=0,"",SUM(F34:Q34))</f>
         <v/>
       </c>
@@ -23178,23 +23193,23 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n"/>
-      <c r="B35" s="36" t="n"/>
-      <c r="C35" s="36" t="n"/>
-      <c r="D35" s="45" t="n"/>
-      <c r="E35" s="45" t="n"/>
-      <c r="F35" s="37" t="n"/>
-      <c r="G35" s="37" t="n"/>
-      <c r="H35" s="37" t="n"/>
-      <c r="I35" s="37" t="n"/>
-      <c r="J35" s="37" t="n"/>
-      <c r="K35" s="37" t="n"/>
-      <c r="L35" s="37" t="n"/>
-      <c r="M35" s="37" t="n"/>
-      <c r="N35" s="37" t="n"/>
-      <c r="O35" s="37" t="n"/>
-      <c r="P35" s="37" t="n"/>
-      <c r="Q35" s="37" t="n"/>
-      <c r="R35" s="35">
+      <c r="B35" s="37" t="n"/>
+      <c r="C35" s="37" t="n"/>
+      <c r="D35" s="46" t="n"/>
+      <c r="E35" s="46" t="n"/>
+      <c r="F35" s="38" t="n"/>
+      <c r="G35" s="38" t="n"/>
+      <c r="H35" s="38" t="n"/>
+      <c r="I35" s="38" t="n"/>
+      <c r="J35" s="38" t="n"/>
+      <c r="K35" s="38" t="n"/>
+      <c r="L35" s="38" t="n"/>
+      <c r="M35" s="38" t="n"/>
+      <c r="N35" s="38" t="n"/>
+      <c r="O35" s="38" t="n"/>
+      <c r="P35" s="38" t="n"/>
+      <c r="Q35" s="38" t="n"/>
+      <c r="R35" s="36">
         <f>IF(COUNT(F35:Q35)=0,"",SUM(F35:Q35))</f>
         <v/>
       </c>
@@ -23213,23 +23228,23 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n"/>
-      <c r="B36" s="38" t="n"/>
-      <c r="C36" s="38" t="n"/>
-      <c r="D36" s="44" t="n"/>
-      <c r="E36" s="44" t="n"/>
-      <c r="F36" s="39" t="n"/>
-      <c r="G36" s="39" t="n"/>
-      <c r="H36" s="39" t="n"/>
-      <c r="I36" s="39" t="n"/>
-      <c r="J36" s="39" t="n"/>
-      <c r="K36" s="39" t="n"/>
-      <c r="L36" s="39" t="n"/>
-      <c r="M36" s="39" t="n"/>
-      <c r="N36" s="39" t="n"/>
-      <c r="O36" s="39" t="n"/>
-      <c r="P36" s="39" t="n"/>
-      <c r="Q36" s="39" t="n"/>
-      <c r="R36" s="35">
+      <c r="B36" s="39" t="n"/>
+      <c r="C36" s="39" t="n"/>
+      <c r="D36" s="45" t="n"/>
+      <c r="E36" s="45" t="n"/>
+      <c r="F36" s="40" t="n"/>
+      <c r="G36" s="40" t="n"/>
+      <c r="H36" s="40" t="n"/>
+      <c r="I36" s="40" t="n"/>
+      <c r="J36" s="40" t="n"/>
+      <c r="K36" s="40" t="n"/>
+      <c r="L36" s="40" t="n"/>
+      <c r="M36" s="40" t="n"/>
+      <c r="N36" s="40" t="n"/>
+      <c r="O36" s="40" t="n"/>
+      <c r="P36" s="40" t="n"/>
+      <c r="Q36" s="40" t="n"/>
+      <c r="R36" s="36">
         <f>IF(COUNT(F36:Q36)=0,"",SUM(F36:Q36))</f>
         <v/>
       </c>
@@ -23248,23 +23263,23 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n"/>
-      <c r="B37" s="36" t="n"/>
-      <c r="C37" s="36" t="n"/>
-      <c r="D37" s="45" t="n"/>
-      <c r="E37" s="45" t="n"/>
-      <c r="F37" s="37" t="n"/>
-      <c r="G37" s="37" t="n"/>
-      <c r="H37" s="37" t="n"/>
-      <c r="I37" s="37" t="n"/>
-      <c r="J37" s="37" t="n"/>
-      <c r="K37" s="37" t="n"/>
-      <c r="L37" s="37" t="n"/>
-      <c r="M37" s="37" t="n"/>
-      <c r="N37" s="37" t="n"/>
-      <c r="O37" s="37" t="n"/>
-      <c r="P37" s="37" t="n"/>
-      <c r="Q37" s="37" t="n"/>
-      <c r="R37" s="35">
+      <c r="B37" s="37" t="n"/>
+      <c r="C37" s="37" t="n"/>
+      <c r="D37" s="46" t="n"/>
+      <c r="E37" s="46" t="n"/>
+      <c r="F37" s="38" t="n"/>
+      <c r="G37" s="38" t="n"/>
+      <c r="H37" s="38" t="n"/>
+      <c r="I37" s="38" t="n"/>
+      <c r="J37" s="38" t="n"/>
+      <c r="K37" s="38" t="n"/>
+      <c r="L37" s="38" t="n"/>
+      <c r="M37" s="38" t="n"/>
+      <c r="N37" s="38" t="n"/>
+      <c r="O37" s="38" t="n"/>
+      <c r="P37" s="38" t="n"/>
+      <c r="Q37" s="38" t="n"/>
+      <c r="R37" s="36">
         <f>IF(COUNT(F37:Q37)=0,"",SUM(F37:Q37))</f>
         <v/>
       </c>
@@ -23283,23 +23298,23 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n"/>
-      <c r="B38" s="38" t="n"/>
-      <c r="C38" s="38" t="n"/>
-      <c r="D38" s="44" t="n"/>
-      <c r="E38" s="44" t="n"/>
-      <c r="F38" s="39" t="n"/>
-      <c r="G38" s="39" t="n"/>
-      <c r="H38" s="39" t="n"/>
-      <c r="I38" s="39" t="n"/>
-      <c r="J38" s="39" t="n"/>
-      <c r="K38" s="39" t="n"/>
-      <c r="L38" s="39" t="n"/>
-      <c r="M38" s="39" t="n"/>
-      <c r="N38" s="39" t="n"/>
-      <c r="O38" s="39" t="n"/>
-      <c r="P38" s="39" t="n"/>
-      <c r="Q38" s="39" t="n"/>
-      <c r="R38" s="35">
+      <c r="B38" s="39" t="n"/>
+      <c r="C38" s="39" t="n"/>
+      <c r="D38" s="45" t="n"/>
+      <c r="E38" s="45" t="n"/>
+      <c r="F38" s="40" t="n"/>
+      <c r="G38" s="40" t="n"/>
+      <c r="H38" s="40" t="n"/>
+      <c r="I38" s="40" t="n"/>
+      <c r="J38" s="40" t="n"/>
+      <c r="K38" s="40" t="n"/>
+      <c r="L38" s="40" t="n"/>
+      <c r="M38" s="40" t="n"/>
+      <c r="N38" s="40" t="n"/>
+      <c r="O38" s="40" t="n"/>
+      <c r="P38" s="40" t="n"/>
+      <c r="Q38" s="40" t="n"/>
+      <c r="R38" s="36">
         <f>IF(COUNT(F38:Q38)=0,"",SUM(F38:Q38))</f>
         <v/>
       </c>
@@ -23318,23 +23333,23 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n"/>
-      <c r="B39" s="36" t="n"/>
-      <c r="C39" s="36" t="n"/>
-      <c r="D39" s="45" t="n"/>
-      <c r="E39" s="45" t="n"/>
-      <c r="F39" s="37" t="n"/>
-      <c r="G39" s="37" t="n"/>
-      <c r="H39" s="37" t="n"/>
-      <c r="I39" s="37" t="n"/>
-      <c r="J39" s="37" t="n"/>
-      <c r="K39" s="37" t="n"/>
-      <c r="L39" s="37" t="n"/>
-      <c r="M39" s="37" t="n"/>
-      <c r="N39" s="37" t="n"/>
-      <c r="O39" s="37" t="n"/>
-      <c r="P39" s="37" t="n"/>
-      <c r="Q39" s="37" t="n"/>
-      <c r="R39" s="35">
+      <c r="B39" s="37" t="n"/>
+      <c r="C39" s="37" t="n"/>
+      <c r="D39" s="46" t="n"/>
+      <c r="E39" s="46" t="n"/>
+      <c r="F39" s="38" t="n"/>
+      <c r="G39" s="38" t="n"/>
+      <c r="H39" s="38" t="n"/>
+      <c r="I39" s="38" t="n"/>
+      <c r="J39" s="38" t="n"/>
+      <c r="K39" s="38" t="n"/>
+      <c r="L39" s="38" t="n"/>
+      <c r="M39" s="38" t="n"/>
+      <c r="N39" s="38" t="n"/>
+      <c r="O39" s="38" t="n"/>
+      <c r="P39" s="38" t="n"/>
+      <c r="Q39" s="38" t="n"/>
+      <c r="R39" s="36">
         <f>IF(COUNT(F39:Q39)=0,"",SUM(F39:Q39))</f>
         <v/>
       </c>
@@ -23353,23 +23368,23 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n"/>
-      <c r="B40" s="38" t="n"/>
-      <c r="C40" s="38" t="n"/>
-      <c r="D40" s="44" t="n"/>
-      <c r="E40" s="44" t="n"/>
-      <c r="F40" s="39" t="n"/>
-      <c r="G40" s="39" t="n"/>
-      <c r="H40" s="39" t="n"/>
-      <c r="I40" s="39" t="n"/>
-      <c r="J40" s="39" t="n"/>
-      <c r="K40" s="39" t="n"/>
-      <c r="L40" s="39" t="n"/>
-      <c r="M40" s="39" t="n"/>
-      <c r="N40" s="39" t="n"/>
-      <c r="O40" s="39" t="n"/>
-      <c r="P40" s="39" t="n"/>
-      <c r="Q40" s="39" t="n"/>
-      <c r="R40" s="35">
+      <c r="B40" s="39" t="n"/>
+      <c r="C40" s="39" t="n"/>
+      <c r="D40" s="45" t="n"/>
+      <c r="E40" s="45" t="n"/>
+      <c r="F40" s="40" t="n"/>
+      <c r="G40" s="40" t="n"/>
+      <c r="H40" s="40" t="n"/>
+      <c r="I40" s="40" t="n"/>
+      <c r="J40" s="40" t="n"/>
+      <c r="K40" s="40" t="n"/>
+      <c r="L40" s="40" t="n"/>
+      <c r="M40" s="40" t="n"/>
+      <c r="N40" s="40" t="n"/>
+      <c r="O40" s="40" t="n"/>
+      <c r="P40" s="40" t="n"/>
+      <c r="Q40" s="40" t="n"/>
+      <c r="R40" s="36">
         <f>IF(COUNT(F40:Q40)=0,"",SUM(F40:Q40))</f>
         <v/>
       </c>
@@ -23388,23 +23403,23 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n"/>
-      <c r="B41" s="36" t="n"/>
-      <c r="C41" s="36" t="n"/>
-      <c r="D41" s="45" t="n"/>
-      <c r="E41" s="45" t="n"/>
-      <c r="F41" s="37" t="n"/>
-      <c r="G41" s="37" t="n"/>
-      <c r="H41" s="37" t="n"/>
-      <c r="I41" s="37" t="n"/>
-      <c r="J41" s="37" t="n"/>
-      <c r="K41" s="37" t="n"/>
-      <c r="L41" s="37" t="n"/>
-      <c r="M41" s="37" t="n"/>
-      <c r="N41" s="37" t="n"/>
-      <c r="O41" s="37" t="n"/>
-      <c r="P41" s="37" t="n"/>
-      <c r="Q41" s="37" t="n"/>
-      <c r="R41" s="35">
+      <c r="B41" s="37" t="n"/>
+      <c r="C41" s="37" t="n"/>
+      <c r="D41" s="46" t="n"/>
+      <c r="E41" s="46" t="n"/>
+      <c r="F41" s="38" t="n"/>
+      <c r="G41" s="38" t="n"/>
+      <c r="H41" s="38" t="n"/>
+      <c r="I41" s="38" t="n"/>
+      <c r="J41" s="38" t="n"/>
+      <c r="K41" s="38" t="n"/>
+      <c r="L41" s="38" t="n"/>
+      <c r="M41" s="38" t="n"/>
+      <c r="N41" s="38" t="n"/>
+      <c r="O41" s="38" t="n"/>
+      <c r="P41" s="38" t="n"/>
+      <c r="Q41" s="38" t="n"/>
+      <c r="R41" s="36">
         <f>IF(COUNT(F41:Q41)=0,"",SUM(F41:Q41))</f>
         <v/>
       </c>
@@ -23423,23 +23438,23 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n"/>
-      <c r="B42" s="38" t="n"/>
-      <c r="C42" s="38" t="n"/>
-      <c r="D42" s="44" t="n"/>
-      <c r="E42" s="44" t="n"/>
-      <c r="F42" s="39" t="n"/>
-      <c r="G42" s="39" t="n"/>
-      <c r="H42" s="39" t="n"/>
-      <c r="I42" s="39" t="n"/>
-      <c r="J42" s="39" t="n"/>
-      <c r="K42" s="39" t="n"/>
-      <c r="L42" s="39" t="n"/>
-      <c r="M42" s="39" t="n"/>
-      <c r="N42" s="39" t="n"/>
-      <c r="O42" s="39" t="n"/>
-      <c r="P42" s="39" t="n"/>
-      <c r="Q42" s="39" t="n"/>
-      <c r="R42" s="35">
+      <c r="B42" s="39" t="n"/>
+      <c r="C42" s="39" t="n"/>
+      <c r="D42" s="45" t="n"/>
+      <c r="E42" s="45" t="n"/>
+      <c r="F42" s="40" t="n"/>
+      <c r="G42" s="40" t="n"/>
+      <c r="H42" s="40" t="n"/>
+      <c r="I42" s="40" t="n"/>
+      <c r="J42" s="40" t="n"/>
+      <c r="K42" s="40" t="n"/>
+      <c r="L42" s="40" t="n"/>
+      <c r="M42" s="40" t="n"/>
+      <c r="N42" s="40" t="n"/>
+      <c r="O42" s="40" t="n"/>
+      <c r="P42" s="40" t="n"/>
+      <c r="Q42" s="40" t="n"/>
+      <c r="R42" s="36">
         <f>IF(COUNT(F42:Q42)=0,"",SUM(F42:Q42))</f>
         <v/>
       </c>
@@ -23458,23 +23473,23 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n"/>
-      <c r="B43" s="36" t="n"/>
-      <c r="C43" s="36" t="n"/>
-      <c r="D43" s="45" t="n"/>
-      <c r="E43" s="45" t="n"/>
-      <c r="F43" s="37" t="n"/>
-      <c r="G43" s="37" t="n"/>
-      <c r="H43" s="37" t="n"/>
-      <c r="I43" s="37" t="n"/>
-      <c r="J43" s="37" t="n"/>
-      <c r="K43" s="37" t="n"/>
-      <c r="L43" s="37" t="n"/>
-      <c r="M43" s="37" t="n"/>
-      <c r="N43" s="37" t="n"/>
-      <c r="O43" s="37" t="n"/>
-      <c r="P43" s="37" t="n"/>
-      <c r="Q43" s="37" t="n"/>
-      <c r="R43" s="35">
+      <c r="B43" s="37" t="n"/>
+      <c r="C43" s="37" t="n"/>
+      <c r="D43" s="46" t="n"/>
+      <c r="E43" s="46" t="n"/>
+      <c r="F43" s="38" t="n"/>
+      <c r="G43" s="38" t="n"/>
+      <c r="H43" s="38" t="n"/>
+      <c r="I43" s="38" t="n"/>
+      <c r="J43" s="38" t="n"/>
+      <c r="K43" s="38" t="n"/>
+      <c r="L43" s="38" t="n"/>
+      <c r="M43" s="38" t="n"/>
+      <c r="N43" s="38" t="n"/>
+      <c r="O43" s="38" t="n"/>
+      <c r="P43" s="38" t="n"/>
+      <c r="Q43" s="38" t="n"/>
+      <c r="R43" s="36">
         <f>IF(COUNT(F43:Q43)=0,"",SUM(F43:Q43))</f>
         <v/>
       </c>
@@ -23493,23 +23508,23 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n"/>
-      <c r="B44" s="38" t="n"/>
-      <c r="C44" s="38" t="n"/>
-      <c r="D44" s="44" t="n"/>
-      <c r="E44" s="44" t="n"/>
-      <c r="F44" s="39" t="n"/>
-      <c r="G44" s="39" t="n"/>
-      <c r="H44" s="39" t="n"/>
-      <c r="I44" s="39" t="n"/>
-      <c r="J44" s="39" t="n"/>
-      <c r="K44" s="39" t="n"/>
-      <c r="L44" s="39" t="n"/>
-      <c r="M44" s="39" t="n"/>
-      <c r="N44" s="39" t="n"/>
-      <c r="O44" s="39" t="n"/>
-      <c r="P44" s="39" t="n"/>
-      <c r="Q44" s="39" t="n"/>
-      <c r="R44" s="35">
+      <c r="B44" s="39" t="n"/>
+      <c r="C44" s="39" t="n"/>
+      <c r="D44" s="45" t="n"/>
+      <c r="E44" s="45" t="n"/>
+      <c r="F44" s="40" t="n"/>
+      <c r="G44" s="40" t="n"/>
+      <c r="H44" s="40" t="n"/>
+      <c r="I44" s="40" t="n"/>
+      <c r="J44" s="40" t="n"/>
+      <c r="K44" s="40" t="n"/>
+      <c r="L44" s="40" t="n"/>
+      <c r="M44" s="40" t="n"/>
+      <c r="N44" s="40" t="n"/>
+      <c r="O44" s="40" t="n"/>
+      <c r="P44" s="40" t="n"/>
+      <c r="Q44" s="40" t="n"/>
+      <c r="R44" s="36">
         <f>IF(COUNT(F44:Q44)=0,"",SUM(F44:Q44))</f>
         <v/>
       </c>
@@ -23528,23 +23543,23 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n"/>
-      <c r="B45" s="36" t="n"/>
-      <c r="C45" s="36" t="n"/>
-      <c r="D45" s="45" t="n"/>
-      <c r="E45" s="45" t="n"/>
-      <c r="F45" s="37" t="n"/>
-      <c r="G45" s="37" t="n"/>
-      <c r="H45" s="37" t="n"/>
-      <c r="I45" s="37" t="n"/>
-      <c r="J45" s="37" t="n"/>
-      <c r="K45" s="37" t="n"/>
-      <c r="L45" s="37" t="n"/>
-      <c r="M45" s="37" t="n"/>
-      <c r="N45" s="37" t="n"/>
-      <c r="O45" s="37" t="n"/>
-      <c r="P45" s="37" t="n"/>
-      <c r="Q45" s="37" t="n"/>
-      <c r="R45" s="35">
+      <c r="B45" s="37" t="n"/>
+      <c r="C45" s="37" t="n"/>
+      <c r="D45" s="46" t="n"/>
+      <c r="E45" s="46" t="n"/>
+      <c r="F45" s="38" t="n"/>
+      <c r="G45" s="38" t="n"/>
+      <c r="H45" s="38" t="n"/>
+      <c r="I45" s="38" t="n"/>
+      <c r="J45" s="38" t="n"/>
+      <c r="K45" s="38" t="n"/>
+      <c r="L45" s="38" t="n"/>
+      <c r="M45" s="38" t="n"/>
+      <c r="N45" s="38" t="n"/>
+      <c r="O45" s="38" t="n"/>
+      <c r="P45" s="38" t="n"/>
+      <c r="Q45" s="38" t="n"/>
+      <c r="R45" s="36">
         <f>IF(COUNT(F45:Q45)=0,"",SUM(F45:Q45))</f>
         <v/>
       </c>
@@ -23563,23 +23578,23 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n"/>
-      <c r="B46" s="38" t="n"/>
-      <c r="C46" s="38" t="n"/>
-      <c r="D46" s="44" t="n"/>
-      <c r="E46" s="44" t="n"/>
-      <c r="F46" s="39" t="n"/>
-      <c r="G46" s="39" t="n"/>
-      <c r="H46" s="39" t="n"/>
-      <c r="I46" s="39" t="n"/>
-      <c r="J46" s="39" t="n"/>
-      <c r="K46" s="39" t="n"/>
-      <c r="L46" s="39" t="n"/>
-      <c r="M46" s="39" t="n"/>
-      <c r="N46" s="39" t="n"/>
-      <c r="O46" s="39" t="n"/>
-      <c r="P46" s="39" t="n"/>
-      <c r="Q46" s="39" t="n"/>
-      <c r="R46" s="35">
+      <c r="B46" s="39" t="n"/>
+      <c r="C46" s="39" t="n"/>
+      <c r="D46" s="45" t="n"/>
+      <c r="E46" s="45" t="n"/>
+      <c r="F46" s="40" t="n"/>
+      <c r="G46" s="40" t="n"/>
+      <c r="H46" s="40" t="n"/>
+      <c r="I46" s="40" t="n"/>
+      <c r="J46" s="40" t="n"/>
+      <c r="K46" s="40" t="n"/>
+      <c r="L46" s="40" t="n"/>
+      <c r="M46" s="40" t="n"/>
+      <c r="N46" s="40" t="n"/>
+      <c r="O46" s="40" t="n"/>
+      <c r="P46" s="40" t="n"/>
+      <c r="Q46" s="40" t="n"/>
+      <c r="R46" s="36">
         <f>IF(COUNT(F46:Q46)=0,"",SUM(F46:Q46))</f>
         <v/>
       </c>
@@ -23598,23 +23613,23 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n"/>
-      <c r="B47" s="36" t="n"/>
-      <c r="C47" s="36" t="n"/>
-      <c r="D47" s="45" t="n"/>
-      <c r="E47" s="45" t="n"/>
-      <c r="F47" s="37" t="n"/>
-      <c r="G47" s="37" t="n"/>
-      <c r="H47" s="37" t="n"/>
-      <c r="I47" s="37" t="n"/>
-      <c r="J47" s="37" t="n"/>
-      <c r="K47" s="37" t="n"/>
-      <c r="L47" s="37" t="n"/>
-      <c r="M47" s="37" t="n"/>
-      <c r="N47" s="37" t="n"/>
-      <c r="O47" s="37" t="n"/>
-      <c r="P47" s="37" t="n"/>
-      <c r="Q47" s="37" t="n"/>
-      <c r="R47" s="35">
+      <c r="B47" s="37" t="n"/>
+      <c r="C47" s="37" t="n"/>
+      <c r="D47" s="46" t="n"/>
+      <c r="E47" s="46" t="n"/>
+      <c r="F47" s="38" t="n"/>
+      <c r="G47" s="38" t="n"/>
+      <c r="H47" s="38" t="n"/>
+      <c r="I47" s="38" t="n"/>
+      <c r="J47" s="38" t="n"/>
+      <c r="K47" s="38" t="n"/>
+      <c r="L47" s="38" t="n"/>
+      <c r="M47" s="38" t="n"/>
+      <c r="N47" s="38" t="n"/>
+      <c r="O47" s="38" t="n"/>
+      <c r="P47" s="38" t="n"/>
+      <c r="Q47" s="38" t="n"/>
+      <c r="R47" s="36">
         <f>IF(COUNT(F47:Q47)=0,"",SUM(F47:Q47))</f>
         <v/>
       </c>
@@ -23633,23 +23648,23 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n"/>
-      <c r="B48" s="38" t="n"/>
-      <c r="C48" s="38" t="n"/>
-      <c r="D48" s="44" t="n"/>
-      <c r="E48" s="44" t="n"/>
-      <c r="F48" s="39" t="n"/>
-      <c r="G48" s="39" t="n"/>
-      <c r="H48" s="39" t="n"/>
-      <c r="I48" s="39" t="n"/>
-      <c r="J48" s="39" t="n"/>
-      <c r="K48" s="39" t="n"/>
-      <c r="L48" s="39" t="n"/>
-      <c r="M48" s="39" t="n"/>
-      <c r="N48" s="39" t="n"/>
-      <c r="O48" s="39" t="n"/>
-      <c r="P48" s="39" t="n"/>
-      <c r="Q48" s="39" t="n"/>
-      <c r="R48" s="35">
+      <c r="B48" s="39" t="n"/>
+      <c r="C48" s="39" t="n"/>
+      <c r="D48" s="45" t="n"/>
+      <c r="E48" s="45" t="n"/>
+      <c r="F48" s="40" t="n"/>
+      <c r="G48" s="40" t="n"/>
+      <c r="H48" s="40" t="n"/>
+      <c r="I48" s="40" t="n"/>
+      <c r="J48" s="40" t="n"/>
+      <c r="K48" s="40" t="n"/>
+      <c r="L48" s="40" t="n"/>
+      <c r="M48" s="40" t="n"/>
+      <c r="N48" s="40" t="n"/>
+      <c r="O48" s="40" t="n"/>
+      <c r="P48" s="40" t="n"/>
+      <c r="Q48" s="40" t="n"/>
+      <c r="R48" s="36">
         <f>IF(COUNT(F48:Q48)=0,"",SUM(F48:Q48))</f>
         <v/>
       </c>
@@ -23668,23 +23683,23 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n"/>
-      <c r="B49" s="36" t="n"/>
-      <c r="C49" s="36" t="n"/>
-      <c r="D49" s="45" t="n"/>
-      <c r="E49" s="45" t="n"/>
-      <c r="F49" s="37" t="n"/>
-      <c r="G49" s="37" t="n"/>
-      <c r="H49" s="37" t="n"/>
-      <c r="I49" s="37" t="n"/>
-      <c r="J49" s="37" t="n"/>
-      <c r="K49" s="37" t="n"/>
-      <c r="L49" s="37" t="n"/>
-      <c r="M49" s="37" t="n"/>
-      <c r="N49" s="37" t="n"/>
-      <c r="O49" s="37" t="n"/>
-      <c r="P49" s="37" t="n"/>
-      <c r="Q49" s="37" t="n"/>
-      <c r="R49" s="35">
+      <c r="B49" s="37" t="n"/>
+      <c r="C49" s="37" t="n"/>
+      <c r="D49" s="46" t="n"/>
+      <c r="E49" s="46" t="n"/>
+      <c r="F49" s="38" t="n"/>
+      <c r="G49" s="38" t="n"/>
+      <c r="H49" s="38" t="n"/>
+      <c r="I49" s="38" t="n"/>
+      <c r="J49" s="38" t="n"/>
+      <c r="K49" s="38" t="n"/>
+      <c r="L49" s="38" t="n"/>
+      <c r="M49" s="38" t="n"/>
+      <c r="N49" s="38" t="n"/>
+      <c r="O49" s="38" t="n"/>
+      <c r="P49" s="38" t="n"/>
+      <c r="Q49" s="38" t="n"/>
+      <c r="R49" s="36">
         <f>IF(COUNT(F49:Q49)=0,"",SUM(F49:Q49))</f>
         <v/>
       </c>
@@ -23703,23 +23718,23 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n"/>
-      <c r="B50" s="38" t="n"/>
-      <c r="C50" s="38" t="n"/>
-      <c r="D50" s="44" t="n"/>
-      <c r="E50" s="44" t="n"/>
-      <c r="F50" s="39" t="n"/>
-      <c r="G50" s="39" t="n"/>
-      <c r="H50" s="39" t="n"/>
-      <c r="I50" s="39" t="n"/>
-      <c r="J50" s="39" t="n"/>
-      <c r="K50" s="39" t="n"/>
-      <c r="L50" s="39" t="n"/>
-      <c r="M50" s="39" t="n"/>
-      <c r="N50" s="39" t="n"/>
-      <c r="O50" s="39" t="n"/>
-      <c r="P50" s="39" t="n"/>
-      <c r="Q50" s="39" t="n"/>
-      <c r="R50" s="35">
+      <c r="B50" s="39" t="n"/>
+      <c r="C50" s="39" t="n"/>
+      <c r="D50" s="45" t="n"/>
+      <c r="E50" s="45" t="n"/>
+      <c r="F50" s="40" t="n"/>
+      <c r="G50" s="40" t="n"/>
+      <c r="H50" s="40" t="n"/>
+      <c r="I50" s="40" t="n"/>
+      <c r="J50" s="40" t="n"/>
+      <c r="K50" s="40" t="n"/>
+      <c r="L50" s="40" t="n"/>
+      <c r="M50" s="40" t="n"/>
+      <c r="N50" s="40" t="n"/>
+      <c r="O50" s="40" t="n"/>
+      <c r="P50" s="40" t="n"/>
+      <c r="Q50" s="40" t="n"/>
+      <c r="R50" s="36">
         <f>IF(COUNT(F50:Q50)=0,"",SUM(F50:Q50))</f>
         <v/>
       </c>
@@ -23738,23 +23753,23 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n"/>
-      <c r="B51" s="36" t="n"/>
-      <c r="C51" s="36" t="n"/>
-      <c r="D51" s="45" t="n"/>
-      <c r="E51" s="45" t="n"/>
-      <c r="F51" s="37" t="n"/>
-      <c r="G51" s="37" t="n"/>
-      <c r="H51" s="37" t="n"/>
-      <c r="I51" s="37" t="n"/>
-      <c r="J51" s="37" t="n"/>
-      <c r="K51" s="37" t="n"/>
-      <c r="L51" s="37" t="n"/>
-      <c r="M51" s="37" t="n"/>
-      <c r="N51" s="37" t="n"/>
-      <c r="O51" s="37" t="n"/>
-      <c r="P51" s="37" t="n"/>
-      <c r="Q51" s="37" t="n"/>
-      <c r="R51" s="35">
+      <c r="B51" s="37" t="n"/>
+      <c r="C51" s="37" t="n"/>
+      <c r="D51" s="46" t="n"/>
+      <c r="E51" s="46" t="n"/>
+      <c r="F51" s="38" t="n"/>
+      <c r="G51" s="38" t="n"/>
+      <c r="H51" s="38" t="n"/>
+      <c r="I51" s="38" t="n"/>
+      <c r="J51" s="38" t="n"/>
+      <c r="K51" s="38" t="n"/>
+      <c r="L51" s="38" t="n"/>
+      <c r="M51" s="38" t="n"/>
+      <c r="N51" s="38" t="n"/>
+      <c r="O51" s="38" t="n"/>
+      <c r="P51" s="38" t="n"/>
+      <c r="Q51" s="38" t="n"/>
+      <c r="R51" s="36">
         <f>IF(COUNT(F51:Q51)=0,"",SUM(F51:Q51))</f>
         <v/>
       </c>
@@ -23773,23 +23788,23 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n"/>
-      <c r="B52" s="38" t="n"/>
-      <c r="C52" s="38" t="n"/>
-      <c r="D52" s="44" t="n"/>
-      <c r="E52" s="44" t="n"/>
-      <c r="F52" s="39" t="n"/>
-      <c r="G52" s="39" t="n"/>
-      <c r="H52" s="39" t="n"/>
-      <c r="I52" s="39" t="n"/>
-      <c r="J52" s="39" t="n"/>
-      <c r="K52" s="39" t="n"/>
-      <c r="L52" s="39" t="n"/>
-      <c r="M52" s="39" t="n"/>
-      <c r="N52" s="39" t="n"/>
-      <c r="O52" s="39" t="n"/>
-      <c r="P52" s="39" t="n"/>
-      <c r="Q52" s="39" t="n"/>
-      <c r="R52" s="35">
+      <c r="B52" s="39" t="n"/>
+      <c r="C52" s="39" t="n"/>
+      <c r="D52" s="45" t="n"/>
+      <c r="E52" s="45" t="n"/>
+      <c r="F52" s="40" t="n"/>
+      <c r="G52" s="40" t="n"/>
+      <c r="H52" s="40" t="n"/>
+      <c r="I52" s="40" t="n"/>
+      <c r="J52" s="40" t="n"/>
+      <c r="K52" s="40" t="n"/>
+      <c r="L52" s="40" t="n"/>
+      <c r="M52" s="40" t="n"/>
+      <c r="N52" s="40" t="n"/>
+      <c r="O52" s="40" t="n"/>
+      <c r="P52" s="40" t="n"/>
+      <c r="Q52" s="40" t="n"/>
+      <c r="R52" s="36">
         <f>IF(COUNT(F52:Q52)=0,"",SUM(F52:Q52))</f>
         <v/>
       </c>
@@ -23808,23 +23823,23 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n"/>
-      <c r="B53" s="36" t="n"/>
-      <c r="C53" s="36" t="n"/>
-      <c r="D53" s="45" t="n"/>
-      <c r="E53" s="45" t="n"/>
-      <c r="F53" s="37" t="n"/>
-      <c r="G53" s="37" t="n"/>
-      <c r="H53" s="37" t="n"/>
-      <c r="I53" s="37" t="n"/>
-      <c r="J53" s="37" t="n"/>
-      <c r="K53" s="37" t="n"/>
-      <c r="L53" s="37" t="n"/>
-      <c r="M53" s="37" t="n"/>
-      <c r="N53" s="37" t="n"/>
-      <c r="O53" s="37" t="n"/>
-      <c r="P53" s="37" t="n"/>
-      <c r="Q53" s="37" t="n"/>
-      <c r="R53" s="35">
+      <c r="B53" s="37" t="n"/>
+      <c r="C53" s="37" t="n"/>
+      <c r="D53" s="46" t="n"/>
+      <c r="E53" s="46" t="n"/>
+      <c r="F53" s="38" t="n"/>
+      <c r="G53" s="38" t="n"/>
+      <c r="H53" s="38" t="n"/>
+      <c r="I53" s="38" t="n"/>
+      <c r="J53" s="38" t="n"/>
+      <c r="K53" s="38" t="n"/>
+      <c r="L53" s="38" t="n"/>
+      <c r="M53" s="38" t="n"/>
+      <c r="N53" s="38" t="n"/>
+      <c r="O53" s="38" t="n"/>
+      <c r="P53" s="38" t="n"/>
+      <c r="Q53" s="38" t="n"/>
+      <c r="R53" s="36">
         <f>IF(COUNT(F53:Q53)=0,"",SUM(F53:Q53))</f>
         <v/>
       </c>
@@ -23843,23 +23858,23 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n"/>
-      <c r="B54" s="38" t="n"/>
-      <c r="C54" s="38" t="n"/>
-      <c r="D54" s="44" t="n"/>
-      <c r="E54" s="44" t="n"/>
-      <c r="F54" s="39" t="n"/>
-      <c r="G54" s="39" t="n"/>
-      <c r="H54" s="39" t="n"/>
-      <c r="I54" s="39" t="n"/>
-      <c r="J54" s="39" t="n"/>
-      <c r="K54" s="39" t="n"/>
-      <c r="L54" s="39" t="n"/>
-      <c r="M54" s="39" t="n"/>
-      <c r="N54" s="39" t="n"/>
-      <c r="O54" s="39" t="n"/>
-      <c r="P54" s="39" t="n"/>
-      <c r="Q54" s="39" t="n"/>
-      <c r="R54" s="35">
+      <c r="B54" s="39" t="n"/>
+      <c r="C54" s="39" t="n"/>
+      <c r="D54" s="45" t="n"/>
+      <c r="E54" s="45" t="n"/>
+      <c r="F54" s="40" t="n"/>
+      <c r="G54" s="40" t="n"/>
+      <c r="H54" s="40" t="n"/>
+      <c r="I54" s="40" t="n"/>
+      <c r="J54" s="40" t="n"/>
+      <c r="K54" s="40" t="n"/>
+      <c r="L54" s="40" t="n"/>
+      <c r="M54" s="40" t="n"/>
+      <c r="N54" s="40" t="n"/>
+      <c r="O54" s="40" t="n"/>
+      <c r="P54" s="40" t="n"/>
+      <c r="Q54" s="40" t="n"/>
+      <c r="R54" s="36">
         <f>IF(COUNT(F54:Q54)=0,"",SUM(F54:Q54))</f>
         <v/>
       </c>
@@ -23878,23 +23893,23 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n"/>
-      <c r="B55" s="36" t="n"/>
-      <c r="C55" s="36" t="n"/>
-      <c r="D55" s="45" t="n"/>
-      <c r="E55" s="45" t="n"/>
-      <c r="F55" s="37" t="n"/>
-      <c r="G55" s="37" t="n"/>
-      <c r="H55" s="37" t="n"/>
-      <c r="I55" s="37" t="n"/>
-      <c r="J55" s="37" t="n"/>
-      <c r="K55" s="37" t="n"/>
-      <c r="L55" s="37" t="n"/>
-      <c r="M55" s="37" t="n"/>
-      <c r="N55" s="37" t="n"/>
-      <c r="O55" s="37" t="n"/>
-      <c r="P55" s="37" t="n"/>
-      <c r="Q55" s="37" t="n"/>
-      <c r="R55" s="35">
+      <c r="B55" s="37" t="n"/>
+      <c r="C55" s="37" t="n"/>
+      <c r="D55" s="46" t="n"/>
+      <c r="E55" s="46" t="n"/>
+      <c r="F55" s="38" t="n"/>
+      <c r="G55" s="38" t="n"/>
+      <c r="H55" s="38" t="n"/>
+      <c r="I55" s="38" t="n"/>
+      <c r="J55" s="38" t="n"/>
+      <c r="K55" s="38" t="n"/>
+      <c r="L55" s="38" t="n"/>
+      <c r="M55" s="38" t="n"/>
+      <c r="N55" s="38" t="n"/>
+      <c r="O55" s="38" t="n"/>
+      <c r="P55" s="38" t="n"/>
+      <c r="Q55" s="38" t="n"/>
+      <c r="R55" s="36">
         <f>IF(COUNT(F55:Q55)=0,"",SUM(F55:Q55))</f>
         <v/>
       </c>
@@ -23913,23 +23928,23 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n"/>
-      <c r="B56" s="38" t="n"/>
-      <c r="C56" s="38" t="n"/>
-      <c r="D56" s="44" t="n"/>
-      <c r="E56" s="44" t="n"/>
-      <c r="F56" s="39" t="n"/>
-      <c r="G56" s="39" t="n"/>
-      <c r="H56" s="39" t="n"/>
-      <c r="I56" s="39" t="n"/>
-      <c r="J56" s="39" t="n"/>
-      <c r="K56" s="39" t="n"/>
-      <c r="L56" s="39" t="n"/>
-      <c r="M56" s="39" t="n"/>
-      <c r="N56" s="39" t="n"/>
-      <c r="O56" s="39" t="n"/>
-      <c r="P56" s="39" t="n"/>
-      <c r="Q56" s="39" t="n"/>
-      <c r="R56" s="35">
+      <c r="B56" s="39" t="n"/>
+      <c r="C56" s="39" t="n"/>
+      <c r="D56" s="45" t="n"/>
+      <c r="E56" s="45" t="n"/>
+      <c r="F56" s="40" t="n"/>
+      <c r="G56" s="40" t="n"/>
+      <c r="H56" s="40" t="n"/>
+      <c r="I56" s="40" t="n"/>
+      <c r="J56" s="40" t="n"/>
+      <c r="K56" s="40" t="n"/>
+      <c r="L56" s="40" t="n"/>
+      <c r="M56" s="40" t="n"/>
+      <c r="N56" s="40" t="n"/>
+      <c r="O56" s="40" t="n"/>
+      <c r="P56" s="40" t="n"/>
+      <c r="Q56" s="40" t="n"/>
+      <c r="R56" s="36">
         <f>IF(COUNT(F56:Q56)=0,"",SUM(F56:Q56))</f>
         <v/>
       </c>
@@ -23948,23 +23963,23 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n"/>
-      <c r="B57" s="36" t="n"/>
-      <c r="C57" s="36" t="n"/>
-      <c r="D57" s="45" t="n"/>
-      <c r="E57" s="45" t="n"/>
-      <c r="F57" s="37" t="n"/>
-      <c r="G57" s="37" t="n"/>
-      <c r="H57" s="37" t="n"/>
-      <c r="I57" s="37" t="n"/>
-      <c r="J57" s="37" t="n"/>
-      <c r="K57" s="37" t="n"/>
-      <c r="L57" s="37" t="n"/>
-      <c r="M57" s="37" t="n"/>
-      <c r="N57" s="37" t="n"/>
-      <c r="O57" s="37" t="n"/>
-      <c r="P57" s="37" t="n"/>
-      <c r="Q57" s="37" t="n"/>
-      <c r="R57" s="35">
+      <c r="B57" s="37" t="n"/>
+      <c r="C57" s="37" t="n"/>
+      <c r="D57" s="46" t="n"/>
+      <c r="E57" s="46" t="n"/>
+      <c r="F57" s="38" t="n"/>
+      <c r="G57" s="38" t="n"/>
+      <c r="H57" s="38" t="n"/>
+      <c r="I57" s="38" t="n"/>
+      <c r="J57" s="38" t="n"/>
+      <c r="K57" s="38" t="n"/>
+      <c r="L57" s="38" t="n"/>
+      <c r="M57" s="38" t="n"/>
+      <c r="N57" s="38" t="n"/>
+      <c r="O57" s="38" t="n"/>
+      <c r="P57" s="38" t="n"/>
+      <c r="Q57" s="38" t="n"/>
+      <c r="R57" s="36">
         <f>IF(COUNT(F57:Q57)=0,"",SUM(F57:Q57))</f>
         <v/>
       </c>
@@ -23983,23 +23998,23 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n"/>
-      <c r="B58" s="38" t="n"/>
-      <c r="C58" s="38" t="n"/>
-      <c r="D58" s="44" t="n"/>
-      <c r="E58" s="44" t="n"/>
-      <c r="F58" s="39" t="n"/>
-      <c r="G58" s="39" t="n"/>
-      <c r="H58" s="39" t="n"/>
-      <c r="I58" s="39" t="n"/>
-      <c r="J58" s="39" t="n"/>
-      <c r="K58" s="39" t="n"/>
-      <c r="L58" s="39" t="n"/>
-      <c r="M58" s="39" t="n"/>
-      <c r="N58" s="39" t="n"/>
-      <c r="O58" s="39" t="n"/>
-      <c r="P58" s="39" t="n"/>
-      <c r="Q58" s="39" t="n"/>
-      <c r="R58" s="35">
+      <c r="B58" s="39" t="n"/>
+      <c r="C58" s="39" t="n"/>
+      <c r="D58" s="45" t="n"/>
+      <c r="E58" s="45" t="n"/>
+      <c r="F58" s="40" t="n"/>
+      <c r="G58" s="40" t="n"/>
+      <c r="H58" s="40" t="n"/>
+      <c r="I58" s="40" t="n"/>
+      <c r="J58" s="40" t="n"/>
+      <c r="K58" s="40" t="n"/>
+      <c r="L58" s="40" t="n"/>
+      <c r="M58" s="40" t="n"/>
+      <c r="N58" s="40" t="n"/>
+      <c r="O58" s="40" t="n"/>
+      <c r="P58" s="40" t="n"/>
+      <c r="Q58" s="40" t="n"/>
+      <c r="R58" s="36">
         <f>IF(COUNT(F58:Q58)=0,"",SUM(F58:Q58))</f>
         <v/>
       </c>
@@ -24018,23 +24033,23 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n"/>
-      <c r="B59" s="36" t="n"/>
-      <c r="C59" s="36" t="n"/>
-      <c r="D59" s="45" t="n"/>
-      <c r="E59" s="45" t="n"/>
-      <c r="F59" s="37" t="n"/>
-      <c r="G59" s="37" t="n"/>
-      <c r="H59" s="37" t="n"/>
-      <c r="I59" s="37" t="n"/>
-      <c r="J59" s="37" t="n"/>
-      <c r="K59" s="37" t="n"/>
-      <c r="L59" s="37" t="n"/>
-      <c r="M59" s="37" t="n"/>
-      <c r="N59" s="37" t="n"/>
-      <c r="O59" s="37" t="n"/>
-      <c r="P59" s="37" t="n"/>
-      <c r="Q59" s="37" t="n"/>
-      <c r="R59" s="35">
+      <c r="B59" s="37" t="n"/>
+      <c r="C59" s="37" t="n"/>
+      <c r="D59" s="46" t="n"/>
+      <c r="E59" s="46" t="n"/>
+      <c r="F59" s="38" t="n"/>
+      <c r="G59" s="38" t="n"/>
+      <c r="H59" s="38" t="n"/>
+      <c r="I59" s="38" t="n"/>
+      <c r="J59" s="38" t="n"/>
+      <c r="K59" s="38" t="n"/>
+      <c r="L59" s="38" t="n"/>
+      <c r="M59" s="38" t="n"/>
+      <c r="N59" s="38" t="n"/>
+      <c r="O59" s="38" t="n"/>
+      <c r="P59" s="38" t="n"/>
+      <c r="Q59" s="38" t="n"/>
+      <c r="R59" s="36">
         <f>IF(COUNT(F59:Q59)=0,"",SUM(F59:Q59))</f>
         <v/>
       </c>
@@ -24053,23 +24068,23 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n"/>
-      <c r="B60" s="38" t="n"/>
-      <c r="C60" s="38" t="n"/>
-      <c r="D60" s="44" t="n"/>
-      <c r="E60" s="44" t="n"/>
-      <c r="F60" s="39" t="n"/>
-      <c r="G60" s="39" t="n"/>
-      <c r="H60" s="39" t="n"/>
-      <c r="I60" s="39" t="n"/>
-      <c r="J60" s="39" t="n"/>
-      <c r="K60" s="39" t="n"/>
-      <c r="L60" s="39" t="n"/>
-      <c r="M60" s="39" t="n"/>
-      <c r="N60" s="39" t="n"/>
-      <c r="O60" s="39" t="n"/>
-      <c r="P60" s="39" t="n"/>
-      <c r="Q60" s="39" t="n"/>
-      <c r="R60" s="35">
+      <c r="B60" s="39" t="n"/>
+      <c r="C60" s="39" t="n"/>
+      <c r="D60" s="45" t="n"/>
+      <c r="E60" s="45" t="n"/>
+      <c r="F60" s="40" t="n"/>
+      <c r="G60" s="40" t="n"/>
+      <c r="H60" s="40" t="n"/>
+      <c r="I60" s="40" t="n"/>
+      <c r="J60" s="40" t="n"/>
+      <c r="K60" s="40" t="n"/>
+      <c r="L60" s="40" t="n"/>
+      <c r="M60" s="40" t="n"/>
+      <c r="N60" s="40" t="n"/>
+      <c r="O60" s="40" t="n"/>
+      <c r="P60" s="40" t="n"/>
+      <c r="Q60" s="40" t="n"/>
+      <c r="R60" s="36">
         <f>IF(COUNT(F60:Q60)=0,"",SUM(F60:Q60))</f>
         <v/>
       </c>
@@ -24088,23 +24103,23 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n"/>
-      <c r="B61" s="36" t="n"/>
-      <c r="C61" s="36" t="n"/>
-      <c r="D61" s="45" t="n"/>
-      <c r="E61" s="45" t="n"/>
-      <c r="F61" s="37" t="n"/>
-      <c r="G61" s="37" t="n"/>
-      <c r="H61" s="37" t="n"/>
-      <c r="I61" s="37" t="n"/>
-      <c r="J61" s="37" t="n"/>
-      <c r="K61" s="37" t="n"/>
-      <c r="L61" s="37" t="n"/>
-      <c r="M61" s="37" t="n"/>
-      <c r="N61" s="37" t="n"/>
-      <c r="O61" s="37" t="n"/>
-      <c r="P61" s="37" t="n"/>
-      <c r="Q61" s="37" t="n"/>
-      <c r="R61" s="35">
+      <c r="B61" s="37" t="n"/>
+      <c r="C61" s="37" t="n"/>
+      <c r="D61" s="46" t="n"/>
+      <c r="E61" s="46" t="n"/>
+      <c r="F61" s="38" t="n"/>
+      <c r="G61" s="38" t="n"/>
+      <c r="H61" s="38" t="n"/>
+      <c r="I61" s="38" t="n"/>
+      <c r="J61" s="38" t="n"/>
+      <c r="K61" s="38" t="n"/>
+      <c r="L61" s="38" t="n"/>
+      <c r="M61" s="38" t="n"/>
+      <c r="N61" s="38" t="n"/>
+      <c r="O61" s="38" t="n"/>
+      <c r="P61" s="38" t="n"/>
+      <c r="Q61" s="38" t="n"/>
+      <c r="R61" s="36">
         <f>IF(COUNT(F61:Q61)=0,"",SUM(F61:Q61))</f>
         <v/>
       </c>
@@ -24123,23 +24138,23 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n"/>
-      <c r="B62" s="38" t="n"/>
-      <c r="C62" s="38" t="n"/>
-      <c r="D62" s="44" t="n"/>
-      <c r="E62" s="44" t="n"/>
-      <c r="F62" s="39" t="n"/>
-      <c r="G62" s="39" t="n"/>
-      <c r="H62" s="39" t="n"/>
-      <c r="I62" s="39" t="n"/>
-      <c r="J62" s="39" t="n"/>
-      <c r="K62" s="39" t="n"/>
-      <c r="L62" s="39" t="n"/>
-      <c r="M62" s="39" t="n"/>
-      <c r="N62" s="39" t="n"/>
-      <c r="O62" s="39" t="n"/>
-      <c r="P62" s="39" t="n"/>
-      <c r="Q62" s="39" t="n"/>
-      <c r="R62" s="35">
+      <c r="B62" s="39" t="n"/>
+      <c r="C62" s="39" t="n"/>
+      <c r="D62" s="45" t="n"/>
+      <c r="E62" s="45" t="n"/>
+      <c r="F62" s="40" t="n"/>
+      <c r="G62" s="40" t="n"/>
+      <c r="H62" s="40" t="n"/>
+      <c r="I62" s="40" t="n"/>
+      <c r="J62" s="40" t="n"/>
+      <c r="K62" s="40" t="n"/>
+      <c r="L62" s="40" t="n"/>
+      <c r="M62" s="40" t="n"/>
+      <c r="N62" s="40" t="n"/>
+      <c r="O62" s="40" t="n"/>
+      <c r="P62" s="40" t="n"/>
+      <c r="Q62" s="40" t="n"/>
+      <c r="R62" s="36">
         <f>IF(COUNT(F62:Q62)=0,"",SUM(F62:Q62))</f>
         <v/>
       </c>
@@ -24158,23 +24173,23 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n"/>
-      <c r="B63" s="36" t="n"/>
-      <c r="C63" s="36" t="n"/>
-      <c r="D63" s="45" t="n"/>
-      <c r="E63" s="45" t="n"/>
-      <c r="F63" s="37" t="n"/>
-      <c r="G63" s="37" t="n"/>
-      <c r="H63" s="37" t="n"/>
-      <c r="I63" s="37" t="n"/>
-      <c r="J63" s="37" t="n"/>
-      <c r="K63" s="37" t="n"/>
-      <c r="L63" s="37" t="n"/>
-      <c r="M63" s="37" t="n"/>
-      <c r="N63" s="37" t="n"/>
-      <c r="O63" s="37" t="n"/>
-      <c r="P63" s="37" t="n"/>
-      <c r="Q63" s="37" t="n"/>
-      <c r="R63" s="35">
+      <c r="B63" s="37" t="n"/>
+      <c r="C63" s="37" t="n"/>
+      <c r="D63" s="46" t="n"/>
+      <c r="E63" s="46" t="n"/>
+      <c r="F63" s="38" t="n"/>
+      <c r="G63" s="38" t="n"/>
+      <c r="H63" s="38" t="n"/>
+      <c r="I63" s="38" t="n"/>
+      <c r="J63" s="38" t="n"/>
+      <c r="K63" s="38" t="n"/>
+      <c r="L63" s="38" t="n"/>
+      <c r="M63" s="38" t="n"/>
+      <c r="N63" s="38" t="n"/>
+      <c r="O63" s="38" t="n"/>
+      <c r="P63" s="38" t="n"/>
+      <c r="Q63" s="38" t="n"/>
+      <c r="R63" s="36">
         <f>IF(COUNT(F63:Q63)=0,"",SUM(F63:Q63))</f>
         <v/>
       </c>
@@ -24193,23 +24208,23 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n"/>
-      <c r="B64" s="38" t="n"/>
-      <c r="C64" s="38" t="n"/>
-      <c r="D64" s="44" t="n"/>
-      <c r="E64" s="44" t="n"/>
-      <c r="F64" s="39" t="n"/>
-      <c r="G64" s="39" t="n"/>
-      <c r="H64" s="39" t="n"/>
-      <c r="I64" s="39" t="n"/>
-      <c r="J64" s="39" t="n"/>
-      <c r="K64" s="39" t="n"/>
-      <c r="L64" s="39" t="n"/>
-      <c r="M64" s="39" t="n"/>
-      <c r="N64" s="39" t="n"/>
-      <c r="O64" s="39" t="n"/>
-      <c r="P64" s="39" t="n"/>
-      <c r="Q64" s="39" t="n"/>
-      <c r="R64" s="35">
+      <c r="B64" s="39" t="n"/>
+      <c r="C64" s="39" t="n"/>
+      <c r="D64" s="45" t="n"/>
+      <c r="E64" s="45" t="n"/>
+      <c r="F64" s="40" t="n"/>
+      <c r="G64" s="40" t="n"/>
+      <c r="H64" s="40" t="n"/>
+      <c r="I64" s="40" t="n"/>
+      <c r="J64" s="40" t="n"/>
+      <c r="K64" s="40" t="n"/>
+      <c r="L64" s="40" t="n"/>
+      <c r="M64" s="40" t="n"/>
+      <c r="N64" s="40" t="n"/>
+      <c r="O64" s="40" t="n"/>
+      <c r="P64" s="40" t="n"/>
+      <c r="Q64" s="40" t="n"/>
+      <c r="R64" s="36">
         <f>IF(COUNT(F64:Q64)=0,"",SUM(F64:Q64))</f>
         <v/>
       </c>
@@ -24228,23 +24243,23 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n"/>
-      <c r="B65" s="36" t="n"/>
-      <c r="C65" s="36" t="n"/>
-      <c r="D65" s="45" t="n"/>
-      <c r="E65" s="45" t="n"/>
-      <c r="F65" s="37" t="n"/>
-      <c r="G65" s="37" t="n"/>
-      <c r="H65" s="37" t="n"/>
-      <c r="I65" s="37" t="n"/>
-      <c r="J65" s="37" t="n"/>
-      <c r="K65" s="37" t="n"/>
-      <c r="L65" s="37" t="n"/>
-      <c r="M65" s="37" t="n"/>
-      <c r="N65" s="37" t="n"/>
-      <c r="O65" s="37" t="n"/>
-      <c r="P65" s="37" t="n"/>
-      <c r="Q65" s="37" t="n"/>
-      <c r="R65" s="35">
+      <c r="B65" s="37" t="n"/>
+      <c r="C65" s="37" t="n"/>
+      <c r="D65" s="46" t="n"/>
+      <c r="E65" s="46" t="n"/>
+      <c r="F65" s="38" t="n"/>
+      <c r="G65" s="38" t="n"/>
+      <c r="H65" s="38" t="n"/>
+      <c r="I65" s="38" t="n"/>
+      <c r="J65" s="38" t="n"/>
+      <c r="K65" s="38" t="n"/>
+      <c r="L65" s="38" t="n"/>
+      <c r="M65" s="38" t="n"/>
+      <c r="N65" s="38" t="n"/>
+      <c r="O65" s="38" t="n"/>
+      <c r="P65" s="38" t="n"/>
+      <c r="Q65" s="38" t="n"/>
+      <c r="R65" s="36">
         <f>IF(COUNT(F65:Q65)=0,"",SUM(F65:Q65))</f>
         <v/>
       </c>
@@ -24263,63 +24278,63 @@
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="1" t="n"/>
-      <c r="B66" s="24" t="inlineStr">
+      <c r="B66" s="25" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C66" s="24" t="n"/>
-      <c r="D66" s="24" t="n"/>
-      <c r="E66" s="24" t="n"/>
-      <c r="F66" s="28">
+      <c r="C66" s="25" t="n"/>
+      <c r="D66" s="25" t="n"/>
+      <c r="E66" s="25" t="n"/>
+      <c r="F66" s="29">
         <f>SUM(F6:F65)</f>
         <v/>
       </c>
-      <c r="G66" s="28">
+      <c r="G66" s="29">
         <f>SUM(G6:G65)</f>
         <v/>
       </c>
-      <c r="H66" s="28">
+      <c r="H66" s="29">
         <f>SUM(H6:H65)</f>
         <v/>
       </c>
-      <c r="I66" s="28">
+      <c r="I66" s="29">
         <f>SUM(I6:I65)</f>
         <v/>
       </c>
-      <c r="J66" s="28">
+      <c r="J66" s="29">
         <f>SUM(J6:J65)</f>
         <v/>
       </c>
-      <c r="K66" s="28">
+      <c r="K66" s="29">
         <f>SUM(K6:K65)</f>
         <v/>
       </c>
-      <c r="L66" s="28">
+      <c r="L66" s="29">
         <f>SUM(L6:L65)</f>
         <v/>
       </c>
-      <c r="M66" s="28">
+      <c r="M66" s="29">
         <f>SUM(M6:M65)</f>
         <v/>
       </c>
-      <c r="N66" s="28">
+      <c r="N66" s="29">
         <f>SUM(N6:N65)</f>
         <v/>
       </c>
-      <c r="O66" s="28">
+      <c r="O66" s="29">
         <f>SUM(O6:O65)</f>
         <v/>
       </c>
-      <c r="P66" s="28">
+      <c r="P66" s="29">
         <f>SUM(P6:P65)</f>
         <v/>
       </c>
-      <c r="Q66" s="28">
+      <c r="Q66" s="29">
         <f>SUM(Q6:Q65)</f>
         <v/>
       </c>
-      <c r="R66" s="28">
+      <c r="R66" s="29">
         <f>SUM(R6:R65)</f>
         <v/>
       </c>
@@ -28625,8 +28640,9 @@
       <c r="AD200" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B2:R2"/>
+    <mergeCell ref="B4:R4"/>
     <mergeCell ref="B3:R3"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D65">
@@ -28642,8 +28658,19 @@
       <formula1>=Lists!$B$2:$B$3</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;R&amp;8 &amp;K9AA3C2Budget Planner - Claude Skill by 6inq</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -28759,15 +28786,13 @@
       <c r="AC3" s="1" t="n"/>
       <c r="AD3" s="1" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" ht="14" customHeight="1">
       <c r="A4" s="1" t="n"/>
-      <c r="B4" s="1" t="n"/>
-      <c r="C4" s="1" t="n"/>
-      <c r="D4" s="1" t="n"/>
-      <c r="E4" s="1" t="n"/>
-      <c r="F4" s="1" t="n"/>
-      <c r="G4" s="1" t="n"/>
-      <c r="H4" s="1" t="n"/>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Budget Planner - Claude Skill by 6inq</t>
+        </is>
+      </c>
       <c r="I4" s="1" t="n"/>
       <c r="J4" s="1" t="n"/>
       <c r="K4" s="1" t="n"/>
@@ -28793,37 +28818,37 @@
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="1" t="n"/>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Debt</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>Balance</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>APR %</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>Min Payment</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>Months to Payoff</t>
         </is>
       </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>Est. Interest</t>
         </is>
       </c>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="H5" s="14" t="inlineStr">
         <is>
           <t>Payoff Date</t>
         </is>
@@ -28853,23 +28878,23 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
-      <c r="B6" s="38" t="inlineStr">
+      <c r="B6" s="39" t="inlineStr">
         <is>
           <t>Credit Card</t>
         </is>
       </c>
-      <c r="C6" s="39" t="n"/>
-      <c r="D6" s="46" t="n"/>
-      <c r="E6" s="39" t="n"/>
-      <c r="F6" s="47">
+      <c r="C6" s="40" t="n"/>
+      <c r="D6" s="47" t="n"/>
+      <c r="E6" s="40" t="n"/>
+      <c r="F6" s="48">
         <f>IF(OR(C6="",E6=""),"",IF(N(D6)=0,ROUNDUP(C6/E6,0),IFERROR(ROUNDUP(NPER(D6/1200,-E6,C6),0),"Never")))</f>
         <v/>
       </c>
-      <c r="G6" s="48">
+      <c r="G6" s="49">
         <f>IF(ISNUMBER(F6),MAX(0,F6*E6-C6),"")</f>
         <v/>
       </c>
-      <c r="H6" s="49">
+      <c r="H6" s="50">
         <f>IF(ISNUMBER(F6),EDATE(TODAY(),F6),"")</f>
         <v/>
       </c>
@@ -28898,23 +28923,23 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>Car Loan</t>
         </is>
       </c>
-      <c r="C7" s="37" t="n"/>
-      <c r="D7" s="50" t="n"/>
-      <c r="E7" s="37" t="n"/>
-      <c r="F7" s="47">
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="51" t="n"/>
+      <c r="E7" s="38" t="n"/>
+      <c r="F7" s="48">
         <f>IF(OR(C7="",E7=""),"",IF(N(D7)=0,ROUNDUP(C7/E7,0),IFERROR(ROUNDUP(NPER(D7/1200,-E7,C7),0),"Never")))</f>
         <v/>
       </c>
-      <c r="G7" s="48">
+      <c r="G7" s="49">
         <f>IF(ISNUMBER(F7),MAX(0,F7*E7-C7),"")</f>
         <v/>
       </c>
-      <c r="H7" s="49">
+      <c r="H7" s="50">
         <f>IF(ISNUMBER(F7),EDATE(TODAY(),F7),"")</f>
         <v/>
       </c>
@@ -28943,19 +28968,19 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
-      <c r="B8" s="38" t="n"/>
-      <c r="C8" s="39" t="n"/>
-      <c r="D8" s="46" t="n"/>
-      <c r="E8" s="39" t="n"/>
-      <c r="F8" s="47">
+      <c r="B8" s="39" t="n"/>
+      <c r="C8" s="40" t="n"/>
+      <c r="D8" s="47" t="n"/>
+      <c r="E8" s="40" t="n"/>
+      <c r="F8" s="48">
         <f>IF(OR(C8="",E8=""),"",IF(N(D8)=0,ROUNDUP(C8/E8,0),IFERROR(ROUNDUP(NPER(D8/1200,-E8,C8),0),"Never")))</f>
         <v/>
       </c>
-      <c r="G8" s="48">
+      <c r="G8" s="49">
         <f>IF(ISNUMBER(F8),MAX(0,F8*E8-C8),"")</f>
         <v/>
       </c>
-      <c r="H8" s="49">
+      <c r="H8" s="50">
         <f>IF(ISNUMBER(F8),EDATE(TODAY(),F8),"")</f>
         <v/>
       </c>
@@ -28984,19 +29009,19 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
-      <c r="B9" s="36" t="n"/>
-      <c r="C9" s="37" t="n"/>
-      <c r="D9" s="50" t="n"/>
-      <c r="E9" s="37" t="n"/>
-      <c r="F9" s="47">
+      <c r="B9" s="37" t="n"/>
+      <c r="C9" s="38" t="n"/>
+      <c r="D9" s="51" t="n"/>
+      <c r="E9" s="38" t="n"/>
+      <c r="F9" s="48">
         <f>IF(OR(C9="",E9=""),"",IF(N(D9)=0,ROUNDUP(C9/E9,0),IFERROR(ROUNDUP(NPER(D9/1200,-E9,C9),0),"Never")))</f>
         <v/>
       </c>
-      <c r="G9" s="48">
+      <c r="G9" s="49">
         <f>IF(ISNUMBER(F9),MAX(0,F9*E9-C9),"")</f>
         <v/>
       </c>
-      <c r="H9" s="49">
+      <c r="H9" s="50">
         <f>IF(ISNUMBER(F9),EDATE(TODAY(),F9),"")</f>
         <v/>
       </c>
@@ -29025,19 +29050,19 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
-      <c r="B10" s="38" t="n"/>
-      <c r="C10" s="39" t="n"/>
-      <c r="D10" s="46" t="n"/>
-      <c r="E10" s="39" t="n"/>
-      <c r="F10" s="47">
+      <c r="B10" s="39" t="n"/>
+      <c r="C10" s="40" t="n"/>
+      <c r="D10" s="47" t="n"/>
+      <c r="E10" s="40" t="n"/>
+      <c r="F10" s="48">
         <f>IF(OR(C10="",E10=""),"",IF(N(D10)=0,ROUNDUP(C10/E10,0),IFERROR(ROUNDUP(NPER(D10/1200,-E10,C10),0),"Never")))</f>
         <v/>
       </c>
-      <c r="G10" s="48">
+      <c r="G10" s="49">
         <f>IF(ISNUMBER(F10),MAX(0,F10*E10-C10),"")</f>
         <v/>
       </c>
-      <c r="H10" s="49">
+      <c r="H10" s="50">
         <f>IF(ISNUMBER(F10),EDATE(TODAY(),F10),"")</f>
         <v/>
       </c>
@@ -29066,19 +29091,19 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
-      <c r="B11" s="36" t="n"/>
-      <c r="C11" s="37" t="n"/>
-      <c r="D11" s="50" t="n"/>
-      <c r="E11" s="37" t="n"/>
-      <c r="F11" s="47">
+      <c r="B11" s="37" t="n"/>
+      <c r="C11" s="38" t="n"/>
+      <c r="D11" s="51" t="n"/>
+      <c r="E11" s="38" t="n"/>
+      <c r="F11" s="48">
         <f>IF(OR(C11="",E11=""),"",IF(N(D11)=0,ROUNDUP(C11/E11,0),IFERROR(ROUNDUP(NPER(D11/1200,-E11,C11),0),"Never")))</f>
         <v/>
       </c>
-      <c r="G11" s="48">
+      <c r="G11" s="49">
         <f>IF(ISNUMBER(F11),MAX(0,F11*E11-C11),"")</f>
         <v/>
       </c>
-      <c r="H11" s="49">
+      <c r="H11" s="50">
         <f>IF(ISNUMBER(F11),EDATE(TODAY(),F11),"")</f>
         <v/>
       </c>
@@ -29107,19 +29132,19 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
-      <c r="B12" s="38" t="n"/>
-      <c r="C12" s="39" t="n"/>
-      <c r="D12" s="46" t="n"/>
-      <c r="E12" s="39" t="n"/>
-      <c r="F12" s="47">
+      <c r="B12" s="39" t="n"/>
+      <c r="C12" s="40" t="n"/>
+      <c r="D12" s="47" t="n"/>
+      <c r="E12" s="40" t="n"/>
+      <c r="F12" s="48">
         <f>IF(OR(C12="",E12=""),"",IF(N(D12)=0,ROUNDUP(C12/E12,0),IFERROR(ROUNDUP(NPER(D12/1200,-E12,C12),0),"Never")))</f>
         <v/>
       </c>
-      <c r="G12" s="48">
+      <c r="G12" s="49">
         <f>IF(ISNUMBER(F12),MAX(0,F12*E12-C12),"")</f>
         <v/>
       </c>
-      <c r="H12" s="49">
+      <c r="H12" s="50">
         <f>IF(ISNUMBER(F12),EDATE(TODAY(),F12),"")</f>
         <v/>
       </c>
@@ -29148,19 +29173,19 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
-      <c r="B13" s="36" t="n"/>
-      <c r="C13" s="37" t="n"/>
-      <c r="D13" s="50" t="n"/>
-      <c r="E13" s="37" t="n"/>
-      <c r="F13" s="47">
+      <c r="B13" s="37" t="n"/>
+      <c r="C13" s="38" t="n"/>
+      <c r="D13" s="51" t="n"/>
+      <c r="E13" s="38" t="n"/>
+      <c r="F13" s="48">
         <f>IF(OR(C13="",E13=""),"",IF(N(D13)=0,ROUNDUP(C13/E13,0),IFERROR(ROUNDUP(NPER(D13/1200,-E13,C13),0),"Never")))</f>
         <v/>
       </c>
-      <c r="G13" s="48">
+      <c r="G13" s="49">
         <f>IF(ISNUMBER(F13),MAX(0,F13*E13-C13),"")</f>
         <v/>
       </c>
-      <c r="H13" s="49">
+      <c r="H13" s="50">
         <f>IF(ISNUMBER(F13),EDATE(TODAY(),F13),"")</f>
         <v/>
       </c>
@@ -29189,19 +29214,19 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
-      <c r="B14" s="38" t="n"/>
-      <c r="C14" s="39" t="n"/>
-      <c r="D14" s="46" t="n"/>
-      <c r="E14" s="39" t="n"/>
-      <c r="F14" s="47">
+      <c r="B14" s="39" t="n"/>
+      <c r="C14" s="40" t="n"/>
+      <c r="D14" s="47" t="n"/>
+      <c r="E14" s="40" t="n"/>
+      <c r="F14" s="48">
         <f>IF(OR(C14="",E14=""),"",IF(N(D14)=0,ROUNDUP(C14/E14,0),IFERROR(ROUNDUP(NPER(D14/1200,-E14,C14),0),"Never")))</f>
         <v/>
       </c>
-      <c r="G14" s="48">
+      <c r="G14" s="49">
         <f>IF(ISNUMBER(F14),MAX(0,F14*E14-C14),"")</f>
         <v/>
       </c>
-      <c r="H14" s="49">
+      <c r="H14" s="50">
         <f>IF(ISNUMBER(F14),EDATE(TODAY(),F14),"")</f>
         <v/>
       </c>
@@ -29230,19 +29255,19 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
-      <c r="B15" s="36" t="n"/>
-      <c r="C15" s="37" t="n"/>
-      <c r="D15" s="50" t="n"/>
-      <c r="E15" s="37" t="n"/>
-      <c r="F15" s="47">
+      <c r="B15" s="37" t="n"/>
+      <c r="C15" s="38" t="n"/>
+      <c r="D15" s="51" t="n"/>
+      <c r="E15" s="38" t="n"/>
+      <c r="F15" s="48">
         <f>IF(OR(C15="",E15=""),"",IF(N(D15)=0,ROUNDUP(C15/E15,0),IFERROR(ROUNDUP(NPER(D15/1200,-E15,C15),0),"Never")))</f>
         <v/>
       </c>
-      <c r="G15" s="48">
+      <c r="G15" s="49">
         <f>IF(ISNUMBER(F15),MAX(0,F15*E15-C15),"")</f>
         <v/>
       </c>
-      <c r="H15" s="49">
+      <c r="H15" s="50">
         <f>IF(ISNUMBER(F15),EDATE(TODAY(),F15),"")</f>
         <v/>
       </c>
@@ -29271,23 +29296,23 @@
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="1" t="n"/>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="29">
         <f>SUM(C6:C15)</f>
         <v/>
       </c>
-      <c r="D16" s="24" t="n"/>
-      <c r="E16" s="28">
+      <c r="D16" s="25" t="n"/>
+      <c r="E16" s="29">
         <f>SUM(E6:E15)</f>
         <v/>
       </c>
-      <c r="F16" s="24" t="n"/>
-      <c r="G16" s="24" t="n"/>
-      <c r="H16" s="24" t="n"/>
+      <c r="F16" s="25" t="n"/>
+      <c r="G16" s="25" t="n"/>
+      <c r="H16" s="25" t="n"/>
       <c r="I16" s="1" t="n"/>
       <c r="J16" s="1" t="n"/>
       <c r="K16" s="1" t="n"/>
@@ -35200,12 +35225,24 @@
       <c r="AD200" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B4:H4"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;R&amp;8 &amp;K9AA3C2Budget Planner - Claude Skill by 6inq</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -35215,7 +35252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35234,6 +35271,11 @@
           <t>Income Categories</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Planner Settings</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -35251,6 +35293,11 @@
           <t>Primary</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>{"format": 1, "budget_type": "personal", "title": "2026 Budget Planner", "owner": "", "year": 2026, "start_month": 1, "currency_symbol": "$", "mode": "light", "accent": "rose", "category_chart": "pie", "features": {"savings_goals": false, "debt_tracker": true}, "pay": {"frequency": "semimonthly", "amount": 0.0, "semimonthly_days": ["1", "15"]}}</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
